--- a/reports/devops-jobs-israel-2026-W41.xlsx
+++ b/reports/devops-jobs-israel-2026-W41.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="498">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="488">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-05T14:24:29</t>
+    <t xml:space="preserve">2026-10-06T13:12:25</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Junior %</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0%</t>
+    <t xml:space="preserve">2.1%</t>
   </si>
   <si>
     <t xml:space="preserve">Salary disclosure rate %</t>
@@ -522,13 +522,16 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-echo-4459855925</t>
   </si>
   <si>
-    <t xml:space="preserve">Wiz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-wiz-4406742504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-08</t>
+    <t xml:space="preserve">EX.CO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-ex-co-4474043806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-06</t>
   </si>
   <si>
     <t xml:space="preserve">Senior DevOps</t>
@@ -546,10 +549,13 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-eitan-medical-4461889332</t>
   </si>
   <si>
-    <t xml:space="preserve">At-Bay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-at-bay-4471503422</t>
+    <t xml:space="preserve">Senior DevOps Platform Engineer- CTI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dream</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-platform-engineer-cti-at-dream-4465727084</t>
   </si>
   <si>
     <t xml:space="preserve">Logica-IT</t>
@@ -603,487 +609,478 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-devops-engineer-at-harmonic-4360460066</t>
   </si>
   <si>
+    <t xml:space="preserve">Gini-Apps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gini-apps-4476189127</t>
+  </si>
+  <si>
     <t xml:space="preserve">Connecteam</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4428832411</t>
   </si>
   <si>
-    <t xml:space="preserve">Senior\Lead DevOps Engineer</t>
+    <t xml:space="preserve">Buildots</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-buildots-4473477683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zafran Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-zafran-security-4475510036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akeyless Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-akeyless-security-4457183616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blink</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-blink-4473214725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Automation &amp; Infrastructure as Code Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E2E Solutions IL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-automation-infrastructure-as-code-specialist-at-e2e-solutions-il-4473724881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer, AIOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-aiops-at-nvidia-4471970512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fetcherr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fetcherr-4429844723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer - Base44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-base44-at-base44-4474179911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cellebrite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-cellebrite-4469980397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GNESS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gness-4474945658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personetics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-personetics-4428829912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps / Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">recruitricks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-platform-engineer-at-recruitricks-4475527624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRE-DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apple</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-devops-engineer-at-apple-4471599502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moon Active</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-moon-active-4447023421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Principal DevOps Engineer - AI Platforms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-devops-engineer-ai-platforms-at-palo-alto-networks-4471749164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Polytex Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-polytex-technologies-4473474269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-gong-4457888927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Developer (37703)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-developer-37703-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4475562544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extreme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-devops-engineer-at-extreme-4475385097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VYBS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-vybs-4472171413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps - AI Factory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kaltura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-ai-factory-at-kaltura-4475505499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure and Automation Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dialog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-and-automation-engineer-at-dialog-4473641075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jobgether</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-jobgether-4472898137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior DevOps Engineer — AI-Native</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ArtAc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-devops-engineer-%E2%80%94-ai-native-at-artac-4476141177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4470850779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Data Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">evoke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-data-infrastructure-engineer-at-evoke-4462157157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staff Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grubhub</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/staff-site-reliability-engineer-at-grubhub-4473025762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr. SRE AI Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Navan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-sre-ai-engineer-at-navan-4437742346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Platform &amp; SRE Group Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-sre-group-leader-at-extreme-4450267100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Software Engineer, DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aiven</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-software-engineer-devops-at-aiven-4426867332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SciPlay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-sciplay-4391151881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medulla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-medulla-4475546635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure Engineer (Kubernetes &amp; Node.js)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oriient</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-kubernetes-node-js-at-oriient-4461069125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viz.ai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-viz-ai-4437383686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ThetaRay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-thetaray-4472910650</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Principal Devops &amp; Infra Tech Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sunbit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-devops-infra-tech-lead-at-sunbit-4474134295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platform &amp; DevOps Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pango</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-devops-team-lead-at-pango-4461809622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud DevOps Technical Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OnTarget Communications</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-devops-technical-manager-at-ontarget-communications-4475801640</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alice (Formerly ActiveFence)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-alice-formerly-activefence-4472729462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior AI Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guesty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-ai-platform-engineer-at-guesty-4473205757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Developer (DevOps and Infrastructure)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rapyd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-developer-devops-and-infrastructure-at-rapyd-4428485007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DoiT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-doit-4463987032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Backend &amp; Infrastructure Engineer | Supabase / Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MISTERBIT Technological Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/backend-infrastructure-engineer-supabase-cloud-at-misterbit-technological-solutions-4476190575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Infrastructure &amp; Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-cloud-engineer-at-moon-active-4447031167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-system-engineer-at-logica-it-4473666027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TeraSky</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-terasky-4455198528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer (FinOps oriented)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CloudTeam.ai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FinOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-finops-oriented-at-cloudteam-ai-4473603103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DriveNets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-devops-engineer-at-drivenets-4465793281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cato Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-system-engineer-at-cato-networks-4463471007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior System &amp; Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Final</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat HaSharon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-infrastructure-engineer-at-final-4475581791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure Engineer</t>
   </si>
   <si>
     <t xml:space="preserve">Elbit Systems Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-lead-devops-engineer-at-elbit-systems-israel-4375574113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Buildots</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-buildots-4473477683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tonkean (acquired by Coupa)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-tonkean-acquired-by-coupa-4471287704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zafran Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-zafran-security-4475510036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Akeyless Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-akeyless-security-4457183616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blink</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-blink-4473214725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Frame Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-frame-security-4462248477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Automation &amp; Infrastructure as Code Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E2E Solutions IL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-automation-infrastructure-as-code-specialist-at-e2e-solutions-il-4473724881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer, AIOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-aiops-at-nvidia-4471970512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer - Base44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Base44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-base44-at-base44-4474179911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cellebrite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-cellebrite-4469980397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-paragon-4400922396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Personetics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-personetics-4428829912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps / Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">recruitricks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-platform-engineer-at-recruitricks-4475527624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRE-DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Apple</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-devops-engineer-at-apple-4471599502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moon Active</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-moon-active-4447023421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Principal DevOps Engineer - AI Platforms</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-devops-engineer-ai-platforms-at-palo-alto-networks-4471749164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Polytex Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-polytex-technologies-4473474269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-gong-4457888927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Developer (37703)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-developer-37703-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4475562544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extreme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-devops-engineer-at-extreme-4475385097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer (Backend Oriented)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gini-Apps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-backend-oriented-at-gini-apps-4472772683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer- Avon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pagaya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-avon-at-pagaya-4472747108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VYBS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-vybs-4472171413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure &amp; Automation Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-automation-engineer-at-gini-apps-4472772736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps - AI Factory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kaltura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-ai-factory-at-kaltura-4475505499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure and Automation Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dialog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-and-automation-engineer-at-dialog-4473641075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer (Cortex)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-cortex-at-palo-alto-networks-4398688765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Staff Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grubhub</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/staff-site-reliability-engineer-at-grubhub-4473025762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sr. SRE AI Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Navan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-sre-ai-engineer-at-navan-4437742346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radware</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-radware-4462205520</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Platform &amp; SRE Group Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-sre-group-leader-at-extreme-4450267100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Software Engineer, DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aiven</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-software-engineer-devops-at-aiven-4426867332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Data Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">evoke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-data-infrastructure-engineer-at-evoke-4462157157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medulla</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-medulla-4475546635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure Engineer (Kubernetes &amp; Node.js)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oriient</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-kubernetes-node-js-at-oriient-4461069125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fetcherr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fetcherr-4429844723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Viz.ai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-viz-ai-4437383686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ThetaRay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-thetaray-4472910650</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Infrastructure Team Leader – Cloud Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Genpact</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-team-leader-%E2%80%93-cloud-platform-at-genpact-4471296292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Principal Devops &amp; Infra Tech Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sunbit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-devops-infra-tech-lead-at-sunbit-4474134295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps &amp; Backend Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Directeam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-backend-engineer-at-directeam-4471712480</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior AI Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Guesty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-ai-platform-engineer-at-guesty-4473205757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4470850779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Developer (DevOps and Infrastructure)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rapyd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-developer-devops-and-infrastructure-at-rapyd-4428485007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DoiT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-doit-4463987032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Infrastructure &amp; Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-cloud-engineer-at-moon-active-4447031167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-system-engineer-at-logica-it-4473666027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TeraSky</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-terasky-4455198528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (FinOps oriented)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CloudTeam.ai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FinOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-finops-oriented-at-cloudteam-ai-4473603103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DriveNets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-devops-engineer-at-drivenets-4465793281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cato Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-system-engineer-at-cato-networks-4463471007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior System &amp; Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Final</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat HaSharon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-infrastructure-engineer-at-final-4475581791</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-elbit-systems-israel-4474036853</t>
   </si>
   <si>
     <t xml:space="preserve">Microsoft System Engineer</t>
@@ -1116,234 +1113,246 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-talent-integration-4466204750</t>
   </si>
   <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Development Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clarivate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/development-operations-engineer-at-clarivate-4467992253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps &amp; Cloud Infrastructure Intern</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-infrastructure-intern-at-f5-4464650168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Student DevOps Engineer- CxP Commercial Foundation Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Terraform/IaC, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-devops-engineer-cxp-commercial-foundation-services-at-sap-4436819328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Terraform/IaC, Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HPC Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Terraform/IaC, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/hpc-operations-engineer-at-nvidia-4471977303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Technical Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4452212223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security Analyst (Student Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upwind Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/security-analyst-student-position-at-upwind-security-4473525994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineer Student, SPIV team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amazon Web Services (AWS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, CI/CD, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-student-spiv-team-at-amazon-web-services-aws-4456348779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Production Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Torq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6179167004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kela Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk / IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4461059776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Terraform/IaC, Networking, Automation</t>
+  </si>
+  <si>
     <t xml:space="preserve">Stealth Startup</t>
   </si>
   <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Terraform/IaC, Networking, Virtualization, Automation</t>
+  </si>
+  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-stealth-startup-4473602938</t>
   </si>
   <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strength Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.4%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.5%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Development Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clarivate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/development-operations-engineer-at-clarivate-4467992253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps &amp; Cloud Infrastructure Intern</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-infrastructure-intern-at-f5-4464650168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Student DevOps Engineer- CxP Commercial Foundation Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Terraform/IaC, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-devops-engineer-cxp-commercial-foundation-services-at-sap-4436819328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HPC Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Terraform/IaC, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/hpc-operations-engineer-at-nvidia-4471977303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Technical Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4452212223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security Analyst (Student Position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upwind Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/security-analyst-student-position-at-upwind-security-4473525994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineer Student, SPIV team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amazon Web Services (AWS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, CI/CD, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-student-spiv-team-at-amazon-web-services-aws-4456348779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Production Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Torq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6179167004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kela Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk / IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4461059776</t>
-  </si>
-  <si>
     <t xml:space="preserve">Technical Support Specialist</t>
   </si>
   <si>
@@ -1362,21 +1371,36 @@
     <t xml:space="preserve">OnCloud</t>
   </si>
   <si>
-    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
-  </si>
-  <si>
     <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
   </si>
   <si>
+    <t xml:space="preserve">TytoCare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-tytocare-4475569150</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Operations Student - Nights &amp; Weekend shifts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Voyantis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Git, Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-operations-student-nights-weekend-shifts-at-voyantis-4473649691</t>
+  </si>
+  <si>
     <t xml:space="preserve">Junior System Administrator (Monitoring Team)</t>
   </si>
   <si>
-    <t xml:space="preserve">Jobgether</t>
-  </si>
-  <si>
     <t xml:space="preserve">Junior SysAdmin / Linux</t>
   </si>
   <si>
@@ -1413,69 +1437,15 @@
     <t xml:space="preserve">2026-07-13</t>
   </si>
   <si>
-    <t xml:space="preserve">Python, Networking, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4449296509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator (24/7 Shift-Based)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-24-7-shift-based-at-evoke-4462157700</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring Technical Support Specialist (NOC)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SuperCom (NASDAQ: SPCB)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Cloud (any), Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/monitoring-technical-support-specialist-noc-at-supercom-nasdaq-spcb-4465838312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-11</t>
-  </si>
-  <si>
     <t xml:space="preserve">Roles requiring it</t>
   </si>
   <si>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
     <t xml:space="preserve">Troubleshooting</t>
   </si>
   <si>
-    <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cloud (any)</t>
   </si>
   <si>
@@ -1485,7 +1455,7 @@
     <t xml:space="preserve">Bash/Shell</t>
   </si>
   <si>
-    <t xml:space="preserve">Git</t>
+    <t xml:space="preserve">Terraform/IaC</t>
   </si>
   <si>
     <t xml:space="preserve">Elapsed (s)</t>
@@ -1637,7 +1607,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7">
@@ -1645,7 +1615,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
@@ -1653,7 +1623,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9">
@@ -1661,7 +1631,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>882</v>
+        <v>878</v>
       </c>
     </row>
     <row r="10">
@@ -1669,7 +1639,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1733,7 +1703,7 @@
         <v>23</v>
       </c>
       <c r="B19" s="3">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="20">
@@ -1760,28 +1730,28 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="B2" s="3">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="B3" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B4" s="3">
         <v>8</v>
@@ -1789,23 +1759,23 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>452</v>
+        <v>410</v>
       </c>
       <c r="B5" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>400</v>
+        <v>460</v>
       </c>
       <c r="B6" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>447</v>
+        <v>397</v>
       </c>
       <c r="B7" s="3">
         <v>1</v>
@@ -1824,42 +1794,42 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>482</v>
+        <v>472</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>483</v>
+        <v>473</v>
       </c>
       <c r="B2" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>484</v>
+        <v>474</v>
       </c>
       <c r="B3" s="3">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>485</v>
+        <v>374</v>
       </c>
       <c r="B4" s="3">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>380</v>
+        <v>475</v>
       </c>
       <c r="B5" s="3">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6">
@@ -1867,36 +1837,36 @@
         <v>377</v>
       </c>
       <c r="B6" s="3">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="B7" s="3">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>378</v>
+        <v>477</v>
       </c>
       <c r="B8" s="3">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>487</v>
+        <v>375</v>
       </c>
       <c r="B9" s="3">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="B10" s="3">
         <v>8</v>
@@ -1904,7 +1874,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>303</v>
+        <v>371</v>
       </c>
       <c r="B11" s="3">
         <v>8</v>
@@ -1912,7 +1882,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B12" s="3">
         <v>8</v>
@@ -1920,34 +1890,34 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>371</v>
+        <v>299</v>
       </c>
       <c r="B13" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="B14" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>372</v>
+        <v>478</v>
       </c>
       <c r="B15" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>488</v>
+        <v>369</v>
       </c>
       <c r="B16" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1972,13 +1942,13 @@
         <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>489</v>
+        <v>479</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>490</v>
+        <v>480</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>491</v>
+        <v>481</v>
       </c>
     </row>
     <row r="2">
@@ -1989,10 +1959,10 @@
         <v>29</v>
       </c>
       <c r="C2" s="3">
-        <v>13.3</v>
+        <v>11.8</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>492</v>
+        <v>482</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -2004,85 +1974,85 @@
         <v>72</v>
       </c>
       <c r="C3" s="3">
-        <v>36.4</v>
+        <v>36.7</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>492</v>
+        <v>482</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>493</v>
+        <v>483</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>8.5</v>
+        <v>8.3</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>492</v>
+        <v>482</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>494</v>
+        <v>484</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>492</v>
+        <v>482</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>495</v>
+        <v>485</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>33.8</v>
+        <v>31.5</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>492</v>
+        <v>482</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>496</v>
+        <v>486</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>15.7</v>
+        <v>16.3</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>492</v>
+        <v>482</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>497</v>
+        <v>487</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>23.6</v>
+        <v>18.7</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>492</v>
+        <v>482</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -2094,7 +2064,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="59" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="2" max="2" width="35" customWidth="1"/>
     <col min="3" max="3" width="43" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -2166,7 +2136,7 @@
         <v>41</v>
       </c>
       <c r="J2" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -2198,7 +2168,7 @@
         <v>41</v>
       </c>
       <c r="J3" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
@@ -2230,7 +2200,7 @@
         <v>41</v>
       </c>
       <c r="J4" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
@@ -2262,7 +2232,7 @@
         <v>52</v>
       </c>
       <c r="J5" s="3">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6">
@@ -2294,7 +2264,7 @@
         <v>52</v>
       </c>
       <c r="J6" s="3">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7">
@@ -2326,7 +2296,7 @@
         <v>59</v>
       </c>
       <c r="J7" s="3">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8">
@@ -2358,7 +2328,7 @@
         <v>65</v>
       </c>
       <c r="J8" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9">
@@ -2390,7 +2360,7 @@
         <v>52</v>
       </c>
       <c r="J9" s="3">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10">
@@ -2422,7 +2392,7 @@
         <v>72</v>
       </c>
       <c r="J10" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">
@@ -2454,7 +2424,7 @@
         <v>76</v>
       </c>
       <c r="J11" s="3">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12">
@@ -2486,7 +2456,7 @@
         <v>81</v>
       </c>
       <c r="J12" s="3">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13">
@@ -2518,7 +2488,7 @@
         <v>84</v>
       </c>
       <c r="J13" s="3">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="14">
@@ -2550,7 +2520,7 @@
         <v>88</v>
       </c>
       <c r="J14" s="3">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -2582,7 +2552,7 @@
         <v>92</v>
       </c>
       <c r="J15" s="3">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16">
@@ -2614,7 +2584,7 @@
         <v>96</v>
       </c>
       <c r="J16" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17">
@@ -2646,7 +2616,7 @@
         <v>102</v>
       </c>
       <c r="J17" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18">
@@ -2678,7 +2648,7 @@
         <v>106</v>
       </c>
       <c r="J18" s="3">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="19">
@@ -2710,7 +2680,7 @@
         <v>96</v>
       </c>
       <c r="J19" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20">
@@ -2742,7 +2712,7 @@
         <v>65</v>
       </c>
       <c r="J20" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -2774,7 +2744,7 @@
         <v>116</v>
       </c>
       <c r="J21" s="3">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="22">
@@ -2806,7 +2776,7 @@
         <v>92</v>
       </c>
       <c r="J22" s="3">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="23">
@@ -2838,7 +2808,7 @@
         <v>125</v>
       </c>
       <c r="J23" s="3">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="24">
@@ -2870,7 +2840,7 @@
         <v>128</v>
       </c>
       <c r="J24" s="3">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="25">
@@ -2902,7 +2872,7 @@
         <v>133</v>
       </c>
       <c r="J25" s="3">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="26">
@@ -2934,7 +2904,7 @@
         <v>136</v>
       </c>
       <c r="J26" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="27">
@@ -2966,7 +2936,7 @@
         <v>141</v>
       </c>
       <c r="J27" s="3">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="28">
@@ -2998,7 +2968,7 @@
         <v>52</v>
       </c>
       <c r="J28" s="3">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="29">
@@ -3030,7 +3000,7 @@
         <v>81</v>
       </c>
       <c r="J29" s="3">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="30">
@@ -3062,7 +3032,7 @@
         <v>157</v>
       </c>
       <c r="J30" s="3">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="31">
@@ -3092,7 +3062,7 @@
         <v>161</v>
       </c>
       <c r="J31" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -3122,7 +3092,7 @@
         <v>76</v>
       </c>
       <c r="J32" s="3">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="33">
@@ -3152,7 +3122,7 @@
         <v>116</v>
       </c>
       <c r="J33" s="3">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="34">
@@ -3163,7 +3133,7 @@
         <v>167</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>49</v>
@@ -3176,27 +3146,27 @@
         <v>23</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="J34" s="3">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>43</v>
@@ -3206,21 +3176,21 @@
         <v>23</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I35" s="3" t="s">
         <v>157</v>
       </c>
       <c r="J35" s="3">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>159</v>
@@ -3229,20 +3199,20 @@
         <v>49</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>41</v>
+        <v>96</v>
       </c>
       <c r="J36" s="3">
-        <v>6</v>
+        <v>22</v>
       </c>
     </row>
     <row r="37">
@@ -3250,10 +3220,10 @@
         <v>164</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>49</v>
@@ -3266,21 +3236,21 @@
         <v>23</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="J37" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>159</v>
@@ -3296,24 +3266,24 @@
         <v>23</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="I38" s="3" t="s">
         <v>88</v>
       </c>
       <c r="J38" s="3">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>150</v>
@@ -3326,27 +3296,27 @@
         <v>23</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="J39" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>43</v>
@@ -3356,13 +3326,13 @@
         <v>23</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="I40" s="3" t="s">
         <v>59</v>
       </c>
       <c r="J40" s="3">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="41">
@@ -3370,7 +3340,7 @@
         <v>164</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>159</v>
@@ -3386,43 +3356,43 @@
         <v>23</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>96</v>
+        <v>170</v>
       </c>
       <c r="J41" s="3">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>196</v>
+        <v>164</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>173</v>
+        <v>49</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F42" s="3"/>
       <c r="G42" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>199</v>
+        <v>96</v>
       </c>
       <c r="J42" s="3">
-        <v>42</v>
+        <v>22</v>
       </c>
     </row>
     <row r="43">
@@ -3433,7 +3403,7 @@
         <v>200</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>201</v>
+        <v>168</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>49</v>
@@ -3446,30 +3416,30 @@
         <v>23</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="I43" s="3" t="s">
         <v>161</v>
       </c>
       <c r="J43" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>47</v>
+        <v>202</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>203</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>201</v>
+        <v>159</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3" t="s">
@@ -3479,57 +3449,57 @@
         <v>204</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>41</v>
+        <v>182</v>
       </c>
       <c r="J44" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B45" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="B45" s="3" t="s">
-        <v>206</v>
-      </c>
       <c r="C45" s="3" t="s">
-        <v>159</v>
+        <v>180</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H45" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="I45" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>180</v>
-      </c>
       <c r="J45" s="3">
-        <v>0</v>
+        <v>42</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>47</v>
+        <v>164</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>208</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>178</v>
+        <v>56</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="3" t="s">
@@ -3539,24 +3509,24 @@
         <v>209</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>210</v>
+        <v>161</v>
       </c>
       <c r="J46" s="3">
-        <v>41</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>164</v>
+        <v>210</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>211</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>56</v>
+        <v>212</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>49</v>
+        <v>194</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>38</v>
@@ -3566,24 +3536,24 @@
         <v>23</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>161</v>
+        <v>214</v>
       </c>
       <c r="J47" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>47</v>
+        <v>215</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>49</v>
@@ -3596,43 +3566,43 @@
         <v>23</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="J48" s="3">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>215</v>
+        <v>47</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>217</v>
+        <v>173</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>192</v>
+        <v>174</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F49" s="3"/>
       <c r="G49" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>219</v>
+        <v>182</v>
       </c>
       <c r="J49" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3643,13 +3613,13 @@
         <v>221</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>201</v>
+        <v>159</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="3" t="s">
@@ -3659,57 +3629,57 @@
         <v>222</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="J50" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B51" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="B51" s="3" t="s">
+      <c r="C51" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="C51" s="3" t="s">
-        <v>159</v>
-      </c>
       <c r="D51" s="3" t="s">
-        <v>49</v>
+        <v>225</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F51" s="3"/>
       <c r="G51" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>188</v>
+        <v>227</v>
       </c>
       <c r="J51" s="3">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>47</v>
+        <v>164</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>227</v>
+        <v>168</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>228</v>
+        <v>49</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F52" s="3"/>
       <c r="G52" s="3" t="s">
@@ -3719,10 +3689,10 @@
         <v>229</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>230</v>
+        <v>170</v>
       </c>
       <c r="J52" s="3">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3730,10 +3700,10 @@
         <v>164</v>
       </c>
       <c r="B53" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="C53" s="3" t="s">
         <v>231</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>159</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>49</v>
@@ -3749,57 +3719,57 @@
         <v>232</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>199</v>
+        <v>96</v>
       </c>
       <c r="J53" s="3">
-        <v>42</v>
+        <v>22</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>164</v>
+        <v>233</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>49</v>
+        <v>194</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F54" s="3"/>
       <c r="G54" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>96</v>
+        <v>182</v>
       </c>
       <c r="J54" s="3">
-        <v>21</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>238</v>
+        <v>56</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>192</v>
+        <v>49</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3" t="s">
@@ -3809,21 +3779,21 @@
         <v>239</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>180</v>
+        <v>214</v>
       </c>
       <c r="J55" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="B56" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="B56" s="3" t="s">
-        <v>241</v>
-      </c>
       <c r="C56" s="3" t="s">
-        <v>56</v>
+        <v>159</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>49</v>
@@ -3836,21 +3806,21 @@
         <v>23</v>
       </c>
       <c r="H56" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="I56" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="I56" s="3" t="s">
-        <v>219</v>
-      </c>
       <c r="J56" s="3">
-        <v>5</v>
+        <v>67</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>164</v>
+        <v>243</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>243</v>
+        <v>184</v>
       </c>
       <c r="C57" s="3" t="s">
         <v>159</v>
@@ -3859,7 +3829,7 @@
         <v>49</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F57" s="3"/>
       <c r="G57" s="3" t="s">
@@ -3869,111 +3839,111 @@
         <v>244</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>245</v>
+        <v>214</v>
       </c>
       <c r="J57" s="3">
-        <v>66</v>
+        <v>6</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>246</v>
+        <v>164</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>182</v>
+        <v>245</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>159</v>
+        <v>193</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>49</v>
+        <v>194</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F58" s="3"/>
       <c r="G58" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>219</v>
+        <v>161</v>
       </c>
       <c r="J58" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>164</v>
+        <v>47</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>191</v>
+        <v>159</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>192</v>
+        <v>49</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F59" s="3"/>
       <c r="G59" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H59" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="I59" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>161</v>
-      </c>
       <c r="J59" s="3">
-        <v>1</v>
+        <v>43</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>47</v>
+        <v>250</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>159</v>
+        <v>252</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>49</v>
+        <v>150</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F60" s="3"/>
       <c r="G60" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>199</v>
+        <v>182</v>
       </c>
       <c r="J60" s="3">
-        <v>42</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="C61" s="3" t="s">
         <v>252</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="C61" s="3" t="s">
-        <v>254</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>150</v>
@@ -3986,30 +3956,30 @@
         <v>23</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>180</v>
+        <v>161</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>256</v>
+        <v>47</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>257</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>254</v>
+        <v>168</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>150</v>
+        <v>49</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F62" s="3"/>
       <c r="G62" s="3" t="s">
@@ -4019,10 +3989,10 @@
         <v>258</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>161</v>
+        <v>214</v>
       </c>
       <c r="J62" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="63">
@@ -4033,40 +4003,40 @@
         <v>260</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>159</v>
+        <v>261</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F63" s="3"/>
       <c r="G63" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>41</v>
+        <v>182</v>
       </c>
       <c r="J63" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>159</v>
+        <v>252</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>49</v>
+        <v>150</v>
       </c>
       <c r="E64" s="3" t="s">
         <v>38</v>
@@ -4076,13 +4046,13 @@
         <v>23</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>72</v>
+        <v>182</v>
       </c>
       <c r="J64" s="3">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4090,13 +4060,13 @@
         <v>47</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>201</v>
+        <v>267</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>49</v>
+        <v>150</v>
       </c>
       <c r="E65" s="3" t="s">
         <v>43</v>
@@ -4106,54 +4076,54 @@
         <v>23</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>219</v>
+        <v>269</v>
       </c>
       <c r="J65" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="C66" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="B66" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="C66" s="3" t="s">
-        <v>159</v>
-      </c>
       <c r="D66" s="3" t="s">
-        <v>49</v>
+        <v>150</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>38</v>
+        <v>272</v>
       </c>
       <c r="F66" s="3"/>
       <c r="G66" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>41</v>
+        <v>170</v>
       </c>
       <c r="J66" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>269</v>
+        <v>164</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>271</v>
+        <v>168</v>
       </c>
       <c r="D67" s="3" t="s">
         <v>49</v>
@@ -4166,27 +4136,27 @@
         <v>23</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>180</v>
+        <v>72</v>
       </c>
       <c r="J67" s="3">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>254</v>
+        <v>56</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>150</v>
+        <v>49</v>
       </c>
       <c r="E68" s="3" t="s">
         <v>38</v>
@@ -4196,21 +4166,21 @@
         <v>23</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>180</v>
+        <v>279</v>
       </c>
       <c r="J68" s="3">
-        <v>0</v>
+        <v>34</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>182</v>
+        <v>281</v>
       </c>
       <c r="C69" s="3" t="s">
         <v>159</v>
@@ -4226,21 +4196,21 @@
         <v>23</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>169</v>
+        <v>41</v>
       </c>
       <c r="J69" s="3">
-        <v>27</v>
+        <v>7</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="C70" s="3" t="s">
         <v>159</v>
@@ -4256,130 +4226,130 @@
         <v>23</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>41</v>
+        <v>170</v>
       </c>
       <c r="J70" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>282</v>
+        <v>255</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>159</v>
+        <v>252</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>49</v>
+        <v>150</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F71" s="3"/>
       <c r="G71" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="J71" s="3">
-        <v>90</v>
+        <v>60</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>159</v>
+        <v>291</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>49</v>
+        <v>150</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F72" s="3"/>
       <c r="G72" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>41</v>
+        <v>161</v>
       </c>
       <c r="J72" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>288</v>
+        <v>53</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>257</v>
+        <v>293</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>254</v>
+        <v>159</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>150</v>
+        <v>49</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F73" s="3"/>
       <c r="G73" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>290</v>
+        <v>249</v>
       </c>
       <c r="J73" s="3">
-        <v>59</v>
+        <v>43</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>291</v>
+        <v>164</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>293</v>
+        <v>168</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>150</v>
+        <v>49</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F74" s="3"/>
       <c r="G74" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>161</v>
+        <v>182</v>
       </c>
       <c r="J74" s="3">
         <v>1</v>
@@ -4387,13 +4357,13 @@
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>56</v>
+        <v>168</v>
       </c>
       <c r="D75" s="3" t="s">
         <v>49</v>
@@ -4401,94 +4371,94 @@
       <c r="E75" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F75" s="3"/>
+      <c r="F75" s="3" t="s">
+        <v>299</v>
+      </c>
       <c r="G75" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>298</v>
+        <v>81</v>
       </c>
       <c r="J75" s="3">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>164</v>
+        <v>53</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>201</v>
+        <v>159</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F76" s="3"/>
       <c r="G76" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>180</v>
+        <v>303</v>
       </c>
       <c r="J76" s="3">
-        <v>0</v>
+        <v>86</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>301</v>
+        <v>164</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>201</v>
+        <v>291</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>49</v>
+        <v>150</v>
       </c>
       <c r="E77" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F77" s="3" t="s">
-        <v>303</v>
-      </c>
+      <c r="F77" s="3"/>
       <c r="G77" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>81</v>
+        <v>190</v>
       </c>
       <c r="J77" s="3">
-        <v>35</v>
+        <v>5</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>47</v>
+        <v>306</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>173</v>
+        <v>49</v>
       </c>
       <c r="E78" s="3" t="s">
         <v>43</v>
@@ -4498,27 +4468,27 @@
         <v>23</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="J78" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>53</v>
+        <v>309</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>159</v>
+        <v>224</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>49</v>
+        <v>225</v>
       </c>
       <c r="E79" s="3" t="s">
         <v>43</v>
@@ -4528,27 +4498,27 @@
         <v>23</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>309</v>
+        <v>190</v>
       </c>
       <c r="J79" s="3">
-        <v>85</v>
+        <v>5</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>164</v>
+        <v>312</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>293</v>
+        <v>159</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>150</v>
+        <v>49</v>
       </c>
       <c r="E80" s="3" t="s">
         <v>38</v>
@@ -4558,27 +4528,27 @@
         <v>23</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>188</v>
+        <v>170</v>
       </c>
       <c r="J80" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>173</v>
+        <v>49</v>
       </c>
       <c r="E81" s="3" t="s">
         <v>38</v>
@@ -4588,24 +4558,24 @@
         <v>23</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>41</v>
+        <v>170</v>
       </c>
       <c r="J81" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>201</v>
+        <v>159</v>
       </c>
       <c r="D82" s="3" t="s">
         <v>49</v>
@@ -4618,24 +4588,24 @@
         <v>23</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>188</v>
+        <v>41</v>
       </c>
       <c r="J82" s="3">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>178</v>
+        <v>159</v>
       </c>
       <c r="D83" s="3" t="s">
         <v>49</v>
@@ -4648,27 +4618,27 @@
         <v>23</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>41</v>
+        <v>84</v>
       </c>
       <c r="J83" s="3">
-        <v>6</v>
+        <v>44</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>321</v>
+        <v>53</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>159</v>
+        <v>267</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>49</v>
+        <v>150</v>
       </c>
       <c r="E84" s="3" t="s">
         <v>43</v>
@@ -4678,24 +4648,24 @@
         <v>23</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>41</v>
+        <v>326</v>
       </c>
       <c r="J84" s="3">
-        <v>6</v>
+        <v>23</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>164</v>
+        <v>327</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>201</v>
+        <v>168</v>
       </c>
       <c r="D85" s="3" t="s">
         <v>49</v>
@@ -4708,21 +4678,21 @@
         <v>23</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>72</v>
+        <v>170</v>
       </c>
       <c r="J85" s="3">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>327</v>
+        <v>240</v>
       </c>
       <c r="C86" s="3" t="s">
         <v>159</v>
@@ -4731,91 +4701,91 @@
         <v>49</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F86" s="3"/>
       <c r="G86" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>84</v>
+        <v>242</v>
       </c>
       <c r="J86" s="3">
-        <v>43</v>
+        <v>67</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>53</v>
+        <v>332</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>329</v>
+        <v>179</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>150</v>
+        <v>49</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F87" s="3"/>
       <c r="G87" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>332</v>
+        <v>182</v>
       </c>
       <c r="J87" s="3">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>333</v>
+        <v>47</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>243</v>
+        <v>335</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>159</v>
+        <v>224</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>49</v>
+        <v>225</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F88" s="3"/>
       <c r="G88" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>245</v>
+        <v>128</v>
       </c>
       <c r="J88" s="3">
-        <v>66</v>
+        <v>50</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>177</v>
+        <v>338</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>336</v>
+        <v>168</v>
       </c>
       <c r="D89" s="3" t="s">
         <v>49</v>
@@ -4823,59 +4793,61 @@
       <c r="E89" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F89" s="3"/>
+      <c r="F89" s="3" t="s">
+        <v>339</v>
+      </c>
       <c r="G89" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="J89" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>47</v>
+        <v>341</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>227</v>
+        <v>159</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>228</v>
+        <v>49</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F90" s="3"/>
       <c r="G90" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>128</v>
+        <v>65</v>
       </c>
       <c r="J90" s="3">
-        <v>49</v>
+        <v>21</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>201</v>
+        <v>168</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>49</v>
@@ -4883,61 +4855,59 @@
       <c r="E91" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F91" s="3" t="s">
-        <v>342</v>
-      </c>
+      <c r="F91" s="3"/>
       <c r="G91" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>180</v>
+        <v>76</v>
       </c>
       <c r="J91" s="3">
-        <v>0</v>
+        <v>26</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>159</v>
+        <v>349</v>
       </c>
       <c r="D92" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>38</v>
+        <v>272</v>
       </c>
       <c r="F92" s="3"/>
       <c r="G92" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>65</v>
+        <v>182</v>
       </c>
       <c r="J92" s="3">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>201</v>
+        <v>333</v>
       </c>
       <c r="D93" s="3" t="s">
         <v>49</v>
@@ -4950,57 +4920,57 @@
         <v>23</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>76</v>
+        <v>170</v>
       </c>
       <c r="J93" s="3">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>352</v>
+        <v>168</v>
       </c>
       <c r="D94" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>353</v>
+        <v>38</v>
       </c>
       <c r="F94" s="3"/>
       <c r="G94" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="J94" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>201</v>
+        <v>359</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>49</v>
+        <v>150</v>
       </c>
       <c r="E95" s="3" t="s">
         <v>38</v>
@@ -5010,27 +4980,27 @@
         <v>23</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="J95" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>360</v>
+        <v>180</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>150</v>
+        <v>49</v>
       </c>
       <c r="E96" s="3" t="s">
         <v>38</v>
@@ -5040,77 +5010,17 @@
         <v>23</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>180</v>
+        <v>102</v>
       </c>
       <c r="J96" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="B97" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="C97" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="D97" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E97" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F97" s="3"/>
-      <c r="G97" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H97" s="3" t="s">
-        <v>364</v>
-      </c>
-      <c r="I97" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="J97" s="3">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="B98" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="C98" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="D98" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E98" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F98" s="3"/>
-      <c r="G98" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H98" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="I98" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="J98" s="3">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J98"/>
+  <autoFilter ref="A1:J96"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -5207,8 +5117,6 @@
     <hyperlink ref="H94" r:id="rId93"/>
     <hyperlink ref="H95" r:id="rId94"/>
     <hyperlink ref="H96" r:id="rId95"/>
-    <hyperlink ref="H97" r:id="rId96"/>
-    <hyperlink ref="H98" r:id="rId97"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5216,9 +5124,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="41" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="43" customWidth="1"/>
+    <col min="1" max="1" width="54" customWidth="1"/>
+    <col min="2" max="2" width="35" customWidth="1"/>
+    <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
@@ -5253,10 +5161,10 @@
         <v>164</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
@@ -5264,15 +5172,15 @@
         <v>23</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>205</v>
+        <v>164</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>159</v>
@@ -5283,18 +5191,18 @@
         <v>23</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>236</v>
+        <v>164</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>238</v>
+        <v>168</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -5302,18 +5210,18 @@
         <v>23</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>252</v>
+        <v>270</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>253</v>
+        <v>271</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>254</v>
+        <v>267</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -5321,18 +5229,18 @@
         <v>23</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>255</v>
+        <v>273</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>269</v>
+        <v>283</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>270</v>
+        <v>284</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>271</v>
+        <v>159</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -5340,18 +5248,18 @@
         <v>23</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>272</v>
+        <v>285</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>273</v>
+        <v>312</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>274</v>
+        <v>313</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>254</v>
+        <v>159</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -5359,18 +5267,18 @@
         <v>23</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>275</v>
+        <v>314</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>164</v>
+        <v>315</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>299</v>
+        <v>316</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>201</v>
+        <v>180</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -5378,18 +5286,18 @@
         <v>23</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>300</v>
+        <v>317</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>47</v>
+        <v>327</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>305</v>
+        <v>328</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -5397,18 +5305,18 @@
         <v>23</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>306</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>335</v>
+        <v>351</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>177</v>
+        <v>352</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -5416,106 +5324,11 @@
         <v>23</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>352</v>
-      </c>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="s">
-        <v>355</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>356</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>359</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>366</v>
+        <v>353</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G15"/>
+  <autoFilter ref="A1:G10"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -5526,11 +5339,6 @@
     <hyperlink ref="G8" r:id="rId7"/>
     <hyperlink ref="G9" r:id="rId8"/>
     <hyperlink ref="G10" r:id="rId9"/>
-    <hyperlink ref="G11" r:id="rId10"/>
-    <hyperlink ref="G12" r:id="rId11"/>
-    <hyperlink ref="G13" r:id="rId12"/>
-    <hyperlink ref="G14" r:id="rId13"/>
-    <hyperlink ref="G15" r:id="rId14"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5544,15 +5352,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="B2" s="3">
         <v>23</v>
@@ -5560,7 +5368,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="B3" s="3">
         <v>20</v>
@@ -5568,7 +5376,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="B4" s="3">
         <v>20</v>
@@ -5576,7 +5384,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="B5" s="3">
         <v>19</v>
@@ -5584,7 +5392,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="B6" s="3">
         <v>14</v>
@@ -5600,7 +5408,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="B8" s="3">
         <v>13</v>
@@ -5608,7 +5416,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="B9" s="3">
         <v>12</v>
@@ -5616,7 +5424,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="B10" s="3">
         <v>11</v>
@@ -5624,7 +5432,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="B11" s="3">
         <v>10</v>
@@ -5632,7 +5440,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="B12" s="3">
         <v>10</v>
@@ -5640,7 +5448,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="B13" s="3">
         <v>9</v>
@@ -5648,7 +5456,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="B14" s="3">
         <v>8</v>
@@ -5656,7 +5464,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="B15" s="3">
         <v>6</v>
@@ -5664,7 +5472,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="B16" s="3">
         <v>6</v>
@@ -5686,7 +5494,7 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
     </row>
     <row r="2">
@@ -5731,15 +5539,15 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>182</v>
+        <v>48</v>
       </c>
       <c r="B7" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>48</v>
+        <v>130</v>
       </c>
       <c r="B8" s="3">
         <v>2</v>
@@ -5747,7 +5555,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>130</v>
+        <v>179</v>
       </c>
       <c r="B9" s="3">
         <v>2</v>
@@ -5755,7 +5563,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="B10" s="3">
         <v>2</v>
@@ -5763,7 +5571,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -5771,7 +5579,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -5779,15 +5587,15 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>260</v>
+        <v>55</v>
       </c>
       <c r="B13" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>55</v>
+        <v>138</v>
       </c>
       <c r="B14" s="3">
         <v>1</v>
@@ -5795,7 +5603,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="B15" s="3">
         <v>1</v>
@@ -5803,7 +5611,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="B16" s="3">
         <v>1</v>
@@ -5824,16 +5632,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
     </row>
     <row r="2">
@@ -5939,13 +5747,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>182</v>
+        <v>55</v>
       </c>
       <c r="C9" s="3">
-        <v>3.6</v>
+        <v>3.0</v>
       </c>
       <c r="D9" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -5953,10 +5761,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>55</v>
+        <v>138</v>
       </c>
       <c r="C10" s="3">
-        <v>3.0</v>
+        <v>2.6</v>
       </c>
       <c r="D10" s="3">
         <v>1</v>
@@ -5967,13 +5775,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>260</v>
+        <v>143</v>
       </c>
       <c r="C11" s="3">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="D11" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -5981,13 +5789,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>138</v>
+        <v>179</v>
       </c>
       <c r="C12" s="3">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="D12" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -5995,13 +5803,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>143</v>
+        <v>184</v>
       </c>
       <c r="C13" s="3">
         <v>2.4</v>
       </c>
       <c r="D13" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -6009,7 +5817,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>177</v>
+        <v>240</v>
       </c>
       <c r="C14" s="3">
         <v>2.4</v>
@@ -6023,7 +5831,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="C15" s="3">
         <v>2.4</v>
@@ -6037,13 +5845,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>257</v>
+        <v>148</v>
       </c>
       <c r="C16" s="3">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="D16" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -6063,18 +5871,18 @@
         <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>353</v>
+        <v>272</v>
       </c>
       <c r="B2" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>12</v>
@@ -6085,10 +5893,10 @@
         <v>38</v>
       </c>
       <c r="B3" s="3">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
     </row>
     <row r="4">
@@ -6096,10 +5904,10 @@
         <v>43</v>
       </c>
       <c r="B4" s="3">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
     </row>
   </sheetData>
@@ -6118,7 +5926,7 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="2">
@@ -6126,7 +5934,7 @@
         <v>49</v>
       </c>
       <c r="B2" s="3">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3">
@@ -6134,12 +5942,12 @@
         <v>150</v>
       </c>
       <c r="B3" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="B4" s="3">
         <v>4</v>
@@ -6147,15 +5955,15 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>192</v>
+        <v>37</v>
       </c>
       <c r="B5" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>37</v>
+        <v>225</v>
       </c>
       <c r="B6" s="3">
         <v>3</v>
@@ -6163,7 +5971,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>228</v>
+        <v>174</v>
       </c>
       <c r="B7" s="3">
         <v>2</v>
@@ -6179,7 +5987,7 @@
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
     <col min="3" max="3" width="32" customWidth="1"/>
-    <col min="4" max="4" width="42" customWidth="1"/>
+    <col min="4" max="4" width="43" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
     <col min="7" max="7" width="60" customWidth="1"/>
@@ -6190,10 +5998,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>26</v>
@@ -6205,10 +6013,10 @@
         <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>21</v>
@@ -6225,31 +6033,31 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>391</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>392</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>393</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>394</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
     </row>
     <row r="3">
@@ -6257,31 +6065,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>159</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
     </row>
     <row r="4">
@@ -6289,28 +6097,28 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>404</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>405</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>406</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>407</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>88</v>
@@ -6321,28 +6129,28 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>159</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="F5" s="3">
         <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>88</v>
@@ -6353,31 +6161,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>413</v>
+        <v>347</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>221</v>
+        <v>348</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>414</v>
+        <v>349</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>394</v>
+        <v>410</v>
       </c>
       <c r="F6" s="3">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>416</v>
+        <v>350</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>219</v>
+        <v>182</v>
       </c>
     </row>
     <row r="7">
@@ -6385,31 +6193,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>418</v>
+        <v>216</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>159</v>
+        <v>413</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="F7" s="3">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>421</v>
+        <v>214</v>
       </c>
     </row>
     <row r="8">
@@ -6417,31 +6225,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>178</v>
+        <v>159</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>407</v>
+        <v>391</v>
       </c>
       <c r="F8" s="3">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>219</v>
+        <v>420</v>
       </c>
     </row>
     <row r="9">
@@ -6449,31 +6257,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>238</v>
+        <v>180</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="F9" s="3">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>88</v>
+        <v>214</v>
       </c>
     </row>
     <row r="10">
@@ -6481,31 +6289,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>432</v>
+        <v>235</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>394</v>
+        <v>404</v>
       </c>
       <c r="F10" s="3">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>435</v>
+        <v>88</v>
       </c>
     </row>
     <row r="11">
@@ -6513,31 +6321,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>159</v>
+        <v>431</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>438</v>
+        <v>391</v>
       </c>
       <c r="F11" s="3">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>439</v>
+        <v>432</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>440</v>
+        <v>433</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>81</v>
+        <v>434</v>
       </c>
     </row>
     <row r="12">
@@ -6545,31 +6353,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>423</v>
+        <v>436</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>178</v>
+        <v>159</v>
       </c>
       <c r="E12" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="F12" s="3">
+        <v>61</v>
+      </c>
+      <c r="G12" s="3" t="s">
         <v>438</v>
       </c>
-      <c r="F12" s="3">
-        <v>47</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>442</v>
-      </c>
       <c r="H12" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>444</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13">
@@ -6577,31 +6385,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>445</v>
+        <v>332</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>446</v>
+        <v>179</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>254</v>
+        <v>333</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>447</v>
+        <v>391</v>
       </c>
       <c r="F13" s="3">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>448</v>
+        <v>440</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>449</v>
+        <v>334</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>59</v>
+        <v>182</v>
       </c>
     </row>
     <row r="14">
@@ -6609,31 +6417,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>450</v>
+        <v>361</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>451</v>
+        <v>441</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>330</v>
+        <v>168</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>452</v>
+        <v>391</v>
       </c>
       <c r="F14" s="3">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>453</v>
+        <v>442</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>454</v>
+        <v>443</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>41</v>
+        <v>182</v>
       </c>
     </row>
     <row r="15">
@@ -6641,31 +6449,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>455</v>
+        <v>444</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>456</v>
+        <v>422</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>330</v>
+        <v>180</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>407</v>
+        <v>437</v>
       </c>
       <c r="F15" s="3">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>457</v>
+        <v>445</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>458</v>
+        <v>446</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>88</v>
+        <v>447</v>
       </c>
     </row>
     <row r="16">
@@ -6673,31 +6481,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>459</v>
+        <v>448</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>460</v>
+        <v>449</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>159</v>
+        <v>252</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>394</v>
+        <v>410</v>
       </c>
       <c r="F16" s="3">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>461</v>
+        <v>450</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>462</v>
+        <v>451</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>463</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17">
@@ -6705,31 +6513,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>459</v>
+        <v>361</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>260</v>
+        <v>452</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>159</v>
+        <v>173</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="F17" s="3">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>464</v>
+        <v>453</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>465</v>
+        <v>454</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>88</v>
+        <v>182</v>
       </c>
     </row>
     <row r="18">
@@ -6737,31 +6545,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>466</v>
+        <v>455</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>305</v>
+        <v>456</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>438</v>
+        <v>404</v>
       </c>
       <c r="F18" s="3">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>468</v>
+        <v>458</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>469</v>
+        <v>182</v>
       </c>
     </row>
     <row r="19">
@@ -6769,31 +6577,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>470</v>
+        <v>459</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>296</v>
+        <v>266</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>56</v>
+        <v>267</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>394</v>
+        <v>460</v>
       </c>
       <c r="F19" s="3">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>471</v>
+        <v>461</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>472</v>
+        <v>462</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>298</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20">
@@ -6801,31 +6609,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>473</v>
+        <v>464</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>254</v>
+        <v>267</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>394</v>
+        <v>404</v>
       </c>
       <c r="F20" s="3">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>474</v>
+        <v>465</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>475</v>
+        <v>466</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>476</v>
+        <v>88</v>
       </c>
     </row>
     <row r="21">
@@ -6833,31 +6641,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>477</v>
+        <v>467</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>478</v>
+        <v>468</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>159</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>438</v>
+        <v>391</v>
       </c>
       <c r="F21" s="3">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>480</v>
+        <v>470</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>481</v>
+        <v>471</v>
       </c>
     </row>
   </sheetData>

--- a/reports/devops-jobs-israel-2026-W41.xlsx
+++ b/reports/devops-jobs-israel-2026-W41.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="488">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="496" uniqueCount="496">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-06T13:12:25</t>
+    <t xml:space="preserve">2026-10-07T13:10:32</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Junior %</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1%</t>
+    <t xml:space="preserve">2.0%</t>
   </si>
   <si>
     <t xml:space="preserve">Salary disclosure rate %</t>
@@ -384,21 +384,6 @@
     <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7962665</t>
   </si>
   <si>
-    <t xml:space="preserve">Senior Data Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CloudFormation, Security, ECS/Fargate, Databricks, Airflow, Spark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7556162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-01</t>
-  </si>
-  <si>
     <t xml:space="preserve">AWS, GCP, Docker, Linux, Python, Networking, Observability</t>
   </si>
   <si>
@@ -432,6 +417,24 @@
     <t xml:space="preserve">2026-09-18</t>
   </si>
   <si>
+    <t xml:space="preserve">Senior AI Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Riskified</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lisbon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel (other)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.riskified.com/careers/job-description/?gh_jid=8873995002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-07</t>
+  </si>
+  <si>
     <t xml:space="preserve">Senior DevEx/DevOps Engineer</t>
   </si>
   <si>
@@ -471,9 +474,6 @@
     <t xml:space="preserve">United States</t>
   </si>
   <si>
-    <t xml:space="preserve">Israel (other)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, CI/CD, Helm, Security</t>
   </si>
   <si>
@@ -522,108 +522,120 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-echo-4459855925</t>
   </si>
   <si>
-    <t xml:space="preserve">EX.CO</t>
+    <t xml:space="preserve">Senior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eitan Medical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-eitan-medical-4461889332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Platform Engineer- CTI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dream</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-platform-engineer-cti-at-dream-4465727084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Logica-IT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-logica-it-4473616803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer - Data Platform (Cortex)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palo Alto Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-data-platform-cortex-at-palo-alto-networks-4455871961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Principal DevOps Engineer (Cortex Cloud)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-principal-devops-engineer-cortex-cloud-at-palo-alto-networks-4443693726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps- 243492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yehud Monosson, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-243492-at-experis-israel-4472685735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Checkmarx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-checkmarx-4439196775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr. DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harmonic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-devops-engineer-at-harmonic-4360460066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gini-Apps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gini-apps-4476189127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connecteam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4428832411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buildots</t>
   </si>
   <si>
     <t xml:space="preserve">Tel Aviv District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-ex-co-4474043806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eitan Medical</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-eitan-medical-4461889332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Platform Engineer- CTI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dream</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-platform-engineer-cti-at-dream-4465727084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Logica-IT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-logica-it-4473616803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Principal DevOps Engineer (Cortex Cloud)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palo Alto Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-principal-devops-engineer-cortex-cloud-at-palo-alto-networks-4443693726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps- 243492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yehud Monosson, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-243492-at-experis-israel-4472685735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sr. DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harmonic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-devops-engineer-at-harmonic-4360460066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gini-Apps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gini-apps-4476189127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connecteam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4428832411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Buildots</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-buildots-4473477683</t>
   </si>
   <si>
@@ -642,615 +654,642 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-akeyless-security-4457183616</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-25</t>
-  </si>
-  <si>
     <t xml:space="preserve">Blink</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-blink-4473214725</t>
   </si>
   <si>
-    <t xml:space="preserve">DevOps Automation &amp; Infrastructure as Code Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E2E Solutions IL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-automation-infrastructure-as-code-specialist-at-e2e-solutions-il-4473724881</t>
+    <t xml:space="preserve">Fetcherr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fetcherr-4429844723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cellebrite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-cellebrite-4469980397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer - Base44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-base44-at-base44-4474179911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personetics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-personetics-4428829912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps / Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">recruitricks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-platform-engineer-at-recruitricks-4475527624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moon Active</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-moon-active-4447023421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Polytex Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-polytex-technologies-4473474269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-gong-4457888927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Developer (37703)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-developer-37703-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4475562544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extreme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-devops-engineer-at-extreme-4475385097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4475164979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-4474645372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gloat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gloat-4474071911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps - AI Factory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kaltura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-ai-factory-at-kaltura-4475505499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure and Automation Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dialog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-and-automation-engineer-at-dialog-4473641075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jobgether</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-jobgether-4472898137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior DevOps Engineer — AI-Native</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ArtAc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-devops-engineer-%E2%80%94-ai-native-at-artac-4476141177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRE / DevOps Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">april</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-devops-lead-at-april-4416179005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantum Machines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-quantum-machines-4474990509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Data Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">evoke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-data-infrastructure-engineer-at-evoke-4462157157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staff Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grubhub</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/staff-site-reliability-engineer-at-grubhub-4473025762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineering - Storage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineering-storage-at-nvidia-4457190574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-nvidia-4457410161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Platform &amp; SRE Group Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-sre-group-leader-at-extreme-4450267100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Software Engineer, DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aiven</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-software-engineer-devops-at-aiven-4426867332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SciPlay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-sciplay-4391151881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medulla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-medulla-4475546635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure Engineer (Kubernetes &amp; Node.js)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oriient</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-kubernetes-node-js-at-oriient-4461069125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viz.ai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-viz-ai-4437383686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineer III, Platform Engineering and Infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-iii-platform-engineering-and-infrastructure-at-google-4465561954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platform Engineering Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corsa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineering-team-lead-at-corsa-4476174341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ThetaRay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-thetaray-4472910650</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Principal Devops &amp; Infra Tech Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sunbit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-devops-infra-tech-lead-at-sunbit-4474134295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Millennium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-millennium-4457617255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI &amp; Software Infra Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BioCatch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-software-infra-engineer-at-biocatch-4447894244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alice (Formerly ActiveFence)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-alice-formerly-activefence-4472729462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineer – DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential Careers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-%E2%80%93-devops-at-confidential-careers-4475416238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Developer (DevOps and Infrastructure)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rapyd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-developer-devops-and-infrastructure-at-rapyd-4428485007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DoiT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-doit-4463987032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TeraSky</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-terasky-4455198528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Infrastructure &amp; Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-cloud-engineer-at-moon-active-4447031167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-system-engineer-at-logica-it-4473666027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Cloud Network &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Applied Materials - Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloud-network-devops-engineer-at-applied-materials-israel-4474407748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer (FinOps oriented)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CloudTeam.ai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FinOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-finops-oriented-at-cloudteam-ai-4473603103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DriveNets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-devops-engineer-at-drivenets-4465793281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cato Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-system-engineer-at-cato-networks-4463471007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior System &amp; Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Final</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat HaSharon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-infrastructure-engineer-at-final-4475581791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Infrastructure Engineer - Proxy Network</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nimble</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-proxy-network-at-nimble-4475424343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wayve</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-wayve-4474417523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-elbit-systems-israel-4474036853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-system-engineer-at-comda-4473615194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQLink Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashdod, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-sqlink-group-4473649114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Talent Integration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-talent-integration-4466204750</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Development Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clarivate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/development-operations-engineer-at-clarivate-4467992253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps &amp; Cloud Infrastructure Intern</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-infrastructure-intern-at-f5-4464650168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Student DevOps Engineer- CxP Commercial Foundation Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Terraform/IaC, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-devops-engineer-cxp-commercial-foundation-services-at-sap-4436819328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
   </si>
   <si>
     <t xml:space="preserve">2026-09-30</t>
   </si>
   <si>
-    <t xml:space="preserve">Senior DevOps Engineer, AIOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-aiops-at-nvidia-4471970512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fetcherr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fetcherr-4429844723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer - Base44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Base44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-base44-at-base44-4474179911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cellebrite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-cellebrite-4469980397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GNESS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gness-4474945658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Personetics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-personetics-4428829912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps / Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">recruitricks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-platform-engineer-at-recruitricks-4475527624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRE-DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Apple</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-devops-engineer-at-apple-4471599502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moon Active</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-moon-active-4447023421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Principal DevOps Engineer - AI Platforms</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-devops-engineer-ai-platforms-at-palo-alto-networks-4471749164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Polytex Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-polytex-technologies-4473474269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-gong-4457888927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Developer (37703)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-developer-37703-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4475562544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extreme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-devops-engineer-at-extreme-4475385097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VYBS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-vybs-4472171413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps - AI Factory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kaltura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-ai-factory-at-kaltura-4475505499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure and Automation Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dialog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-and-automation-engineer-at-dialog-4473641075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jobgether</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-jobgether-4472898137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior DevOps Engineer — AI-Native</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ArtAc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-devops-engineer-%E2%80%94-ai-native-at-artac-4476141177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4470850779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Data Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">evoke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-data-infrastructure-engineer-at-evoke-4462157157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Staff Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grubhub</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/staff-site-reliability-engineer-at-grubhub-4473025762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sr. SRE AI Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Navan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-sre-ai-engineer-at-navan-4437742346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Platform &amp; SRE Group Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-sre-group-leader-at-extreme-4450267100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Software Engineer, DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aiven</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-software-engineer-devops-at-aiven-4426867332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SciPlay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-sciplay-4391151881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medulla</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-medulla-4475546635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure Engineer (Kubernetes &amp; Node.js)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oriient</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-kubernetes-node-js-at-oriient-4461069125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Viz.ai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-viz-ai-4437383686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ThetaRay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-thetaray-4472910650</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Principal Devops &amp; Infra Tech Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sunbit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-devops-infra-tech-lead-at-sunbit-4474134295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Platform &amp; DevOps Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pango</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-devops-team-lead-at-pango-4461809622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud DevOps Technical Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OnTarget Communications</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-devops-technical-manager-at-ontarget-communications-4475801640</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alice (Formerly ActiveFence)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-alice-formerly-activefence-4472729462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior AI Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Guesty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-ai-platform-engineer-at-guesty-4473205757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Developer (DevOps and Infrastructure)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rapyd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-developer-devops-and-infrastructure-at-rapyd-4428485007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DoiT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-doit-4463987032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Backend &amp; Infrastructure Engineer | Supabase / Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MISTERBIT Technological Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/backend-infrastructure-engineer-supabase-cloud-at-misterbit-technological-solutions-4476190575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Infrastructure &amp; Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-cloud-engineer-at-moon-active-4447031167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-system-engineer-at-logica-it-4473666027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TeraSky</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-terasky-4455198528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (FinOps oriented)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CloudTeam.ai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FinOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-finops-oriented-at-cloudteam-ai-4473603103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DriveNets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-devops-engineer-at-drivenets-4465793281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cato Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-system-engineer-at-cato-networks-4463471007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior System &amp; Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Final</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat HaSharon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-infrastructure-engineer-at-final-4475581791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-elbit-systems-israel-4474036853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-system-engineer-at-comda-4473615194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQLink Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ashdod, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-sqlink-group-4473649114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Talent Integration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-talent-integration-4466204750</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strength Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.4%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.5%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Development Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clarivate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/development-operations-engineer-at-clarivate-4467992253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps &amp; Cloud Infrastructure Intern</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-infrastructure-intern-at-f5-4464650168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Student DevOps Engineer- CxP Commercial Foundation Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Terraform/IaC, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-devops-engineer-cxp-commercial-foundation-services-at-sap-4436819328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
-  </si>
-  <si>
     <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
   </si>
   <si>
@@ -1260,9 +1299,6 @@
     <t xml:space="preserve">HPC Operations Engineer</t>
   </si>
   <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Terraform/IaC, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
   </si>
   <si>
@@ -1344,13 +1380,28 @@
     <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Terraform/IaC, Networking, Automation</t>
   </si>
   <si>
-    <t xml:space="preserve">Stealth Startup</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Terraform/IaC, Networking, Virtualization, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-stealth-startup-4473602938</t>
+    <t xml:space="preserve">System Administrator #1350</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Docker, Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%231350-at-rad-4473722167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONTROP Precision Technologies Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Networking, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-controp-precision-technologies-ltd-4460943847</t>
   </si>
   <si>
     <t xml:space="preserve">Technical Support Specialist</t>
@@ -1408,33 +1459,6 @@
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-monitoring-team-at-jobgether-4471710321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineering INTERN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Cloud (any), CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-intern-at-microsoft-4451071541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raft Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-13</t>
   </si>
   <si>
     <t xml:space="preserve">Roles requiring it</t>
@@ -1607,7 +1631,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>95</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7">
@@ -1615,7 +1639,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8">
@@ -1631,7 +1655,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>878</v>
+        <v>869</v>
       </c>
     </row>
     <row r="10">
@@ -1703,7 +1727,7 @@
         <v>23</v>
       </c>
       <c r="B19" s="3">
-        <v>66</v>
+        <v>70</v>
       </c>
     </row>
     <row r="20">
@@ -1730,20 +1754,20 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>391</v>
+        <v>402</v>
       </c>
       <c r="B2" s="3">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>404</v>
+        <v>413</v>
       </c>
       <c r="B3" s="3">
         <v>9</v>
@@ -1751,15 +1775,15 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="B4" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>410</v>
+        <v>423</v>
       </c>
       <c r="B5" s="3">
         <v>2</v>
@@ -1767,7 +1791,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>460</v>
+        <v>477</v>
       </c>
       <c r="B6" s="3">
         <v>2</v>
@@ -1775,7 +1799,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="B7" s="3">
         <v>1</v>
@@ -1794,71 +1818,71 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>364</v>
+        <v>375</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>472</v>
+        <v>480</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>473</v>
+        <v>481</v>
       </c>
       <c r="B2" s="3">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>474</v>
+        <v>482</v>
       </c>
       <c r="B3" s="3">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>374</v>
+        <v>384</v>
       </c>
       <c r="B4" s="3">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>475</v>
+        <v>388</v>
       </c>
       <c r="B5" s="3">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>377</v>
+        <v>483</v>
       </c>
       <c r="B6" s="3">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>476</v>
+        <v>484</v>
       </c>
       <c r="B7" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>477</v>
+        <v>386</v>
       </c>
       <c r="B8" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>375</v>
+        <v>485</v>
       </c>
       <c r="B9" s="3">
         <v>14</v>
@@ -1866,39 +1890,39 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="B10" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>371</v>
+        <v>381</v>
       </c>
       <c r="B11" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>370</v>
+        <v>383</v>
       </c>
       <c r="B12" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B13" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="B14" s="3">
         <v>8</v>
@@ -1906,7 +1930,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>478</v>
+        <v>380</v>
       </c>
       <c r="B15" s="3">
         <v>6</v>
@@ -1914,10 +1938,10 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>369</v>
+        <v>486</v>
       </c>
       <c r="B16" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -1942,13 +1966,13 @@
         <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>479</v>
+        <v>487</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
     </row>
     <row r="2">
@@ -1959,10 +1983,10 @@
         <v>29</v>
       </c>
       <c r="C2" s="3">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>482</v>
+        <v>490</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -1971,88 +1995,88 @@
         <v>23</v>
       </c>
       <c r="B3" s="3">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C3" s="3">
-        <v>36.7</v>
+        <v>35.6</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>482</v>
+        <v>490</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>483</v>
+        <v>491</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>8.3</v>
+        <v>8.5</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>482</v>
+        <v>490</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>484</v>
+        <v>492</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>482</v>
+        <v>490</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>31.5</v>
+        <v>46.9</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>482</v>
+        <v>490</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>486</v>
+        <v>494</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>16.3</v>
+        <v>17.3</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>482</v>
+        <v>490</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>487</v>
+        <v>495</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>18.7</v>
+        <v>21.0</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>482</v>
+        <v>490</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -2063,8 +2087,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="59" customWidth="1"/>
-    <col min="2" max="2" width="35" customWidth="1"/>
+    <col min="1" max="1" width="60" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="43" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -2136,7 +2160,7 @@
         <v>41</v>
       </c>
       <c r="J2" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
@@ -2168,7 +2192,7 @@
         <v>41</v>
       </c>
       <c r="J3" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
@@ -2200,7 +2224,7 @@
         <v>41</v>
       </c>
       <c r="J4" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
@@ -2232,7 +2256,7 @@
         <v>52</v>
       </c>
       <c r="J5" s="3">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6">
@@ -2264,7 +2288,7 @@
         <v>52</v>
       </c>
       <c r="J6" s="3">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7">
@@ -2296,7 +2320,7 @@
         <v>59</v>
       </c>
       <c r="J7" s="3">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8">
@@ -2328,7 +2352,7 @@
         <v>65</v>
       </c>
       <c r="J8" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9">
@@ -2360,7 +2384,7 @@
         <v>52</v>
       </c>
       <c r="J9" s="3">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10">
@@ -2392,7 +2416,7 @@
         <v>72</v>
       </c>
       <c r="J10" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11">
@@ -2424,7 +2448,7 @@
         <v>76</v>
       </c>
       <c r="J11" s="3">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12">
@@ -2456,7 +2480,7 @@
         <v>81</v>
       </c>
       <c r="J12" s="3">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13">
@@ -2488,7 +2512,7 @@
         <v>84</v>
       </c>
       <c r="J13" s="3">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="14">
@@ -2520,7 +2544,7 @@
         <v>88</v>
       </c>
       <c r="J14" s="3">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15">
@@ -2552,7 +2576,7 @@
         <v>92</v>
       </c>
       <c r="J15" s="3">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="16">
@@ -2584,7 +2608,7 @@
         <v>96</v>
       </c>
       <c r="J16" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17">
@@ -2616,7 +2640,7 @@
         <v>102</v>
       </c>
       <c r="J17" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18">
@@ -2648,7 +2672,7 @@
         <v>106</v>
       </c>
       <c r="J18" s="3">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="19">
@@ -2680,7 +2704,7 @@
         <v>96</v>
       </c>
       <c r="J19" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20">
@@ -2712,7 +2736,7 @@
         <v>65</v>
       </c>
       <c r="J20" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -2744,7 +2768,7 @@
         <v>116</v>
       </c>
       <c r="J21" s="3">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="22">
@@ -2776,18 +2800,18 @@
         <v>92</v>
       </c>
       <c r="J22" s="3">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>121</v>
+        <v>47</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>118</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>49</v>
@@ -2796,27 +2820,27 @@
         <v>43</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="J23" s="3">
-        <v>35</v>
+        <v>51</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>47</v>
+        <v>124</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>49</v>
@@ -2825,7 +2849,7 @@
         <v>49</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>126</v>
@@ -2840,7 +2864,7 @@
         <v>128</v>
       </c>
       <c r="J24" s="3">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25">
@@ -2848,7 +2872,7 @@
         <v>129</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>49</v>
@@ -2857,62 +2881,60 @@
         <v>49</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>131</v>
+        <v>67</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="J25" s="3">
-        <v>46</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>49</v>
-      </c>
       <c r="D26" s="3" t="s">
-        <v>49</v>
+        <v>135</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F26" s="3" t="s">
-        <v>67</v>
-      </c>
+      <c r="F26" s="3"/>
       <c r="G26" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="J26" s="3">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>99</v>
@@ -2924,30 +2946,30 @@
         <v>43</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="J27" s="3">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>49</v>
@@ -2956,33 +2978,33 @@
         <v>43</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I28" s="3" t="s">
         <v>52</v>
       </c>
       <c r="J28" s="3">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>43</v>
@@ -3000,7 +3022,7 @@
         <v>81</v>
       </c>
       <c r="J29" s="3">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="30">
@@ -3032,7 +3054,7 @@
         <v>157</v>
       </c>
       <c r="J30" s="3">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="31">
@@ -3062,7 +3084,7 @@
         <v>161</v>
       </c>
       <c r="J31" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
@@ -3092,7 +3114,7 @@
         <v>76</v>
       </c>
       <c r="J32" s="3">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="33">
@@ -3122,51 +3144,51 @@
         <v>116</v>
       </c>
       <c r="J33" s="3">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>49</v>
+        <v>170</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
       <c r="J34" s="3">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>173</v>
+        <v>159</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>174</v>
+        <v>49</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>43</v>
@@ -3176,60 +3198,60 @@
         <v>23</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>157</v>
+        <v>96</v>
       </c>
       <c r="J35" s="3">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="C36" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="B36" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>159</v>
-      </c>
       <c r="D36" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H36" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="I36" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="I36" s="3" t="s">
-        <v>96</v>
-      </c>
       <c r="J36" s="3">
-        <v>22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>164</v>
+        <v>179</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>180</v>
+        <v>159</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F37" s="3"/>
       <c r="G37" s="3" t="s">
@@ -3242,7 +3264,7 @@
         <v>182</v>
       </c>
       <c r="J37" s="3">
-        <v>1</v>
+        <v>43</v>
       </c>
     </row>
     <row r="38">
@@ -3250,7 +3272,7 @@
         <v>183</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>159</v>
@@ -3266,27 +3288,27 @@
         <v>23</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I38" s="3" t="s">
         <v>88</v>
       </c>
       <c r="J38" s="3">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="B39" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="C39" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="C39" s="3" t="s">
-        <v>188</v>
-      </c>
       <c r="D39" s="3" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>43</v>
@@ -3296,60 +3318,60 @@
         <v>23</v>
       </c>
       <c r="H39" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="I39" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="I39" s="3" t="s">
-        <v>190</v>
-      </c>
       <c r="J39" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>191</v>
+        <v>164</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>193</v>
+        <v>176</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>194</v>
+        <v>49</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F40" s="3"/>
       <c r="G40" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>59</v>
+        <v>192</v>
       </c>
       <c r="J40" s="3">
-        <v>41</v>
+        <v>85</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>164</v>
+        <v>193</v>
       </c>
       <c r="B41" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="D41" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="C41" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>49</v>
-      </c>
       <c r="E41" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
@@ -3359,10 +3381,10 @@
         <v>197</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>170</v>
+        <v>59</v>
       </c>
       <c r="J41" s="3">
-        <v>0</v>
+        <v>42</v>
       </c>
     </row>
     <row r="42">
@@ -3389,10 +3411,10 @@
         <v>199</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>96</v>
+        <v>200</v>
       </c>
       <c r="J42" s="3">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -3400,10 +3422,10 @@
         <v>164</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>49</v>
@@ -3416,24 +3438,24 @@
         <v>23</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>161</v>
+        <v>96</v>
       </c>
       <c r="J43" s="3">
-        <v>2</v>
+        <v>23</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>202</v>
+        <v>164</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>203</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>159</v>
+        <v>204</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>49</v>
@@ -3446,87 +3468,87 @@
         <v>23</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>182</v>
+        <v>161</v>
       </c>
       <c r="J44" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>47</v>
+        <v>206</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>180</v>
+        <v>159</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>207</v>
+        <v>178</v>
       </c>
       <c r="J45" s="3">
-        <v>42</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>164</v>
+        <v>47</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>56</v>
+        <v>176</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>161</v>
+        <v>182</v>
       </c>
       <c r="J46" s="3">
-        <v>2</v>
+        <v>43</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>210</v>
+        <v>164</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>211</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>212</v>
+        <v>56</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>194</v>
+        <v>49</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>38</v>
@@ -3536,27 +3558,27 @@
         <v>23</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>214</v>
+        <v>161</v>
       </c>
       <c r="J47" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>215</v>
+        <v>47</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>49</v>
+        <v>170</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>43</v>
@@ -3566,13 +3588,13 @@
         <v>23</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="J48" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -3580,13 +3602,13 @@
         <v>47</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>173</v>
+        <v>216</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>174</v>
+        <v>217</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>43</v>
@@ -3596,13 +3618,13 @@
         <v>23</v>
       </c>
       <c r="H49" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="I49" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="I49" s="3" t="s">
-        <v>182</v>
-      </c>
       <c r="J49" s="3">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="50">
@@ -3629,15 +3651,15 @@
         <v>222</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="J50" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>47</v>
+        <v>164</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>223</v>
@@ -3646,40 +3668,40 @@
         <v>224</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>225</v>
+        <v>49</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F51" s="3"/>
       <c r="G51" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>227</v>
+        <v>96</v>
       </c>
       <c r="J51" s="3">
-        <v>14</v>
+        <v>23</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>164</v>
+        <v>226</v>
       </c>
       <c r="B52" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="C52" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="C52" s="3" t="s">
-        <v>168</v>
-      </c>
       <c r="D52" s="3" t="s">
-        <v>49</v>
+        <v>196</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F52" s="3"/>
       <c r="G52" s="3" t="s">
@@ -3689,10 +3711,10 @@
         <v>229</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="J52" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -3703,7 +3725,7 @@
         <v>230</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>231</v>
+        <v>159</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>49</v>
@@ -3716,87 +3738,87 @@
         <v>23</v>
       </c>
       <c r="H53" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="I53" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="I53" s="3" t="s">
-        <v>96</v>
-      </c>
       <c r="J53" s="3">
-        <v>22</v>
+        <v>68</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="B54" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="B54" s="3" t="s">
-        <v>234</v>
-      </c>
       <c r="C54" s="3" t="s">
-        <v>235</v>
+        <v>195</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F54" s="3"/>
       <c r="G54" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>182</v>
+        <v>161</v>
       </c>
       <c r="J54" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>237</v>
+        <v>47</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>56</v>
+        <v>159</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>214</v>
+        <v>237</v>
       </c>
       <c r="J55" s="3">
-        <v>6</v>
+        <v>44</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>164</v>
+        <v>238</v>
       </c>
       <c r="B56" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="C56" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="C56" s="3" t="s">
-        <v>159</v>
-      </c>
       <c r="D56" s="3" t="s">
-        <v>49</v>
+        <v>135</v>
       </c>
       <c r="E56" s="3" t="s">
         <v>38</v>
@@ -3809,27 +3831,27 @@
         <v>241</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>242</v>
+        <v>178</v>
       </c>
       <c r="J56" s="3">
-        <v>67</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="B57" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="B57" s="3" t="s">
-        <v>184</v>
-      </c>
       <c r="C57" s="3" t="s">
-        <v>159</v>
+        <v>240</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>49</v>
+        <v>135</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F57" s="3"/>
       <c r="G57" s="3" t="s">
@@ -3839,10 +3861,10 @@
         <v>244</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>214</v>
+        <v>161</v>
       </c>
       <c r="J57" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58">
@@ -3853,10 +3875,10 @@
         <v>245</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>194</v>
+        <v>49</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>38</v>
@@ -3869,54 +3891,54 @@
         <v>246</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>161</v>
+        <v>137</v>
       </c>
       <c r="J58" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>47</v>
+        <v>164</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>247</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>159</v>
+        <v>248</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F59" s="3"/>
       <c r="G59" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>249</v>
+        <v>137</v>
       </c>
       <c r="J59" s="3">
-        <v>43</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="B60" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="B60" s="3" t="s">
-        <v>251</v>
-      </c>
       <c r="C60" s="3" t="s">
-        <v>252</v>
+        <v>204</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>150</v>
+        <v>49</v>
       </c>
       <c r="E60" s="3" t="s">
         <v>38</v>
@@ -3926,27 +3948,27 @@
         <v>23</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>182</v>
+        <v>137</v>
       </c>
       <c r="J60" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="C61" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="B61" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="C61" s="3" t="s">
-        <v>252</v>
-      </c>
       <c r="D61" s="3" t="s">
-        <v>150</v>
+        <v>49</v>
       </c>
       <c r="E61" s="3" t="s">
         <v>38</v>
@@ -3956,10 +3978,10 @@
         <v>23</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>161</v>
+        <v>178</v>
       </c>
       <c r="J61" s="3">
         <v>2</v>
@@ -3967,19 +3989,19 @@
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>47</v>
+        <v>256</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>257</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>168</v>
+        <v>240</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>49</v>
+        <v>135</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F62" s="3"/>
       <c r="G62" s="3" t="s">
@@ -3989,40 +4011,40 @@
         <v>258</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>214</v>
+        <v>178</v>
       </c>
       <c r="J62" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B63" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="B63" s="3" t="s">
+      <c r="C63" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="C63" s="3" t="s">
-        <v>261</v>
-      </c>
       <c r="D63" s="3" t="s">
-        <v>49</v>
+        <v>135</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F63" s="3"/>
       <c r="G63" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H63" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="I63" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="I63" s="3" t="s">
-        <v>182</v>
-      </c>
       <c r="J63" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="64">
@@ -4033,23 +4055,23 @@
         <v>264</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>38</v>
+        <v>265</v>
       </c>
       <c r="F64" s="3"/>
       <c r="G64" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>182</v>
+        <v>200</v>
       </c>
       <c r="J64" s="3">
         <v>1</v>
@@ -4057,16 +4079,16 @@
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>47</v>
+        <v>267</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>267</v>
+        <v>159</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>150</v>
+        <v>49</v>
       </c>
       <c r="E65" s="3" t="s">
         <v>43</v>
@@ -4076,40 +4098,40 @@
         <v>23</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>269</v>
+        <v>65</v>
       </c>
       <c r="J65" s="3">
-        <v>4</v>
+        <v>22</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="B66" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="B66" s="3" t="s">
-        <v>271</v>
-      </c>
       <c r="C66" s="3" t="s">
-        <v>267</v>
+        <v>159</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>150</v>
+        <v>49</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>272</v>
+        <v>38</v>
       </c>
       <c r="F66" s="3"/>
       <c r="G66" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>170</v>
+        <v>137</v>
       </c>
       <c r="J66" s="3">
         <v>0</v>
@@ -4117,13 +4139,13 @@
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>164</v>
+        <v>272</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>168</v>
+        <v>56</v>
       </c>
       <c r="D67" s="3" t="s">
         <v>49</v>
@@ -4136,13 +4158,13 @@
         <v>23</v>
       </c>
       <c r="H67" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="I67" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="I67" s="3" t="s">
-        <v>72</v>
-      </c>
       <c r="J67" s="3">
-        <v>8</v>
+        <v>35</v>
       </c>
     </row>
     <row r="68">
@@ -4153,13 +4175,13 @@
         <v>277</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>56</v>
+        <v>159</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F68" s="3"/>
       <c r="G68" s="3" t="s">
@@ -4169,24 +4191,24 @@
         <v>278</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>279</v>
+        <v>41</v>
       </c>
       <c r="J68" s="3">
-        <v>34</v>
+        <v>8</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C69" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="B69" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="C69" s="3" t="s">
-        <v>159</v>
-      </c>
       <c r="D69" s="3" t="s">
-        <v>49</v>
+        <v>135</v>
       </c>
       <c r="E69" s="3" t="s">
         <v>43</v>
@@ -4196,27 +4218,27 @@
         <v>23</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>41</v>
+        <v>182</v>
       </c>
       <c r="J69" s="3">
-        <v>7</v>
+        <v>43</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>284</v>
+        <v>247</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>159</v>
+        <v>280</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>49</v>
+        <v>135</v>
       </c>
       <c r="E70" s="3" t="s">
         <v>43</v>
@@ -4226,27 +4248,27 @@
         <v>23</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="J70" s="3">
-        <v>0</v>
+        <v>43</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="E71" s="3" t="s">
         <v>38</v>
@@ -4256,27 +4278,27 @@
         <v>23</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="J71" s="3">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="C72" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="B72" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="C72" s="3" t="s">
-        <v>291</v>
-      </c>
       <c r="D72" s="3" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="E72" s="3" t="s">
         <v>43</v>
@@ -4286,13 +4308,13 @@
         <v>23</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="I72" s="3" t="s">
         <v>161</v>
       </c>
       <c r="J72" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="73">
@@ -4300,7 +4322,7 @@
         <v>53</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C73" s="3" t="s">
         <v>159</v>
@@ -4316,13 +4338,13 @@
         <v>23</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="J73" s="3">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="74">
@@ -4330,10 +4352,10 @@
         <v>164</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>168</v>
+        <v>204</v>
       </c>
       <c r="D74" s="3" t="s">
         <v>49</v>
@@ -4346,24 +4368,24 @@
         <v>23</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="J74" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>168</v>
+        <v>204</v>
       </c>
       <c r="D75" s="3" t="s">
         <v>49</v>
@@ -4372,19 +4394,19 @@
         <v>38</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="G75" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="I75" s="3" t="s">
         <v>81</v>
       </c>
       <c r="J75" s="3">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="76">
@@ -4392,7 +4414,7 @@
         <v>53</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C76" s="3" t="s">
         <v>159</v>
@@ -4408,27 +4430,27 @@
         <v>23</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="J76" s="3">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>164</v>
+        <v>302</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>291</v>
+        <v>176</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>150</v>
+        <v>49</v>
       </c>
       <c r="E77" s="3" t="s">
         <v>38</v>
@@ -4438,13 +4460,13 @@
         <v>23</v>
       </c>
       <c r="H77" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="I77" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="I77" s="3" t="s">
-        <v>190</v>
-      </c>
       <c r="J77" s="3">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="78">
@@ -4455,7 +4477,7 @@
         <v>307</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>168</v>
+        <v>204</v>
       </c>
       <c r="D78" s="3" t="s">
         <v>49</v>
@@ -4471,81 +4493,81 @@
         <v>308</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>190</v>
+        <v>137</v>
       </c>
       <c r="J78" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="B79" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="B79" s="3" t="s">
-        <v>310</v>
-      </c>
       <c r="C79" s="3" t="s">
-        <v>224</v>
+        <v>289</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>225</v>
+        <v>135</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F79" s="3"/>
       <c r="G79" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="J79" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="B80" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="B80" s="3" t="s">
-        <v>313</v>
-      </c>
       <c r="C80" s="3" t="s">
-        <v>159</v>
+        <v>204</v>
       </c>
       <c r="D80" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F80" s="3"/>
       <c r="G80" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>170</v>
+        <v>189</v>
       </c>
       <c r="J80" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="B81" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="B81" s="3" t="s">
-        <v>316</v>
-      </c>
       <c r="C81" s="3" t="s">
-        <v>180</v>
+        <v>159</v>
       </c>
       <c r="D81" s="3" t="s">
         <v>49</v>
@@ -4558,21 +4580,21 @@
         <v>23</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>170</v>
+        <v>59</v>
       </c>
       <c r="J81" s="3">
-        <v>0</v>
+        <v>42</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="B82" s="3" t="s">
         <v>318</v>
-      </c>
-      <c r="B82" s="3" t="s">
-        <v>319</v>
       </c>
       <c r="C82" s="3" t="s">
         <v>159</v>
@@ -4581,67 +4603,67 @@
         <v>49</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F82" s="3"/>
       <c r="G82" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>41</v>
+        <v>137</v>
       </c>
       <c r="J82" s="3">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="B83" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="B83" s="3" t="s">
-        <v>322</v>
-      </c>
       <c r="C83" s="3" t="s">
-        <v>159</v>
+        <v>176</v>
       </c>
       <c r="D83" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F83" s="3"/>
       <c r="G83" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>84</v>
+        <v>200</v>
       </c>
       <c r="J83" s="3">
-        <v>44</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>53</v>
+        <v>323</v>
       </c>
       <c r="B84" s="3" t="s">
         <v>324</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>267</v>
+        <v>240</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F84" s="3"/>
       <c r="G84" s="3" t="s">
@@ -4651,141 +4673,141 @@
         <v>325</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>326</v>
+        <v>137</v>
       </c>
       <c r="J84" s="3">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="B85" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="B85" s="3" t="s">
-        <v>328</v>
-      </c>
       <c r="C85" s="3" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="D85" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F85" s="3"/>
       <c r="G85" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>170</v>
+        <v>84</v>
       </c>
       <c r="J85" s="3">
-        <v>0</v>
+        <v>45</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>330</v>
+        <v>53</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>240</v>
+        <v>329</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>159</v>
+        <v>260</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>49</v>
+        <v>135</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F86" s="3"/>
       <c r="G86" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H86" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="I86" s="3" t="s">
         <v>331</v>
       </c>
-      <c r="I86" s="3" t="s">
-        <v>242</v>
-      </c>
       <c r="J86" s="3">
-        <v>67</v>
+        <v>24</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B87" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="B87" s="3" t="s">
-        <v>179</v>
-      </c>
       <c r="C87" s="3" t="s">
-        <v>333</v>
+        <v>216</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>49</v>
+        <v>217</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F87" s="3"/>
       <c r="G87" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>182</v>
+        <v>123</v>
       </c>
       <c r="J87" s="3">
-        <v>1</v>
+        <v>51</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>47</v>
+        <v>334</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>335</v>
+        <v>230</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>224</v>
+        <v>159</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>225</v>
+        <v>49</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F88" s="3"/>
       <c r="G88" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>128</v>
+        <v>232</v>
       </c>
       <c r="J88" s="3">
-        <v>50</v>
+        <v>68</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="C89" s="3" t="s">
         <v>337</v>
-      </c>
-      <c r="B89" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="C89" s="3" t="s">
-        <v>168</v>
       </c>
       <c r="D89" s="3" t="s">
         <v>49</v>
@@ -4793,61 +4815,59 @@
       <c r="E89" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F89" s="3" t="s">
-        <v>339</v>
-      </c>
+      <c r="F89" s="3"/>
       <c r="G89" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="J89" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="C90" s="3" t="s">
         <v>341</v>
       </c>
-      <c r="B90" s="3" t="s">
-        <v>342</v>
-      </c>
-      <c r="C90" s="3" t="s">
-        <v>159</v>
-      </c>
       <c r="D90" s="3" t="s">
-        <v>49</v>
+        <v>135</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F90" s="3"/>
       <c r="G90" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>65</v>
+        <v>137</v>
       </c>
       <c r="J90" s="3">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="B91" s="3" t="s">
         <v>344</v>
       </c>
-      <c r="B91" s="3" t="s">
-        <v>345</v>
-      </c>
       <c r="C91" s="3" t="s">
-        <v>168</v>
+        <v>204</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>49</v>
@@ -4855,7 +4875,9 @@
       <c r="E91" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F91" s="3"/>
+      <c r="F91" s="3" t="s">
+        <v>345</v>
+      </c>
       <c r="G91" s="3" t="s">
         <v>23</v>
       </c>
@@ -4863,10 +4885,10 @@
         <v>346</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>76</v>
+        <v>178</v>
       </c>
       <c r="J91" s="3">
-        <v>26</v>
+        <v>2</v>
       </c>
     </row>
     <row r="92">
@@ -4877,37 +4899,37 @@
         <v>348</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>349</v>
+        <v>159</v>
       </c>
       <c r="D92" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>272</v>
+        <v>38</v>
       </c>
       <c r="F92" s="3"/>
       <c r="G92" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>182</v>
+        <v>65</v>
       </c>
       <c r="J92" s="3">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="B93" s="3" t="s">
         <v>351</v>
       </c>
-      <c r="B93" s="3" t="s">
-        <v>352</v>
-      </c>
       <c r="C93" s="3" t="s">
-        <v>333</v>
+        <v>204</v>
       </c>
       <c r="D93" s="3" t="s">
         <v>49</v>
@@ -4920,30 +4942,30 @@
         <v>23</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>170</v>
+        <v>76</v>
       </c>
       <c r="J93" s="3">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="B94" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="B94" s="3" t="s">
+      <c r="C94" s="3" t="s">
         <v>355</v>
       </c>
-      <c r="C94" s="3" t="s">
-        <v>168</v>
-      </c>
       <c r="D94" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>38</v>
+        <v>265</v>
       </c>
       <c r="F94" s="3"/>
       <c r="G94" s="3" t="s">
@@ -4953,10 +4975,10 @@
         <v>356</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="J94" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="95">
@@ -4967,37 +4989,37 @@
         <v>358</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>359</v>
+        <v>159</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>150</v>
+        <v>49</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F95" s="3"/>
       <c r="G95" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>182</v>
+        <v>137</v>
       </c>
       <c r="J95" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="B96" s="3" t="s">
         <v>361</v>
       </c>
-      <c r="B96" s="3" t="s">
-        <v>362</v>
-      </c>
       <c r="C96" s="3" t="s">
-        <v>180</v>
+        <v>56</v>
       </c>
       <c r="D96" s="3" t="s">
         <v>49</v>
@@ -5010,17 +5032,137 @@
         <v>23</v>
       </c>
       <c r="H96" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="J96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="B97" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="I96" s="3" t="s">
+      <c r="C97" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="D97" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E97" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F97" s="3"/>
+      <c r="G97" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H97" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="I97" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="J97" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="D98" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E98" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F98" s="3"/>
+      <c r="G98" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H98" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="I98" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="J98" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="D99" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="E99" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F99" s="3"/>
+      <c r="G99" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H99" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="I99" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="J99" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="D100" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F100" s="3"/>
+      <c r="G100" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="I100" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="J96" s="3">
-        <v>19</v>
+      <c r="J100" s="3">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J96"/>
+  <autoFilter ref="A1:J100"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -5117,6 +5259,10 @@
     <hyperlink ref="H94" r:id="rId93"/>
     <hyperlink ref="H95" r:id="rId94"/>
     <hyperlink ref="H96" r:id="rId95"/>
+    <hyperlink ref="H97" r:id="rId96"/>
+    <hyperlink ref="H98" r:id="rId97"/>
+    <hyperlink ref="H99" r:id="rId98"/>
+    <hyperlink ref="H100" r:id="rId99"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5124,8 +5270,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="54" customWidth="1"/>
-    <col min="2" max="2" width="35" customWidth="1"/>
+    <col min="1" max="1" width="48" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -5158,21 +5304,21 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>164</v>
+        <v>132</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>167</v>
+        <v>133</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>168</v>
+        <v>134</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>169</v>
+        <v>136</v>
       </c>
     </row>
     <row r="3">
@@ -5180,10 +5326,10 @@
         <v>164</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>196</v>
+        <v>245</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>159</v>
+        <v>204</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -5191,7 +5337,7 @@
         <v>23</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>197</v>
+        <v>246</v>
       </c>
     </row>
     <row r="4">
@@ -5199,10 +5345,10 @@
         <v>164</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>228</v>
+        <v>247</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>168</v>
+        <v>248</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -5210,18 +5356,18 @@
         <v>23</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>229</v>
+        <v>249</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>270</v>
+        <v>164</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>271</v>
+        <v>250</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>267</v>
+        <v>204</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -5229,15 +5375,15 @@
         <v>23</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>273</v>
+        <v>251</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>283</v>
+        <v>164</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>284</v>
+        <v>270</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>159</v>
@@ -5248,18 +5394,18 @@
         <v>23</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>285</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>159</v>
+        <v>204</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -5267,18 +5413,18 @@
         <v>23</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>180</v>
+        <v>159</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -5286,18 +5432,18 @@
         <v>23</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>168</v>
+        <v>240</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -5305,18 +5451,18 @@
         <v>23</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>351</v>
+        <v>339</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>352</v>
+        <v>340</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -5324,11 +5470,49 @@
         <v>23</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>353</v>
+        <v>342</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>362</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G10"/>
+  <autoFilter ref="A1:G12"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -5339,6 +5523,8 @@
     <hyperlink ref="G8" r:id="rId7"/>
     <hyperlink ref="G9" r:id="rId8"/>
     <hyperlink ref="G10" r:id="rId9"/>
+    <hyperlink ref="G11" r:id="rId10"/>
+    <hyperlink ref="G12" r:id="rId11"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5352,23 +5538,23 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>364</v>
+        <v>375</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>365</v>
+        <v>376</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B2" s="3">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="B3" s="3">
         <v>20</v>
@@ -5376,31 +5562,31 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>367</v>
+        <v>378</v>
       </c>
       <c r="B4" s="3">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="B5" s="3">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>369</v>
+        <v>126</v>
       </c>
       <c r="B6" s="3">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>131</v>
+        <v>380</v>
       </c>
       <c r="B7" s="3">
         <v>13</v>
@@ -5408,23 +5594,23 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>370</v>
+        <v>381</v>
       </c>
       <c r="B8" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>371</v>
+        <v>382</v>
       </c>
       <c r="B9" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>372</v>
+        <v>383</v>
       </c>
       <c r="B10" s="3">
         <v>11</v>
@@ -5432,7 +5618,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>373</v>
+        <v>384</v>
       </c>
       <c r="B11" s="3">
         <v>10</v>
@@ -5440,15 +5626,15 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="B12" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>375</v>
+        <v>386</v>
       </c>
       <c r="B13" s="3">
         <v>9</v>
@@ -5456,7 +5642,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c r="B14" s="3">
         <v>8</v>
@@ -5464,7 +5650,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="B15" s="3">
         <v>6</v>
@@ -5472,7 +5658,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="B16" s="3">
         <v>6</v>
@@ -5494,7 +5680,7 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
     </row>
     <row r="2">
@@ -5531,7 +5717,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>118</v>
+        <v>247</v>
       </c>
       <c r="B6" s="3">
         <v>3</v>
@@ -5547,7 +5733,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="B8" s="3">
         <v>2</v>
@@ -5555,7 +5741,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>179</v>
+        <v>125</v>
       </c>
       <c r="B9" s="3">
         <v>2</v>
@@ -5563,7 +5749,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="B10" s="3">
         <v>2</v>
@@ -5571,7 +5757,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>240</v>
+        <v>180</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -5579,7 +5765,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>255</v>
+        <v>230</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -5587,15 +5773,15 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>55</v>
+        <v>243</v>
       </c>
       <c r="B13" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>138</v>
+        <v>55</v>
       </c>
       <c r="B14" s="3">
         <v>1</v>
@@ -5603,7 +5789,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="B15" s="3">
         <v>1</v>
@@ -5611,7 +5797,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="B16" s="3">
         <v>1</v>
@@ -5632,16 +5818,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>380</v>
+        <v>391</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
     </row>
     <row r="2">
@@ -5691,10 +5877,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>118</v>
+        <v>35</v>
       </c>
       <c r="C5" s="3">
-        <v>10.1</v>
+        <v>7.1</v>
       </c>
       <c r="D5" s="3">
         <v>3</v>
@@ -5705,13 +5891,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="C6" s="3">
-        <v>7.1</v>
+        <v>6.0</v>
       </c>
       <c r="D6" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -5719,10 +5905,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>48</v>
+        <v>118</v>
       </c>
       <c r="C7" s="3">
-        <v>6.0</v>
+        <v>5.3</v>
       </c>
       <c r="D7" s="3">
         <v>2</v>
@@ -5733,13 +5919,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>130</v>
+        <v>247</v>
       </c>
       <c r="C8" s="3">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="D8" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -5747,13 +5933,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>55</v>
+        <v>125</v>
       </c>
       <c r="C9" s="3">
-        <v>3.0</v>
+        <v>3.6</v>
       </c>
       <c r="D9" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -5761,10 +5947,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>138</v>
+        <v>55</v>
       </c>
       <c r="C10" s="3">
-        <v>2.6</v>
+        <v>3.0</v>
       </c>
       <c r="D10" s="3">
         <v>1</v>
@@ -5775,10 +5961,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="C11" s="3">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="D11" s="3">
         <v>1</v>
@@ -5789,13 +5975,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>179</v>
+        <v>144</v>
       </c>
       <c r="C12" s="3">
         <v>2.4</v>
       </c>
       <c r="D12" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -5803,7 +5989,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="C13" s="3">
         <v>2.4</v>
@@ -5817,7 +6003,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>240</v>
+        <v>180</v>
       </c>
       <c r="C14" s="3">
         <v>2.4</v>
@@ -5831,7 +6017,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>255</v>
+        <v>230</v>
       </c>
       <c r="C15" s="3">
         <v>2.4</v>
@@ -5845,13 +6031,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>148</v>
+        <v>243</v>
       </c>
       <c r="C16" s="3">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="D16" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5871,15 +6057,15 @@
         <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>382</v>
+        <v>393</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="B2" s="3">
         <v>2</v>
@@ -5893,10 +6079,10 @@
         <v>38</v>
       </c>
       <c r="B3" s="3">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>383</v>
+        <v>394</v>
       </c>
     </row>
     <row r="4">
@@ -5904,10 +6090,10 @@
         <v>43</v>
       </c>
       <c r="B4" s="3">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>384</v>
+        <v>395</v>
       </c>
     </row>
   </sheetData>
@@ -5926,7 +6112,7 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
     </row>
     <row r="2">
@@ -5939,15 +6125,15 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="B3" s="3">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>194</v>
+        <v>37</v>
       </c>
       <c r="B4" s="3">
         <v>4</v>
@@ -5955,7 +6141,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>37</v>
+        <v>196</v>
       </c>
       <c r="B5" s="3">
         <v>3</v>
@@ -5963,15 +6149,15 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>225</v>
+        <v>170</v>
       </c>
       <c r="B6" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>174</v>
+        <v>217</v>
       </c>
       <c r="B7" s="3">
         <v>2</v>
@@ -5986,7 +6172,7 @@
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="32" customWidth="1"/>
+    <col min="3" max="3" width="37" customWidth="1"/>
     <col min="4" max="4" width="43" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
@@ -5998,10 +6184,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>385</v>
+        <v>396</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>26</v>
@@ -6013,10 +6199,10 @@
         <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>387</v>
+        <v>398</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>21</v>
@@ -6033,31 +6219,31 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>388</v>
+        <v>399</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>389</v>
+        <v>400</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>390</v>
+        <v>401</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>391</v>
+        <v>402</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>392</v>
+        <v>403</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>393</v>
+        <v>404</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>394</v>
+        <v>305</v>
       </c>
     </row>
     <row r="3">
@@ -6065,31 +6251,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>395</v>
+        <v>405</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>396</v>
+        <v>406</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>159</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
     </row>
     <row r="4">
@@ -6097,28 +6283,28 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>402</v>
+        <v>412</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>403</v>
+        <v>248</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>404</v>
+        <v>413</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>88</v>
@@ -6129,28 +6315,28 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>407</v>
+        <v>416</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>159</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>391</v>
+        <v>402</v>
       </c>
       <c r="F5" s="3">
         <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>408</v>
+        <v>417</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>409</v>
+        <v>418</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>88</v>
@@ -6161,31 +6347,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>347</v>
+        <v>368</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>348</v>
+        <v>419</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>349</v>
+        <v>159</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="F6" s="3">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>350</v>
+        <v>421</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>182</v>
+        <v>422</v>
       </c>
     </row>
     <row r="7">
@@ -6193,31 +6379,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>412</v>
+        <v>353</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>216</v>
+        <v>354</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>413</v>
+        <v>355</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>391</v>
+        <v>423</v>
       </c>
       <c r="F7" s="3">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>414</v>
+        <v>424</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>415</v>
+        <v>356</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>214</v>
+        <v>178</v>
       </c>
     </row>
     <row r="8">
@@ -6225,31 +6411,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>416</v>
+        <v>425</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>417</v>
+        <v>247</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>159</v>
+        <v>280</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>391</v>
+        <v>402</v>
       </c>
       <c r="F8" s="3">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>418</v>
+        <v>426</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="9">
@@ -6257,31 +6443,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>180</v>
+        <v>159</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="F9" s="3">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>214</v>
+        <v>432</v>
       </c>
     </row>
     <row r="10">
@@ -6289,31 +6475,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>235</v>
+        <v>176</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>404</v>
+        <v>413</v>
       </c>
       <c r="F10" s="3">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>427</v>
+        <v>435</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>428</v>
+        <v>436</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>88</v>
+        <v>422</v>
       </c>
     </row>
     <row r="11">
@@ -6321,31 +6507,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>430</v>
+        <v>438</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>431</v>
+        <v>228</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>391</v>
+        <v>413</v>
       </c>
       <c r="F11" s="3">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>433</v>
+        <v>440</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>434</v>
+        <v>88</v>
       </c>
     </row>
     <row r="12">
@@ -6353,31 +6539,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>159</v>
+        <v>443</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>437</v>
+        <v>402</v>
       </c>
       <c r="F12" s="3">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>81</v>
+        <v>446</v>
       </c>
     </row>
     <row r="13">
@@ -6385,31 +6571,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>332</v>
+        <v>447</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>179</v>
+        <v>448</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>333</v>
+        <v>159</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>391</v>
+        <v>449</v>
       </c>
       <c r="F13" s="3">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>440</v>
+        <v>450</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>334</v>
+        <v>451</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>182</v>
+        <v>81</v>
       </c>
     </row>
     <row r="14">
@@ -6417,31 +6603,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>361</v>
+        <v>336</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>441</v>
+        <v>175</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>168</v>
+        <v>337</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>391</v>
+        <v>402</v>
       </c>
       <c r="F14" s="3">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>443</v>
+        <v>338</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
     </row>
     <row r="15">
@@ -6449,31 +6635,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>444</v>
+        <v>453</v>
       </c>
       <c r="C15" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="F15" s="3">
+        <v>52</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="J15" s="3" t="s">
         <v>422</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>437</v>
-      </c>
-      <c r="F15" s="3">
-        <v>47</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>445</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>446</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>447</v>
       </c>
     </row>
     <row r="16">
@@ -6481,31 +6667,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>448</v>
+        <v>372</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>449</v>
+        <v>457</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>252</v>
+        <v>458</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="F16" s="3">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>450</v>
+        <v>459</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>451</v>
+        <v>460</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>59</v>
+        <v>275</v>
       </c>
     </row>
     <row r="17">
@@ -6513,31 +6699,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>361</v>
+        <v>461</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>452</v>
+        <v>434</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>391</v>
+        <v>449</v>
       </c>
       <c r="F17" s="3">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>453</v>
+        <v>462</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>454</v>
+        <v>463</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>182</v>
+        <v>464</v>
       </c>
     </row>
     <row r="18">
@@ -6545,31 +6731,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>455</v>
+        <v>465</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>456</v>
+        <v>466</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>159</v>
+        <v>240</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>404</v>
+        <v>423</v>
       </c>
       <c r="F18" s="3">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>457</v>
+        <v>467</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>458</v>
+        <v>468</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>182</v>
+        <v>59</v>
       </c>
     </row>
     <row r="19">
@@ -6577,31 +6763,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>459</v>
+        <v>372</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>266</v>
+        <v>469</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>267</v>
+        <v>169</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>460</v>
+        <v>402</v>
       </c>
       <c r="F19" s="3">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>461</v>
+        <v>470</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>462</v>
+        <v>471</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>41</v>
+        <v>178</v>
       </c>
     </row>
     <row r="20">
@@ -6609,31 +6795,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>463</v>
+        <v>472</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>464</v>
+        <v>473</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>267</v>
+        <v>159</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>404</v>
+        <v>413</v>
       </c>
       <c r="F20" s="3">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>465</v>
+        <v>474</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>466</v>
+        <v>475</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>88</v>
+        <v>178</v>
       </c>
     </row>
     <row r="21">
@@ -6641,31 +6827,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>467</v>
+        <v>476</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>468</v>
+        <v>259</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>159</v>
+        <v>260</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>391</v>
+        <v>477</v>
       </c>
       <c r="F21" s="3">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>469</v>
+        <v>478</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>470</v>
+        <v>479</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>471</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/reports/devops-jobs-israel-2026-W41.xlsx
+++ b/reports/devops-jobs-israel-2026-W41.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="496" uniqueCount="496">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="507">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-07T13:10:32</t>
+    <t xml:space="preserve">2026-10-08T13:17:20</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Junior %</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0%</t>
+    <t xml:space="preserve">1.0%</t>
   </si>
   <si>
     <t xml:space="preserve">Salary disclosure rate %</t>
@@ -372,12 +372,27 @@
     <t xml:space="preserve">2026-08-28</t>
   </si>
   <si>
+    <t xml:space="preserve">Agent Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Similarweb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/8264120</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-08</t>
+  </si>
+  <si>
     <t xml:space="preserve">Senior Backend Engineer, Platform Foundations</t>
   </si>
   <si>
-    <t xml:space="preserve">Similarweb</t>
-  </si>
-  <si>
     <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Ansible, Docker, CI/CD, Python</t>
   </si>
   <si>
@@ -546,804 +561,813 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-platform-engineer-cti-at-dream-4465727084</t>
   </si>
   <si>
+    <t xml:space="preserve">DevOps Engineer (25769)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yael Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-25769-at-yael-group-4474444402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer - Data Platform (Cortex)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palo Alto Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-data-platform-cortex-at-palo-alto-networks-4455871961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Principal DevOps Engineer (Cortex Agentix Endpoint Security)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-devops-engineer-cortex-agentix-endpoint-security-at-palo-alto-networks-4418753719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Checkmarx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-checkmarx-4439196775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr. DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harmonic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-devops-engineer-at-harmonic-4360460066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gini-Apps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gini-apps-4476189127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stealth Startup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-stealth-startup-4475760813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connecteam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4428832411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buildots</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-buildots-4473477683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akeyless Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-akeyless-security-4457183616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blink</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-blink-4473214725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zscaler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-devops-engineer-at-zscaler-4465317702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bitsight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-bitsight-4476962715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fetcherr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fetcherr-4429844723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cellebrite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-cellebrite-4469980397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personetics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-personetics-4428829912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moon Active</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-moon-active-4447023421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Polytex Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-polytex-technologies-4473474269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-gong-4457888927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extreme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-devops-engineer-at-extreme-4475385097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4475164979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-4474645372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gloat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gloat-4474071911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cybersixgill, a Bitsight Company</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cybersixgill-a-bitsight-company-4476927366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps - AI Factory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kaltura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-ai-factory-at-kaltura-4475505499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure and Automation Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dialog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-and-automation-engineer-at-dialog-4473641075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jobgether</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-jobgether-4472898137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRE / DevOps Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">april</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-devops-lead-at-april-4416179005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantum Machines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-quantum-machines-4474990509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQLink Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yehud Monosson, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sqlink-group-4476701773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Software Engineer, DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aiven</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-software-engineer-devops-at-aiven-4426867332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staff Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grubhub</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/staff-site-reliability-engineer-at-grubhub-4473025762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineering - Storage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineering-storage-at-nvidia-4457190574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-nvidia-4457410161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Integrator SRE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compie Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-integrator-sre-at-compie-technologies-4477142119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineer III, Platform Engineering and Infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-iii-platform-engineering-and-infrastructure-at-google-4465561954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Platform &amp; SRE Group Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-sre-group-leader-at-extreme-4450267100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SciPlay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-sciplay-4391151881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medulla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-medulla-4475546635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure Engineer (Kubernetes &amp; Node.js)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oriient</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-kubernetes-node-js-at-oriient-4461069125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platform Engineering Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corsa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineering-team-lead-at-corsa-4476174341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Millennium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-millennium-4457617255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI &amp; Software Infra Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BioCatch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-software-infra-engineer-at-biocatch-4447894244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alice (Formerly ActiveFence)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-alice-formerly-activefence-4472729462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shavit Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-shavit-software-4476775539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Backend &amp; DevOps Engineer – AI/LLM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BlackEdge Labs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Savyon, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/backend-devops-engineer-%E2%80%93-ai-llm-at-blackedge-labs-4477122203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Developer (DevOps and Infrastructure)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rapyd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-developer-devops-and-infrastructure-at-rapyd-4475489875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DoiT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-doit-4463987032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TeraSky</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-terasky-4455198528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Infrastructure &amp; Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-cloud-engineer-at-moon-active-4447031167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Cloud Engineer (GCP Focus)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MyOps by Yael Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloud-engineer-gcp-focus-at-myops-by-yael-group-4477131302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure System Engineer</t>
+  </si>
+  <si>
     <t xml:space="preserve">Logica-IT</t>
   </si>
   <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-logica-it-4473616803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer - Data Platform (Cortex)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palo Alto Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-data-platform-cortex-at-palo-alto-networks-4455871961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Principal DevOps Engineer (Cortex Cloud)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-principal-devops-engineer-cortex-cloud-at-palo-alto-networks-4443693726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps- 243492</t>
+    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-system-engineer-at-logica-it-4473666027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Cloud Network &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Applied Materials - Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloud-network-devops-engineer-at-applied-materials-israel-4474407748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT DevOps Engineer - 244284</t>
   </si>
   <si>
     <t xml:space="preserve">Experis Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Yehud Monosson, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-243492-at-experis-israel-4472685735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Checkmarx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-checkmarx-4439196775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sr. DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harmonic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-devops-engineer-at-harmonic-4360460066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gini-Apps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gini-apps-4476189127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connecteam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4428832411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Buildots</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-buildots-4473477683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zafran Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-zafran-security-4475510036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Akeyless Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-akeyless-security-4457183616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blink</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-blink-4473214725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fetcherr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fetcherr-4429844723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cellebrite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-cellebrite-4469980397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer - Base44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Base44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-base44-at-base44-4474179911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Personetics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-personetics-4428829912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps / Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">recruitricks</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-devops-engineer-244284-at-experis-israel-4475777772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer (FinOps oriented)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CloudTeam.ai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FinOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-finops-oriented-at-cloudteam-ai-4473603103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DriveNets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-devops-engineer-at-drivenets-4465793281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cato Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-system-engineer-at-cato-networks-4463471007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tesnet Group Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-tesnet-group-ltd-4477160595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior System &amp; Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Final</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat HaSharon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-infrastructure-engineer-at-final-4475581791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Infrastructure Engineer - Proxy Network</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nimble</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-proxy-network-at-nimble-4475424343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP &amp; System Administrator (36759)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/gcp-system-administrator-36759-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4477174630</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-elbit-systems-israel-4474036853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-system-engineer-at-comda-4473615194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft System Engineer (37652)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-system-engineer-37652-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4477168624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashdod, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-sqlink-group-4473649114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-system-administrator-at-shavit-software-4476766481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft System Administrator (5515)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INGIMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-system-administrator-5515-at-ingima-4476707352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Talent Integration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-talent-integration-4466204750</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Development Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clarivate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/development-operations-engineer-at-clarivate-4467992253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps &amp; Cloud Infrastructure Intern</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-infrastructure-intern-at-f5-4464650168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Student DevOps Engineer- CxP Commercial Foundation Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Terraform/IaC, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-devops-engineer-cxp-commercial-foundation-services-at-sap-4436819328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Terraform/IaC, Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HPC Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Terraform/IaC, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/hpc-operations-engineer-at-nvidia-4471977303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Technical Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4452212223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security Analyst (Student Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upwind Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/security-analyst-student-position-at-upwind-security-4473525994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineer Student, SPIV team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amazon Web Services (AWS)</t>
   </si>
   <si>
     <t xml:space="preserve">Haifa, Haifa District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-platform-engineer-at-recruitricks-4475527624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moon Active</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-moon-active-4447023421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Polytex Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-polytex-technologies-4473474269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-gong-4457888927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Developer (37703)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-developer-37703-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4475562544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extreme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-devops-engineer-at-extreme-4475385097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4475164979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-4474645372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gloat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gloat-4474071911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps - AI Factory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kaltura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-ai-factory-at-kaltura-4475505499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure and Automation Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dialog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-and-automation-engineer-at-dialog-4473641075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jobgether</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-jobgether-4472898137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior DevOps Engineer — AI-Native</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ArtAc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-devops-engineer-%E2%80%94-ai-native-at-artac-4476141177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRE / DevOps Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">april</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-devops-lead-at-april-4416179005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quantum Machines</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-quantum-machines-4474990509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Data Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">evoke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-data-infrastructure-engineer-at-evoke-4462157157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Staff Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grubhub</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/staff-site-reliability-engineer-at-grubhub-4473025762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineering - Storage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineering-storage-at-nvidia-4457190574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-nvidia-4457410161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Platform &amp; SRE Group Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-sre-group-leader-at-extreme-4450267100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Software Engineer, DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aiven</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-software-engineer-devops-at-aiven-4426867332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SciPlay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-sciplay-4391151881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medulla</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-medulla-4475546635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure Engineer (Kubernetes &amp; Node.js)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oriient</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-kubernetes-node-js-at-oriient-4461069125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Viz.ai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-viz-ai-4437383686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineer III, Platform Engineering and Infrastructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-iii-platform-engineering-and-infrastructure-at-google-4465561954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Platform Engineering Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corsa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineering-team-lead-at-corsa-4476174341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ThetaRay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-thetaray-4472910650</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Principal Devops &amp; Infra Tech Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sunbit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-devops-infra-tech-lead-at-sunbit-4474134295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Millennium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-millennium-4457617255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI &amp; Software Infra Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BioCatch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-software-infra-engineer-at-biocatch-4447894244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alice (Formerly ActiveFence)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-alice-formerly-activefence-4472729462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineer – DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential Careers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-%E2%80%93-devops-at-confidential-careers-4475416238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Developer (DevOps and Infrastructure)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rapyd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-developer-devops-and-infrastructure-at-rapyd-4428485007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DoiT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-doit-4463987032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TeraSky</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-terasky-4455198528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Infrastructure &amp; Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-cloud-engineer-at-moon-active-4447031167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-system-engineer-at-logica-it-4473666027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Cloud Network &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Applied Materials - Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloud-network-devops-engineer-at-applied-materials-israel-4474407748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (FinOps oriented)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CloudTeam.ai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FinOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-finops-oriented-at-cloudteam-ai-4473603103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DriveNets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-devops-engineer-at-drivenets-4465793281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cato Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-system-engineer-at-cato-networks-4463471007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior System &amp; Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Final</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat HaSharon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-infrastructure-engineer-at-final-4475581791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Infrastructure Engineer - Proxy Network</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nimble</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-proxy-network-at-nimble-4475424343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wayve</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-wayve-4474417523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-elbit-systems-israel-4474036853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-system-engineer-at-comda-4473615194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQLink Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ashdod, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-sqlink-group-4473649114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Talent Integration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-talent-integration-4466204750</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strength Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.5%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.5%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Development Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clarivate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/development-operations-engineer-at-clarivate-4467992253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps &amp; Cloud Infrastructure Intern</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-infrastructure-intern-at-f5-4464650168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Student DevOps Engineer- CxP Commercial Foundation Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Terraform/IaC, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-devops-engineer-cxp-commercial-foundation-services-at-sap-4436819328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Terraform/IaC, Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HPC Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Terraform/IaC, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/hpc-operations-engineer-at-nvidia-4471977303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Technical Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4452212223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security Analyst (Student Position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upwind Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/security-analyst-student-position-at-upwind-security-4473525994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineer Student, SPIV team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amazon Web Services (AWS)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, CI/CD, Automation</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-student-spiv-team-at-amazon-web-services-aws-4456348779</t>
   </si>
   <si>
+    <t xml:space="preserve">Student Software Engineer – Cloud, Big Data, Billing &amp; AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Cloud (any), Docker, Kubernetes, CI/CD, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-software-engineer-%E2%80%93-cloud-big-data-billing-ai-at-sap-4476596020</t>
+  </si>
+  <si>
     <t xml:space="preserve">Production Operations Engineer</t>
   </si>
   <si>
@@ -1380,28 +1404,13 @@
     <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Terraform/IaC, Networking, Automation</t>
   </si>
   <si>
-    <t xml:space="preserve">System Administrator #1350</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Docker, Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%231350-at-rad-4473722167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CONTROP Precision Technologies Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Networking, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-controp-precision-technologies-ltd-4460943847</t>
+    <t xml:space="preserve">Network Operations Center</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Monitoring, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/network-operations-center-at-compie-technologies-4476168349</t>
   </si>
   <si>
     <t xml:space="preserve">Technical Support Specialist</t>
@@ -1428,15 +1437,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
   </si>
   <si>
-    <t xml:space="preserve">TytoCare</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-tytocare-4475569150</t>
-  </si>
-  <si>
     <t xml:space="preserve">Data Operations Student - Nights &amp; Weekend shifts</t>
   </si>
   <si>
@@ -1449,16 +1449,49 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-operations-student-nights-weekend-shifts-at-voyantis-4473649691</t>
   </si>
   <si>
-    <t xml:space="preserve">Junior System Administrator (Monitoring Team)</t>
+    <t xml:space="preserve">Software Engineering INTERN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Cloud (any), CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-intern-at-microsoft-4451071541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raft Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Service Desk Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appsflyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8874236002?gh_jid=8874236002</t>
   </si>
   <si>
     <t xml:space="preserve">Junior SysAdmin / Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-monitoring-team-at-jobgether-4471710321</t>
   </si>
   <si>
     <t xml:space="preserve">Roles requiring it</t>
@@ -1631,7 +1664,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="7">
@@ -1639,7 +1672,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8">
@@ -1647,7 +1680,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>39</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9">
@@ -1655,7 +1688,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>869</v>
+        <v>877</v>
       </c>
     </row>
     <row r="10">
@@ -1663,7 +1696,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1727,7 +1760,7 @@
         <v>23</v>
       </c>
       <c r="B19" s="3">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="20">
@@ -1735,7 +1768,7 @@
         <v>24</v>
       </c>
       <c r="B20" s="3">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -1754,36 +1787,36 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>392</v>
+        <v>399</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="B2" s="3">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="B3" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>449</v>
+        <v>457</v>
       </c>
       <c r="B4" s="3">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="B5" s="3">
         <v>2</v>
@@ -1791,15 +1824,15 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>477</v>
+        <v>414</v>
       </c>
       <c r="B6" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>407</v>
+        <v>490</v>
       </c>
       <c r="B7" s="3">
         <v>1</v>
@@ -1818,15 +1851,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>375</v>
+        <v>384</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>480</v>
+        <v>491</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>481</v>
+        <v>492</v>
       </c>
       <c r="B2" s="3">
         <v>25</v>
@@ -1834,39 +1867,39 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>482</v>
+        <v>493</v>
       </c>
       <c r="B3" s="3">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>384</v>
+        <v>494</v>
       </c>
       <c r="B4" s="3">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="B5" s="3">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>483</v>
+        <v>395</v>
       </c>
       <c r="B6" s="3">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>484</v>
+        <v>495</v>
       </c>
       <c r="B7" s="3">
         <v>16</v>
@@ -1874,23 +1907,23 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="B8" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="B9" s="3">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c r="B10" s="3">
         <v>10</v>
@@ -1898,7 +1931,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>381</v>
+        <v>296</v>
       </c>
       <c r="B11" s="3">
         <v>10</v>
@@ -1906,7 +1939,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="B12" s="3">
         <v>9</v>
@@ -1914,34 +1947,34 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>297</v>
+        <v>387</v>
       </c>
       <c r="B13" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>377</v>
+        <v>390</v>
       </c>
       <c r="B14" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>380</v>
+        <v>329</v>
       </c>
       <c r="B15" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>486</v>
+        <v>497</v>
       </c>
       <c r="B16" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1966,13 +1999,13 @@
         <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>487</v>
+        <v>498</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>488</v>
+        <v>499</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>489</v>
+        <v>500</v>
       </c>
     </row>
     <row r="2">
@@ -1980,13 +2013,13 @@
         <v>24</v>
       </c>
       <c r="B2" s="3">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C2" s="3">
-        <v>11.9</v>
+        <v>12.0</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>490</v>
+        <v>501</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -1995,88 +2028,88 @@
         <v>23</v>
       </c>
       <c r="B3" s="3">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C3" s="3">
-        <v>35.6</v>
+        <v>36.0</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>490</v>
+        <v>501</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>491</v>
+        <v>502</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>490</v>
+        <v>501</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>492</v>
+        <v>503</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>1.5</v>
+        <v>3.4</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>490</v>
+        <v>501</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>493</v>
+        <v>504</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>46.9</v>
+        <v>30.9</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>490</v>
+        <v>501</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>494</v>
+        <v>505</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>17.3</v>
+        <v>14.5</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>490</v>
+        <v>501</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>495</v>
+        <v>506</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>21.0</v>
+        <v>18.7</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>490</v>
+        <v>501</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -2160,7 +2193,7 @@
         <v>41</v>
       </c>
       <c r="J2" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
@@ -2192,7 +2225,7 @@
         <v>41</v>
       </c>
       <c r="J3" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
@@ -2224,7 +2257,7 @@
         <v>41</v>
       </c>
       <c r="J4" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
@@ -2256,7 +2289,7 @@
         <v>52</v>
       </c>
       <c r="J5" s="3">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6">
@@ -2288,7 +2321,7 @@
         <v>52</v>
       </c>
       <c r="J6" s="3">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7">
@@ -2320,7 +2353,7 @@
         <v>59</v>
       </c>
       <c r="J7" s="3">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8">
@@ -2352,7 +2385,7 @@
         <v>65</v>
       </c>
       <c r="J8" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9">
@@ -2384,7 +2417,7 @@
         <v>52</v>
       </c>
       <c r="J9" s="3">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10">
@@ -2416,7 +2449,7 @@
         <v>72</v>
       </c>
       <c r="J10" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
@@ -2448,7 +2481,7 @@
         <v>76</v>
       </c>
       <c r="J11" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12">
@@ -2480,7 +2513,7 @@
         <v>81</v>
       </c>
       <c r="J12" s="3">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13">
@@ -2512,7 +2545,7 @@
         <v>84</v>
       </c>
       <c r="J13" s="3">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="14">
@@ -2544,7 +2577,7 @@
         <v>88</v>
       </c>
       <c r="J14" s="3">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15">
@@ -2576,7 +2609,7 @@
         <v>92</v>
       </c>
       <c r="J15" s="3">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="16">
@@ -2608,7 +2641,7 @@
         <v>96</v>
       </c>
       <c r="J16" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17">
@@ -2640,7 +2673,7 @@
         <v>102</v>
       </c>
       <c r="J17" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18">
@@ -2672,7 +2705,7 @@
         <v>106</v>
       </c>
       <c r="J18" s="3">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="19">
@@ -2704,7 +2737,7 @@
         <v>96</v>
       </c>
       <c r="J19" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20">
@@ -2736,7 +2769,7 @@
         <v>65</v>
       </c>
       <c r="J20" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -2768,7 +2801,7 @@
         <v>116</v>
       </c>
       <c r="J21" s="3">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="22">
@@ -2779,39 +2812,39 @@
         <v>118</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>99</v>
+        <v>119</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>92</v>
+        <v>122</v>
       </c>
       <c r="J22" s="3">
-        <v>41</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>47</v>
+        <v>123</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>118</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>49</v>
+        <v>99</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>49</v>
@@ -2820,27 +2853,27 @@
         <v>43</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>123</v>
+        <v>92</v>
       </c>
       <c r="J23" s="3">
-        <v>51</v>
+        <v>42</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>124</v>
+        <v>47</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>49</v>
@@ -2849,7 +2882,7 @@
         <v>49</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>126</v>
@@ -2864,7 +2897,7 @@
         <v>128</v>
       </c>
       <c r="J24" s="3">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="25">
@@ -2872,7 +2905,7 @@
         <v>129</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>49</v>
@@ -2881,73 +2914,73 @@
         <v>49</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>67</v>
+        <v>131</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="J25" s="3">
-        <v>19</v>
+        <v>48</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>134</v>
+        <v>49</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>135</v>
+        <v>49</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F26" s="3"/>
+      <c r="F26" s="3" t="s">
+        <v>67</v>
+      </c>
       <c r="G26" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H26" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="I26" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="I26" s="3" t="s">
-        <v>137</v>
-      </c>
       <c r="J26" s="3">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B27" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="C27" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="C27" s="3" t="s">
-        <v>99</v>
-      </c>
       <c r="D27" s="3" t="s">
-        <v>49</v>
+        <v>140</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F27" s="3" t="s">
-        <v>140</v>
-      </c>
+      <c r="F27" s="3"/>
       <c r="G27" s="3" t="s">
         <v>24</v>
       </c>
@@ -2958,7 +2991,7 @@
         <v>142</v>
       </c>
       <c r="J27" s="3">
-        <v>64</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2969,7 +3002,7 @@
         <v>144</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>145</v>
+        <v>99</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>49</v>
@@ -2978,19 +3011,19 @@
         <v>43</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H28" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="I28" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="I28" s="3" t="s">
-        <v>52</v>
-      </c>
       <c r="J28" s="3">
-        <v>57</v>
+        <v>65</v>
       </c>
     </row>
     <row r="29">
@@ -3004,7 +3037,7 @@
         <v>150</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>135</v>
+        <v>49</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>43</v>
@@ -3019,10 +3052,10 @@
         <v>152</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="J29" s="3">
-        <v>37</v>
+        <v>58</v>
       </c>
     </row>
     <row r="30">
@@ -3033,58 +3066,60 @@
         <v>154</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>49</v>
+        <v>155</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>49</v>
+        <v>140</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>157</v>
+        <v>81</v>
       </c>
       <c r="J30" s="3">
-        <v>30</v>
+        <v>38</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>47</v>
+        <v>158</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>159</v>
+        <v>49</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F31" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>160</v>
+      </c>
       <c r="G31" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J31" s="3">
-        <v>3</v>
+        <v>31</v>
       </c>
     </row>
     <row r="32">
@@ -3092,10 +3127,10 @@
         <v>47</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>49</v>
@@ -3108,60 +3143,60 @@
         <v>23</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>76</v>
+        <v>166</v>
       </c>
       <c r="J32" s="3">
-        <v>27</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="C33" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="B33" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>159</v>
-      </c>
       <c r="D33" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F33" s="3"/>
       <c r="G33" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>116</v>
+        <v>76</v>
       </c>
       <c r="J33" s="3">
-        <v>40</v>
+        <v>28</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>170</v>
+        <v>49</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
@@ -3171,10 +3206,10 @@
         <v>171</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>157</v>
+        <v>116</v>
       </c>
       <c r="J34" s="3">
-        <v>30</v>
+        <v>41</v>
       </c>
     </row>
     <row r="35">
@@ -3185,10 +3220,10 @@
         <v>173</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>49</v>
+        <v>175</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>43</v>
@@ -3198,84 +3233,84 @@
         <v>23</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>96</v>
+        <v>162</v>
       </c>
       <c r="J35" s="3">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="C36" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="B36" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>176</v>
-      </c>
       <c r="D36" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>178</v>
+        <v>96</v>
       </c>
       <c r="J36" s="3">
-        <v>2</v>
+        <v>24</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>159</v>
+        <v>182</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F37" s="3"/>
       <c r="G37" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>182</v>
+        <v>122</v>
       </c>
       <c r="J37" s="3">
-        <v>43</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>49</v>
@@ -3288,54 +3323,56 @@
         <v>23</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>88</v>
+        <v>187</v>
       </c>
       <c r="J38" s="3">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="B39" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="B39" s="3" t="s">
-        <v>186</v>
-      </c>
       <c r="C39" s="3" t="s">
-        <v>187</v>
+        <v>164</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>135</v>
+        <v>49</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F39" s="3"/>
+      <c r="F39" s="3" t="s">
+        <v>189</v>
+      </c>
       <c r="G39" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>189</v>
+        <v>92</v>
       </c>
       <c r="J39" s="3">
-        <v>6</v>
+        <v>42</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>176</v>
+        <v>192</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>49</v>
@@ -3348,27 +3385,27 @@
         <v>23</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="J40" s="3">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>43</v>
@@ -3378,24 +3415,24 @@
         <v>23</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="I41" s="3" t="s">
         <v>59</v>
       </c>
       <c r="J41" s="3">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C42" s="3" t="s">
         <v>164</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>159</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>49</v>
@@ -3408,24 +3445,24 @@
         <v>23</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="J42" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>159</v>
+        <v>182</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>49</v>
@@ -3438,24 +3475,24 @@
         <v>23</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>96</v>
+        <v>122</v>
       </c>
       <c r="J43" s="3">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="C44" s="3" t="s">
         <v>164</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>204</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>49</v>
@@ -3468,24 +3505,24 @@
         <v>23</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>161</v>
+        <v>96</v>
       </c>
       <c r="J44" s="3">
-        <v>3</v>
+        <v>24</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>206</v>
+        <v>169</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>207</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>159</v>
+        <v>182</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>49</v>
@@ -3501,10 +3538,10 @@
         <v>208</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="J45" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="46">
@@ -3515,7 +3552,7 @@
         <v>209</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>176</v>
+        <v>192</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>49</v>
@@ -3531,15 +3568,15 @@
         <v>210</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="J46" s="3">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>211</v>
@@ -3561,24 +3598,24 @@
         <v>212</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="J47" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>47</v>
+        <v>195</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>213</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>170</v>
+        <v>49</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>43</v>
@@ -3591,10 +3628,10 @@
         <v>214</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>178</v>
+        <v>76</v>
       </c>
       <c r="J48" s="3">
-        <v>2</v>
+        <v>28</v>
       </c>
     </row>
     <row r="49">
@@ -3605,10 +3642,10 @@
         <v>215</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>216</v>
+        <v>164</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>217</v>
+        <v>49</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>43</v>
@@ -3618,114 +3655,114 @@
         <v>23</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>219</v>
+        <v>122</v>
       </c>
       <c r="J49" s="3">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>220</v>
+        <v>47</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>49</v>
+        <v>175</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>189</v>
+        <v>219</v>
       </c>
       <c r="J50" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>164</v>
+        <v>47</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>49</v>
+        <v>222</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F51" s="3"/>
       <c r="G51" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>96</v>
+        <v>224</v>
       </c>
       <c r="J51" s="3">
-        <v>23</v>
+        <v>16</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="C52" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="B52" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>228</v>
-      </c>
       <c r="D52" s="3" t="s">
-        <v>196</v>
+        <v>49</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F52" s="3"/>
       <c r="G52" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>178</v>
+        <v>96</v>
       </c>
       <c r="J52" s="3">
-        <v>2</v>
+        <v>24</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="C53" s="3" t="s">
         <v>164</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>159</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>49</v>
@@ -3738,27 +3775,27 @@
         <v>23</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="J53" s="3">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>38</v>
@@ -3768,13 +3805,13 @@
         <v>23</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="J54" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="55">
@@ -3782,10 +3819,10 @@
         <v>47</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>49</v>
@@ -3798,27 +3835,27 @@
         <v>23</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="J55" s="3">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="C56" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="B56" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>240</v>
-      </c>
       <c r="D56" s="3" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="E56" s="3" t="s">
         <v>38</v>
@@ -3828,27 +3865,27 @@
         <v>23</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="J56" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>242</v>
+        <v>169</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>240</v>
+        <v>182</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>135</v>
+        <v>49</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>38</v>
@@ -3858,27 +3895,27 @@
         <v>23</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>161</v>
+        <v>142</v>
       </c>
       <c r="J57" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>204</v>
+        <v>243</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>38</v>
@@ -3888,27 +3925,27 @@
         <v>23</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>248</v>
+        <v>182</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>38</v>
@@ -3918,24 +3955,24 @@
         <v>23</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="J59" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>204</v>
+        <v>182</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>49</v>
@@ -3948,10 +3985,10 @@
         <v>23</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="J60" s="3">
         <v>0</v>
@@ -3959,13 +3996,13 @@
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>49</v>
@@ -3978,27 +4015,27 @@
         <v>23</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>178</v>
+        <v>219</v>
       </c>
       <c r="J61" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>38</v>
@@ -4008,13 +4045,13 @@
         <v>23</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>178</v>
+        <v>219</v>
       </c>
       <c r="J62" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="63">
@@ -4022,13 +4059,13 @@
         <v>47</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="E63" s="3" t="s">
         <v>43</v>
@@ -4038,87 +4075,87 @@
         <v>23</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="J63" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>260</v>
+        <v>164</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>135</v>
+        <v>49</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>265</v>
+        <v>43</v>
       </c>
       <c r="F64" s="3"/>
       <c r="G64" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>200</v>
+        <v>65</v>
       </c>
       <c r="J64" s="3">
-        <v>1</v>
+        <v>23</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>267</v>
+        <v>169</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F65" s="3"/>
       <c r="G65" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>65</v>
+        <v>142</v>
       </c>
       <c r="J65" s="3">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>159</v>
+        <v>266</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>49</v>
+        <v>140</v>
       </c>
       <c r="E66" s="3" t="s">
         <v>38</v>
@@ -4128,10 +4165,10 @@
         <v>23</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="J66" s="3">
         <v>0</v>
@@ -4139,43 +4176,43 @@
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>56</v>
+        <v>270</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>49</v>
+        <v>140</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F67" s="3"/>
       <c r="G67" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>275</v>
+        <v>166</v>
       </c>
       <c r="J67" s="3">
-        <v>35</v>
+        <v>4</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>49</v>
@@ -4188,27 +4225,27 @@
         <v>23</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="I68" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J68" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="E69" s="3" t="s">
         <v>43</v>
@@ -4218,27 +4255,27 @@
         <v>23</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="J69" s="3">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="E70" s="3" t="s">
         <v>43</v>
@@ -4248,27 +4285,27 @@
         <v>23</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="J70" s="3">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>243</v>
+        <v>281</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>240</v>
+        <v>182</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>135</v>
+        <v>49</v>
       </c>
       <c r="E71" s="3" t="s">
         <v>38</v>
@@ -4278,114 +4315,114 @@
         <v>23</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>286</v>
+        <v>122</v>
       </c>
       <c r="J71" s="3">
-        <v>61</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>289</v>
+        <v>192</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>135</v>
+        <v>49</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F72" s="3"/>
       <c r="G72" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>161</v>
+        <v>286</v>
       </c>
       <c r="J72" s="3">
-        <v>3</v>
+        <v>22</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>53</v>
+        <v>287</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>291</v>
+        <v>237</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>159</v>
+        <v>238</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>49</v>
+        <v>140</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F73" s="3"/>
       <c r="G73" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>237</v>
+        <v>289</v>
       </c>
       <c r="J73" s="3">
-        <v>44</v>
+        <v>62</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="C74" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="B74" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="C74" s="3" t="s">
-        <v>204</v>
-      </c>
       <c r="D74" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F74" s="3"/>
       <c r="G74" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>178</v>
+        <v>235</v>
       </c>
       <c r="J74" s="3">
-        <v>2</v>
+        <v>45</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>295</v>
+        <v>169</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>204</v>
+        <v>182</v>
       </c>
       <c r="D75" s="3" t="s">
         <v>49</v>
@@ -4393,124 +4430,124 @@
       <c r="E75" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F75" s="3" t="s">
-        <v>297</v>
-      </c>
+      <c r="F75" s="3"/>
       <c r="G75" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>81</v>
+        <v>219</v>
       </c>
       <c r="J75" s="3">
-        <v>37</v>
+        <v>3</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>53</v>
+        <v>294</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>159</v>
+        <v>182</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F76" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>296</v>
+      </c>
       <c r="G76" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>301</v>
+        <v>81</v>
       </c>
       <c r="J76" s="3">
-        <v>87</v>
+        <v>38</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="D77" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F77" s="3"/>
       <c r="G77" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>305</v>
+        <v>142</v>
       </c>
       <c r="J77" s="3">
-        <v>21</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>204</v>
+        <v>164</v>
       </c>
       <c r="D78" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F78" s="3"/>
       <c r="G78" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>137</v>
+        <v>59</v>
       </c>
       <c r="J78" s="3">
-        <v>0</v>
+        <v>43</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="C79" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="B79" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="C79" s="3" t="s">
-        <v>289</v>
-      </c>
       <c r="D79" s="3" t="s">
-        <v>135</v>
+        <v>49</v>
       </c>
       <c r="E79" s="3" t="s">
         <v>38</v>
@@ -4520,54 +4557,54 @@
         <v>23</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>189</v>
+        <v>142</v>
       </c>
       <c r="J79" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="D80" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F80" s="3"/>
       <c r="G80" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="J80" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>314</v>
+        <v>301</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>159</v>
+        <v>182</v>
       </c>
       <c r="D81" s="3" t="s">
         <v>49</v>
@@ -4580,27 +4617,27 @@
         <v>23</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>59</v>
+        <v>122</v>
       </c>
       <c r="J81" s="3">
-        <v>42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>159</v>
+        <v>314</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>49</v>
+        <v>140</v>
       </c>
       <c r="E82" s="3" t="s">
         <v>38</v>
@@ -4610,10 +4647,10 @@
         <v>23</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="J82" s="3">
         <v>0</v>
@@ -4621,76 +4658,76 @@
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="D83" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F83" s="3"/>
       <c r="G83" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>200</v>
+        <v>122</v>
       </c>
       <c r="J83" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>323</v>
+        <v>53</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>240</v>
+        <v>257</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F84" s="3"/>
       <c r="G84" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>137</v>
+        <v>321</v>
       </c>
       <c r="J84" s="3">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>326</v>
+        <v>47</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>159</v>
+        <v>221</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>49</v>
+        <v>222</v>
       </c>
       <c r="E85" s="3" t="s">
         <v>43</v>
@@ -4700,84 +4737,86 @@
         <v>23</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>84</v>
+        <v>128</v>
       </c>
       <c r="J85" s="3">
-        <v>45</v>
+        <v>52</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>53</v>
+        <v>324</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>329</v>
+        <v>228</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>260</v>
+        <v>164</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>135</v>
+        <v>49</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F86" s="3"/>
       <c r="G86" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>331</v>
+        <v>230</v>
       </c>
       <c r="J86" s="3">
-        <v>24</v>
+        <v>69</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>47</v>
+        <v>326</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>216</v>
+        <v>328</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>217</v>
+        <v>140</v>
       </c>
       <c r="E87" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F87" s="3"/>
+      <c r="F87" s="3" t="s">
+        <v>329</v>
+      </c>
       <c r="G87" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J87" s="3">
-        <v>51</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>230</v>
+        <v>332</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>159</v>
+        <v>333</v>
       </c>
       <c r="D88" s="3" t="s">
         <v>49</v>
@@ -4790,30 +4829,30 @@
         <v>23</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>232</v>
+        <v>219</v>
       </c>
       <c r="J88" s="3">
-        <v>68</v>
+        <v>3</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="B89" s="3" t="s">
         <v>336</v>
-      </c>
-      <c r="B89" s="3" t="s">
-        <v>175</v>
       </c>
       <c r="C89" s="3" t="s">
         <v>337</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>49</v>
+        <v>140</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F89" s="3"/>
       <c r="G89" s="3" t="s">
@@ -4823,10 +4862,10 @@
         <v>338</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>178</v>
+        <v>142</v>
       </c>
       <c r="J89" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
@@ -4837,23 +4876,23 @@
         <v>340</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>341</v>
+        <v>243</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>135</v>
+        <v>37</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F90" s="3"/>
       <c r="G90" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="J90" s="3">
         <v>0</v>
@@ -4861,13 +4900,13 @@
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="B91" s="3" t="s">
         <v>343</v>
       </c>
-      <c r="B91" s="3" t="s">
-        <v>344</v>
-      </c>
       <c r="C91" s="3" t="s">
-        <v>204</v>
+        <v>182</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>49</v>
@@ -4876,30 +4915,30 @@
         <v>38</v>
       </c>
       <c r="F91" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H91" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="G91" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H91" s="3" t="s">
-        <v>346</v>
-      </c>
       <c r="I91" s="3" t="s">
-        <v>178</v>
+        <v>219</v>
       </c>
       <c r="J91" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="B92" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="B92" s="3" t="s">
-        <v>348</v>
-      </c>
       <c r="C92" s="3" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="D92" s="3" t="s">
         <v>49</v>
@@ -4912,24 +4951,24 @@
         <v>23</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="I92" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J92" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="B93" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="B93" s="3" t="s">
-        <v>351</v>
-      </c>
       <c r="C93" s="3" t="s">
-        <v>204</v>
+        <v>182</v>
       </c>
       <c r="D93" s="3" t="s">
         <v>49</v>
@@ -4942,122 +4981,124 @@
         <v>23</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="I93" s="3" t="s">
         <v>76</v>
       </c>
       <c r="J93" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="s">
-        <v>353</v>
+        <v>169</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>355</v>
+        <v>182</v>
       </c>
       <c r="D94" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>265</v>
+        <v>38</v>
       </c>
       <c r="F94" s="3"/>
       <c r="G94" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>178</v>
+        <v>122</v>
       </c>
       <c r="J94" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="D95" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E95" s="3" t="s">
         <v>357</v>
-      </c>
-      <c r="B95" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="C95" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="D95" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E95" s="3" t="s">
-        <v>43</v>
       </c>
       <c r="F95" s="3"/>
       <c r="G95" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>137</v>
+        <v>219</v>
       </c>
       <c r="J95" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="B96" s="3" t="s">
         <v>360</v>
       </c>
-      <c r="B96" s="3" t="s">
-        <v>361</v>
-      </c>
       <c r="C96" s="3" t="s">
-        <v>56</v>
+        <v>164</v>
       </c>
       <c r="D96" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F96" s="3"/>
       <c r="G96" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="J96" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B97" s="3" t="s">
         <v>363</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>337</v>
+        <v>238</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>49</v>
+        <v>140</v>
       </c>
       <c r="E97" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F97" s="3"/>
+      <c r="F97" s="3" t="s">
+        <v>329</v>
+      </c>
       <c r="G97" s="3" t="s">
         <v>23</v>
       </c>
@@ -5065,10 +5106,10 @@
         <v>364</v>
       </c>
       <c r="I97" s="3" t="s">
-        <v>200</v>
+        <v>122</v>
       </c>
       <c r="J97" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -5079,7 +5120,7 @@
         <v>366</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>204</v>
+        <v>333</v>
       </c>
       <c r="D98" s="3" t="s">
         <v>49</v>
@@ -5095,7 +5136,7 @@
         <v>367</v>
       </c>
       <c r="I98" s="3" t="s">
-        <v>178</v>
+        <v>202</v>
       </c>
       <c r="J98" s="3">
         <v>2</v>
@@ -5109,10 +5150,10 @@
         <v>369</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>370</v>
+        <v>182</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>135</v>
+        <v>49</v>
       </c>
       <c r="E99" s="3" t="s">
         <v>38</v>
@@ -5122,27 +5163,27 @@
         <v>23</v>
       </c>
       <c r="H99" s="3" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="I99" s="3" t="s">
-        <v>178</v>
+        <v>219</v>
       </c>
       <c r="J99" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>176</v>
+        <v>238</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>49</v>
+        <v>140</v>
       </c>
       <c r="E100" s="3" t="s">
         <v>38</v>
@@ -5152,17 +5193,137 @@
         <v>23</v>
       </c>
       <c r="H100" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="J100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="C101" s="3" t="s">
         <v>374</v>
       </c>
-      <c r="I100" s="3" t="s">
+      <c r="D101" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F101" s="3"/>
+      <c r="G101" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="J101" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="C102" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="D102" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F102" s="3"/>
+      <c r="G102" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H102" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="I102" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="J102" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="D103" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="E103" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F103" s="3"/>
+      <c r="G103" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H103" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="I103" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="J103" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="B104" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="C104" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="D104" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E104" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F104" s="3"/>
+      <c r="G104" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H104" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="I104" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="J100" s="3">
-        <v>20</v>
+      <c r="J104" s="3">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J100"/>
+  <autoFilter ref="A1:J104"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -5263,6 +5424,10 @@
     <hyperlink ref="H98" r:id="rId97"/>
     <hyperlink ref="H99" r:id="rId98"/>
     <hyperlink ref="H100" r:id="rId99"/>
+    <hyperlink ref="H101" r:id="rId100"/>
+    <hyperlink ref="H102" r:id="rId101"/>
+    <hyperlink ref="H103" r:id="rId102"/>
+    <hyperlink ref="H104" r:id="rId103"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5270,8 +5435,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="48" customWidth="1"/>
-    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="1" max="1" width="46" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -5304,13 +5469,13 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>133</v>
+        <v>118</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
@@ -5318,18 +5483,18 @@
         <v>24</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>164</v>
+        <v>180</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>245</v>
+        <v>181</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>204</v>
+        <v>182</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -5337,18 +5502,18 @@
         <v>23</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>246</v>
+        <v>183</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>247</v>
+        <v>203</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>248</v>
+        <v>182</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -5356,18 +5521,18 @@
         <v>23</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>249</v>
+        <v>204</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>164</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>204</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -5375,18 +5540,18 @@
         <v>23</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>251</v>
+        <v>216</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>270</v>
+        <v>247</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>159</v>
+        <v>182</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -5394,18 +5559,18 @@
         <v>23</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>271</v>
+        <v>248</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>306</v>
+        <v>169</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>307</v>
+        <v>265</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>204</v>
+        <v>266</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -5413,18 +5578,18 @@
         <v>23</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>308</v>
+        <v>267</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>317</v>
+        <v>280</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>318</v>
+        <v>281</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>159</v>
+        <v>182</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -5432,18 +5597,18 @@
         <v>23</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>319</v>
+        <v>282</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>323</v>
+        <v>301</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>324</v>
+        <v>310</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>240</v>
+        <v>182</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -5451,18 +5616,18 @@
         <v>23</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>325</v>
+        <v>311</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>339</v>
+        <v>312</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>340</v>
+        <v>313</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>341</v>
+        <v>314</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -5470,18 +5635,18 @@
         <v>23</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>342</v>
+        <v>315</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>357</v>
+        <v>316</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>358</v>
+        <v>317</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -5489,18 +5654,18 @@
         <v>23</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>359</v>
+        <v>318</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>360</v>
+        <v>326</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>361</v>
+        <v>327</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>56</v>
+        <v>328</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
@@ -5508,11 +5673,125 @@
         <v>23</v>
       </c>
       <c r="G12" s="3" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="s">
         <v>362</v>
       </c>
+      <c r="B15" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>380</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G12"/>
+  <autoFilter ref="A1:G18"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -5525,6 +5804,12 @@
     <hyperlink ref="G10" r:id="rId9"/>
     <hyperlink ref="G11" r:id="rId10"/>
     <hyperlink ref="G12" r:id="rId11"/>
+    <hyperlink ref="G13" r:id="rId12"/>
+    <hyperlink ref="G14" r:id="rId13"/>
+    <hyperlink ref="G15" r:id="rId14"/>
+    <hyperlink ref="G16" r:id="rId15"/>
+    <hyperlink ref="G17" r:id="rId16"/>
+    <hyperlink ref="G18" r:id="rId17"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5538,15 +5823,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>375</v>
+        <v>384</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>376</v>
+        <v>385</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B2" s="3">
         <v>22</v>
@@ -5554,7 +5839,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>377</v>
+        <v>386</v>
       </c>
       <c r="B3" s="3">
         <v>20</v>
@@ -5562,31 +5847,31 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>378</v>
+        <v>189</v>
       </c>
       <c r="B4" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="B5" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>126</v>
+        <v>329</v>
       </c>
       <c r="B6" s="3">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>380</v>
+        <v>131</v>
       </c>
       <c r="B7" s="3">
         <v>13</v>
@@ -5594,7 +5879,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="B8" s="3">
         <v>12</v>
@@ -5602,7 +5887,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="B9" s="3">
         <v>11</v>
@@ -5610,7 +5895,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>383</v>
+        <v>390</v>
       </c>
       <c r="B10" s="3">
         <v>11</v>
@@ -5618,7 +5903,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="B11" s="3">
         <v>10</v>
@@ -5626,15 +5911,15 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="B12" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="B13" s="3">
         <v>9</v>
@@ -5642,7 +5927,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="B14" s="3">
         <v>8</v>
@@ -5650,7 +5935,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B15" s="3">
         <v>6</v>
@@ -5658,7 +5943,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>388</v>
+        <v>395</v>
       </c>
       <c r="B16" s="3">
         <v>6</v>
@@ -5671,7 +5956,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="1" max="1" width="34" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5680,7 +5965,7 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>389</v>
+        <v>396</v>
       </c>
     </row>
     <row r="2">
@@ -5717,7 +6002,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>247</v>
+        <v>118</v>
       </c>
       <c r="B6" s="3">
         <v>3</v>
@@ -5725,15 +6010,15 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>48</v>
+        <v>242</v>
       </c>
       <c r="B7" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>118</v>
+        <v>48</v>
       </c>
       <c r="B8" s="3">
         <v>2</v>
@@ -5741,7 +6026,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="B9" s="3">
         <v>2</v>
@@ -5749,7 +6034,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="B10" s="3">
         <v>2</v>
@@ -5757,7 +6042,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>180</v>
+        <v>228</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -5765,7 +6050,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -5773,7 +6058,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>243</v>
+        <v>265</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -5781,23 +6066,23 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>55</v>
+        <v>310</v>
       </c>
       <c r="B14" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>133</v>
+        <v>363</v>
       </c>
       <c r="B15" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>139</v>
+        <v>55</v>
       </c>
       <c r="B16" s="3">
         <v>1</v>
@@ -5811,23 +6096,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>389</v>
+        <v>396</v>
       </c>
     </row>
     <row r="2">
@@ -5877,10 +6162,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>35</v>
+        <v>118</v>
       </c>
       <c r="C5" s="3">
-        <v>7.1</v>
+        <v>9.2</v>
       </c>
       <c r="D5" s="3">
         <v>3</v>
@@ -5891,13 +6176,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="C6" s="3">
-        <v>6.0</v>
+        <v>7.1</v>
       </c>
       <c r="D6" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -5905,10 +6190,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>118</v>
+        <v>48</v>
       </c>
       <c r="C7" s="3">
-        <v>5.3</v>
+        <v>6.0</v>
       </c>
       <c r="D7" s="3">
         <v>2</v>
@@ -5919,7 +6204,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="C8" s="3">
         <v>4.2</v>
@@ -5933,7 +6218,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="C9" s="3">
         <v>3.6</v>
@@ -5961,7 +6246,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="C11" s="3">
         <v>2.6</v>
@@ -5975,13 +6260,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>144</v>
+        <v>185</v>
       </c>
       <c r="C12" s="3">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="D12" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -5989,10 +6274,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>175</v>
+        <v>363</v>
       </c>
       <c r="C13" s="3">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="D13" s="3">
         <v>2</v>
@@ -6003,13 +6288,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>180</v>
+        <v>149</v>
       </c>
       <c r="C14" s="3">
         <v>2.4</v>
       </c>
       <c r="D14" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -6017,7 +6302,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C15" s="3">
         <v>2.4</v>
@@ -6031,7 +6316,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="C16" s="3">
         <v>2.4</v>
@@ -6057,18 +6342,18 @@
         <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>393</v>
+        <v>400</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>265</v>
+        <v>357</v>
       </c>
       <c r="B2" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>12</v>
@@ -6079,10 +6364,10 @@
         <v>38</v>
       </c>
       <c r="B3" s="3">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>394</v>
+        <v>401</v>
       </c>
     </row>
     <row r="4">
@@ -6090,10 +6375,10 @@
         <v>43</v>
       </c>
       <c r="B4" s="3">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>395</v>
+        <v>402</v>
       </c>
     </row>
   </sheetData>
@@ -6112,7 +6397,7 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>392</v>
+        <v>399</v>
       </c>
     </row>
     <row r="2">
@@ -6120,15 +6405,15 @@
         <v>49</v>
       </c>
       <c r="B2" s="3">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="B3" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4">
@@ -6136,20 +6421,20 @@
         <v>37</v>
       </c>
       <c r="B4" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>196</v>
+        <v>175</v>
       </c>
       <c r="B5" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>170</v>
+        <v>198</v>
       </c>
       <c r="B6" s="3">
         <v>2</v>
@@ -6157,7 +6442,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="B7" s="3">
         <v>2</v>
@@ -6172,7 +6457,7 @@
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="37" customWidth="1"/>
+    <col min="3" max="3" width="32" customWidth="1"/>
     <col min="4" max="4" width="43" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
@@ -6184,10 +6469,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>396</v>
+        <v>403</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>26</v>
@@ -6199,10 +6484,10 @@
         <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>21</v>
@@ -6219,31 +6504,31 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>404</v>
+        <v>411</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>305</v>
+        <v>286</v>
       </c>
     </row>
     <row r="3">
@@ -6251,31 +6536,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>405</v>
+        <v>412</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>410</v>
+        <v>417</v>
       </c>
     </row>
     <row r="4">
@@ -6283,28 +6568,28 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>411</v>
+        <v>418</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>412</v>
+        <v>419</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>414</v>
+        <v>421</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>88</v>
@@ -6315,28 +6600,28 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="F5" s="3">
         <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>88</v>
@@ -6347,31 +6632,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>368</v>
+        <v>354</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>419</v>
+        <v>355</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>159</v>
+        <v>356</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>402</v>
+        <v>426</v>
       </c>
       <c r="F6" s="3">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>421</v>
+        <v>358</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>422</v>
+        <v>219</v>
       </c>
     </row>
     <row r="7">
@@ -6379,31 +6664,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>353</v>
+        <v>428</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>354</v>
+        <v>242</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>355</v>
+        <v>276</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>423</v>
+        <v>409</v>
       </c>
       <c r="F7" s="3">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>356</v>
+        <v>430</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>178</v>
+        <v>431</v>
       </c>
     </row>
     <row r="8">
@@ -6411,31 +6696,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>247</v>
+        <v>433</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>280</v>
+        <v>164</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="F8" s="3">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>427</v>
+        <v>435</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>422</v>
+        <v>436</v>
       </c>
     </row>
     <row r="9">
@@ -6443,31 +6728,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>428</v>
+        <v>437</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>429</v>
+        <v>438</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>159</v>
+        <v>192</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>402</v>
+        <v>420</v>
       </c>
       <c r="F9" s="3">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>430</v>
+        <v>439</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I9" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="J9" s="3" t="s">
         <v>431</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>432</v>
       </c>
     </row>
     <row r="10">
@@ -6475,31 +6760,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>433</v>
+        <v>441</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>434</v>
+        <v>442</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>176</v>
+        <v>443</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="F10" s="3">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>435</v>
+        <v>444</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>422</v>
+        <v>88</v>
       </c>
     </row>
     <row r="11">
@@ -6507,31 +6792,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>437</v>
+        <v>446</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>438</v>
+        <v>419</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="F11" s="3">
         <v>70</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>88</v>
+        <v>142</v>
       </c>
     </row>
     <row r="12">
@@ -6539,31 +6824,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="F12" s="3">
         <v>68</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>24</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>446</v>
+        <v>454</v>
       </c>
     </row>
     <row r="13">
@@ -6571,28 +6856,28 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>447</v>
+        <v>455</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>449</v>
+        <v>457</v>
       </c>
       <c r="F13" s="3">
         <v>61</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>450</v>
+        <v>458</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="J13" s="3" t="s">
         <v>81</v>
@@ -6603,31 +6888,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>175</v>
+        <v>332</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="F14" s="3">
         <v>60</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>178</v>
+        <v>219</v>
       </c>
     </row>
     <row r="15">
@@ -6635,31 +6920,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>454</v>
+        <v>281</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>204</v>
+        <v>182</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="F15" s="3">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>455</v>
+        <v>462</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>456</v>
+        <v>463</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>422</v>
+        <v>142</v>
       </c>
     </row>
     <row r="16">
@@ -6667,31 +6952,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>372</v>
+        <v>464</v>
       </c>
       <c r="C16" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E16" s="3" t="s">
         <v>457</v>
       </c>
-      <c r="D16" s="3" t="s">
-        <v>458</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>402</v>
-      </c>
       <c r="F16" s="3">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>459</v>
+        <v>465</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>275</v>
+        <v>467</v>
       </c>
     </row>
     <row r="17">
@@ -6699,31 +6984,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>461</v>
+        <v>468</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>434</v>
+        <v>469</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>176</v>
+        <v>238</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>449</v>
+        <v>426</v>
       </c>
       <c r="F17" s="3">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>462</v>
+        <v>470</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>464</v>
+        <v>59</v>
       </c>
     </row>
     <row r="18">
@@ -6731,31 +7016,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>465</v>
+        <v>472</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>466</v>
+        <v>473</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>240</v>
+        <v>164</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="F18" s="3">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>467</v>
+        <v>474</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>468</v>
+        <v>475</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>59</v>
+        <v>219</v>
       </c>
     </row>
     <row r="19">
@@ -6763,31 +7048,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>372</v>
+        <v>476</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>169</v>
+        <v>257</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>402</v>
+        <v>420</v>
       </c>
       <c r="F19" s="3">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>470</v>
+        <v>478</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>471</v>
+        <v>479</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>178</v>
+        <v>88</v>
       </c>
     </row>
     <row r="20">
@@ -6795,31 +7080,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>472</v>
+        <v>480</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>473</v>
+        <v>481</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="F20" s="3">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>474</v>
+        <v>482</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>475</v>
+        <v>483</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>178</v>
+        <v>484</v>
       </c>
     </row>
     <row r="21">
@@ -6827,31 +7112,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>476</v>
+        <v>485</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>259</v>
+        <v>486</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>260</v>
+        <v>487</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>477</v>
+        <v>457</v>
       </c>
       <c r="F21" s="3">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>478</v>
+        <v>488</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>479</v>
+        <v>489</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>41</v>
+        <v>142</v>
       </c>
     </row>
   </sheetData>

--- a/reports/devops-jobs-israel-2026-W41.xlsx
+++ b/reports/devops-jobs-israel-2026-W41.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="507">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="505">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-08T13:17:20</t>
+    <t xml:space="preserve">2026-10-09T13:05:08</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -522,78 +522,81 @@
     <t xml:space="preserve">2026-10-04</t>
   </si>
   <si>
-    <t xml:space="preserve">Aidoc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-aidoc-4465646027</t>
+    <t xml:space="preserve">Senior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eitan Medical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-eitan-medical-4461889332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Platform Engineer- CTI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dream</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-platform-engineer-cti-at-dream-4465727084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer (25769)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yael Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-25769-at-yael-group-4474444402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer - Data Platform (Cortex)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palo Alto Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-data-platform-cortex-at-palo-alto-networks-4455871961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Principal DevOps Engineer (Cortex Agentix Endpoint Security)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-devops-engineer-cortex-agentix-endpoint-security-at-palo-alto-networks-4418753719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer (37047)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-37047-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4477184463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-09</t>
   </si>
   <si>
     <t xml:space="preserve">DevOps Engineer</t>
   </si>
   <si>
-    <t xml:space="preserve">Echo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-echo-4459855925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eitan Medical</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-eitan-medical-4461889332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Platform Engineer- CTI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dream</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-platform-engineer-cti-at-dream-4465727084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (25769)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yael Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-25769-at-yael-group-4474444402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer - Data Platform (Cortex)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palo Alto Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-data-platform-cortex-at-palo-alto-networks-4455871961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Principal DevOps Engineer (Cortex Agentix Endpoint Security)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-devops-engineer-cortex-agentix-endpoint-security-at-palo-alto-networks-4418753719</t>
-  </si>
-  <si>
     <t xml:space="preserve">Checkmarx</t>
   </si>
   <si>
@@ -606,10 +609,109 @@
     <t xml:space="preserve">2026-07-14</t>
   </si>
   <si>
+    <t xml:space="preserve">Gini-Apps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gini-apps-4476189127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stealth Startup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-stealth-startup-4475760813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buildots</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-buildots-4473477683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comblack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-comblack-4477185811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akeyless Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-akeyless-security-4457183616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blink</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-blink-4473214725</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sr. DevOps Engineer</t>
   </si>
   <si>
-    <t xml:space="preserve">Harmonic</t>
+    <t xml:space="preserve">Zscaler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-devops-engineer-at-zscaler-4465317702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bitsight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-bitsight-4476962715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fetcherr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fetcherr-4429844723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cellebrite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-cellebrite-4469980397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fig Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fig-security-4475988067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personetics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-personetics-4428829912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moon Active</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-moon-active-4447023421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Polytex Technologies</t>
   </si>
   <si>
     <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
@@ -618,105 +720,6 @@
     <t xml:space="preserve">Haifa</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-devops-engineer-at-harmonic-4360460066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gini-Apps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gini-apps-4476189127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stealth Startup</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-stealth-startup-4475760813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connecteam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4428832411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Buildots</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-buildots-4473477683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Akeyless Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-akeyless-security-4457183616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blink</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-blink-4473214725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zscaler</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-devops-engineer-at-zscaler-4465317702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bitsight</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-bitsight-4476962715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fetcherr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fetcherr-4429844723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cellebrite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-cellebrite-4469980397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Personetics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-personetics-4428829912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moon Active</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-moon-active-4447023421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Polytex Technologies</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-polytex-technologies-4473474269</t>
   </si>
   <si>
@@ -735,9 +738,6 @@
     <t xml:space="preserve">Extreme</t>
   </si>
   <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-devops-engineer-at-extreme-4475385097</t>
   </si>
   <si>
@@ -768,6 +768,12 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cybersixgill-a-bitsight-company-4476927366</t>
   </si>
   <si>
+    <t xml:space="preserve">Commit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-commit-4477482711</t>
+  </si>
+  <si>
     <t xml:space="preserve">DevOps - AI Factory</t>
   </si>
   <si>
@@ -789,139 +795,175 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-and-automation-engineer-at-dialog-4473641075</t>
   </si>
   <si>
-    <t xml:space="preserve">Jobgether</t>
+    <t xml:space="preserve">SRE / DevOps Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">april</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-devops-lead-at-april-4416179005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-elbit-systems-israel-4394529806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQLink Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yehud Monosson, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sqlink-group-4476701773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tesnet Group Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-tesnet-group-ltd-4477160595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DriveNets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-devops-engineer-at-drivenets-4465793281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staff Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grubhub</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/staff-site-reliability-engineer-at-grubhub-4473025762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineering - Storage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineering-storage-at-nvidia-4457190574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-nvidia-4458308805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Integrator SRE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compie Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-integrator-sre-at-compie-technologies-4477142119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineer III, Platform Engineering and Infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-iii-platform-engineering-and-infrastructure-at-google-4465561954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Platform &amp; SRE Group Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-sre-group-leader-at-extreme-4450267100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SciPlay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-sciplay-4391151881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medulla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-medulla-4475546635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure Engineer (Kubernetes &amp; Node.js)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oriient</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-kubernetes-node-js-at-oriient-4461069125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Application Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/application-infrastructure-engineer-at-comblack-4477403031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platform Engineering Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corsa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineering-team-lead-at-corsa-4476174341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fiverr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fiverr-4458388230</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud DevOps Technical Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OnTarget Communications</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-devops-technical-manager-at-ontarget-communications-4475801640</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TeraCyte Analytics</t>
   </si>
   <si>
     <t xml:space="preserve">Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-jobgether-4472898137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRE / DevOps Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">april</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-devops-lead-at-april-4416179005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quantum Machines</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-quantum-machines-4474990509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQLink Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yehud Monosson, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sqlink-group-4476701773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Software Engineer, DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aiven</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-software-engineer-devops-at-aiven-4426867332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Staff Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grubhub</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/staff-site-reliability-engineer-at-grubhub-4473025762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineering - Storage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineering-storage-at-nvidia-4457190574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-nvidia-4457410161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Integrator SRE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Compie Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-integrator-sre-at-compie-technologies-4477142119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineer III, Platform Engineering and Infrastructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-iii-platform-engineering-and-infrastructure-at-google-4465561954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Platform &amp; SRE Group Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-sre-group-leader-at-extreme-4450267100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SciPlay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-sciplay-4391151881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medulla</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-medulla-4475546635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure Engineer (Kubernetes &amp; Node.js)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oriient</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-kubernetes-node-js-at-oriient-4461069125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Platform Engineering Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corsa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineering-team-lead-at-corsa-4476174341</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-infrastructure-engineer-at-teracyte-analytics-4475993753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MLOps &amp; Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI/MLOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/mlops-cloud-engineer-at-teracyte-analytics-4476201360</t>
   </si>
   <si>
     <t xml:space="preserve">Cloud Engineer</t>
@@ -963,9 +1005,6 @@
     <t xml:space="preserve">BlackEdge Labs</t>
   </si>
   <si>
-    <t xml:space="preserve">Savyon, Center District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/backend-devops-engineer-%E2%80%93-ai-llm-at-blackedge-labs-4477122203</t>
   </si>
   <si>
@@ -1059,30 +1098,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-finops-oriented-at-cloudteam-ai-4473603103</t>
   </si>
   <si>
-    <t xml:space="preserve">IT DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DriveNets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-devops-engineer-at-drivenets-4465793281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cato Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-system-engineer-at-cato-networks-4463471007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tesnet Group Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-tesnet-group-ltd-4477160595</t>
-  </si>
-  <si>
     <t xml:space="preserve">Junior System &amp; Infrastructure Engineer</t>
   </si>
   <si>
@@ -1110,18 +1125,12 @@
     <t xml:space="preserve">GCP &amp; System Administrator (36759)</t>
   </si>
   <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/gcp-system-administrator-36759-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4477174630</t>
   </si>
   <si>
     <t xml:space="preserve">Infrastructure Engineer</t>
   </si>
   <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-elbit-systems-israel-4474036853</t>
   </si>
   <si>
@@ -1224,10 +1233,10 @@
     <t xml:space="preserve">Percent</t>
   </si>
   <si>
-    <t xml:space="preserve">52.4%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.6%</t>
+    <t xml:space="preserve">55.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.8%</t>
   </si>
   <si>
     <t xml:space="preserve">Role</t>
@@ -1317,6 +1326,18 @@
     <t xml:space="preserve">2026-09-30</t>
   </si>
   <si>
+    <t xml:space="preserve">Cloud Monitoring Engineer (Student Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upwind Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-monitoring-engineer-student-position-at-upwind-security-4476759903</t>
+  </si>
+  <si>
     <t xml:space="preserve">Junior Technical Operations Engineer</t>
   </si>
   <si>
@@ -1335,9 +1356,6 @@
     <t xml:space="preserve">Security Analyst (Student Position)</t>
   </si>
   <si>
-    <t xml:space="preserve">Upwind Security</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, Networking</t>
   </si>
   <si>
@@ -1404,6 +1422,15 @@
     <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Terraform/IaC, Networking, Automation</t>
   </si>
   <si>
+    <t xml:space="preserve">Junior CAD Engineer, University Graduate, Google Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cad-engineer-university-graduate-google-cloud-at-google-4475452638</t>
+  </si>
+  <si>
     <t xml:space="preserve">Network Operations Center</t>
   </si>
   <si>
@@ -1413,18 +1440,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/network-operations-center-at-compie-technologies-4476168349</t>
   </si>
   <si>
-    <t xml:space="preserve">Technical Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4460871956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-30</t>
-  </si>
-  <si>
     <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
   </si>
   <si>
@@ -1437,6 +1452,15 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
   </si>
   <si>
+    <t xml:space="preserve">Software Engineer Intern</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Docker, Kubernetes, CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/8229871?gh_jid=8229871</t>
+  </si>
+  <si>
     <t xml:space="preserve">Data Operations Student - Nights &amp; Weekend shifts</t>
   </si>
   <si>
@@ -1461,36 +1485,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-intern-at-microsoft-4451071541</t>
   </si>
   <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raft Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Service Desk Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appsflyer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8874236002?gh_jid=8874236002</t>
-  </si>
-  <si>
     <t xml:space="preserve">Junior SysAdmin / Linux</t>
   </si>
   <si>
@@ -1500,10 +1494,10 @@
     <t xml:space="preserve">Monitoring</t>
   </si>
   <si>
+    <t xml:space="preserve">Cloud (any)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any)</t>
   </si>
   <si>
     <t xml:space="preserve">Automation</t>
@@ -1664,7 +1658,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="7">
@@ -1672,7 +1666,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>17</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -1680,7 +1674,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>45</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9">
@@ -1688,7 +1682,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>877</v>
+        <v>884</v>
       </c>
     </row>
     <row r="10">
@@ -1760,7 +1754,7 @@
         <v>23</v>
       </c>
       <c r="B19" s="3">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="20">
@@ -1787,44 +1781,44 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="B2" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="B3" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>457</v>
+        <v>463</v>
       </c>
       <c r="B4" s="3">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="B5" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="B6" s="3">
         <v>1</v>
@@ -1832,7 +1826,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="B7" s="3">
         <v>1</v>
@@ -1851,42 +1845,42 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="B2" s="3">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="B3" s="3">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="B4" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>391</v>
+        <v>493</v>
       </c>
       <c r="B5" s="3">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6">
@@ -1894,20 +1888,20 @@
         <v>395</v>
       </c>
       <c r="B6" s="3">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>495</v>
+        <v>394</v>
       </c>
       <c r="B7" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="B8" s="3">
         <v>16</v>
@@ -1915,18 +1909,18 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="B9" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="B10" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11">
@@ -1934,44 +1928,44 @@
         <v>296</v>
       </c>
       <c r="B11" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="B12" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B13" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="B14" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>329</v>
+        <v>342</v>
       </c>
       <c r="B15" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="B16" s="3">
         <v>5</v>
@@ -1999,13 +1993,13 @@
         <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>498</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>499</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>500</v>
       </c>
     </row>
     <row r="2">
@@ -2016,10 +2010,10 @@
         <v>30</v>
       </c>
       <c r="C2" s="3">
-        <v>12.0</v>
+        <v>12.5</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -2028,88 +2022,88 @@
         <v>23</v>
       </c>
       <c r="B3" s="3">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C3" s="3">
-        <v>36.0</v>
+        <v>35.8</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>8.4</v>
+        <v>9.2</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>30.9</v>
+        <v>33.5</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>14.5</v>
+        <v>16.3</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>18.7</v>
+        <v>23.1</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -2193,7 +2187,7 @@
         <v>41</v>
       </c>
       <c r="J2" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
@@ -2225,7 +2219,7 @@
         <v>41</v>
       </c>
       <c r="J3" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
@@ -2257,7 +2251,7 @@
         <v>41</v>
       </c>
       <c r="J4" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
@@ -2289,7 +2283,7 @@
         <v>52</v>
       </c>
       <c r="J5" s="3">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6">
@@ -2321,7 +2315,7 @@
         <v>52</v>
       </c>
       <c r="J6" s="3">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7">
@@ -2353,7 +2347,7 @@
         <v>59</v>
       </c>
       <c r="J7" s="3">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8">
@@ -2385,7 +2379,7 @@
         <v>65</v>
       </c>
       <c r="J8" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9">
@@ -2417,7 +2411,7 @@
         <v>52</v>
       </c>
       <c r="J9" s="3">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10">
@@ -2449,7 +2443,7 @@
         <v>72</v>
       </c>
       <c r="J10" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11">
@@ -2481,7 +2475,7 @@
         <v>76</v>
       </c>
       <c r="J11" s="3">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12">
@@ -2513,7 +2507,7 @@
         <v>81</v>
       </c>
       <c r="J12" s="3">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13">
@@ -2545,7 +2539,7 @@
         <v>84</v>
       </c>
       <c r="J13" s="3">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14">
@@ -2577,7 +2571,7 @@
         <v>88</v>
       </c>
       <c r="J14" s="3">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15">
@@ -2609,7 +2603,7 @@
         <v>92</v>
       </c>
       <c r="J15" s="3">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="16">
@@ -2641,7 +2635,7 @@
         <v>96</v>
       </c>
       <c r="J16" s="3">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17">
@@ -2673,7 +2667,7 @@
         <v>102</v>
       </c>
       <c r="J17" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18">
@@ -2705,7 +2699,7 @@
         <v>106</v>
       </c>
       <c r="J18" s="3">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="19">
@@ -2737,7 +2731,7 @@
         <v>96</v>
       </c>
       <c r="J19" s="3">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="20">
@@ -2769,7 +2763,7 @@
         <v>65</v>
       </c>
       <c r="J20" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21">
@@ -2801,7 +2795,7 @@
         <v>116</v>
       </c>
       <c r="J21" s="3">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="22">
@@ -2833,7 +2827,7 @@
         <v>122</v>
       </c>
       <c r="J22" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -2865,7 +2859,7 @@
         <v>92</v>
       </c>
       <c r="J23" s="3">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="24">
@@ -2897,7 +2891,7 @@
         <v>128</v>
       </c>
       <c r="J24" s="3">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="25">
@@ -2929,7 +2923,7 @@
         <v>133</v>
       </c>
       <c r="J25" s="3">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="26">
@@ -2961,7 +2955,7 @@
         <v>136</v>
       </c>
       <c r="J26" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27">
@@ -2991,7 +2985,7 @@
         <v>142</v>
       </c>
       <c r="J27" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -3023,7 +3017,7 @@
         <v>147</v>
       </c>
       <c r="J28" s="3">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="29">
@@ -3055,7 +3049,7 @@
         <v>52</v>
       </c>
       <c r="J29" s="3">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="30">
@@ -3087,7 +3081,7 @@
         <v>81</v>
       </c>
       <c r="J30" s="3">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="31">
@@ -3119,7 +3113,7 @@
         <v>162</v>
       </c>
       <c r="J31" s="3">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="32">
@@ -3149,21 +3143,21 @@
         <v>166</v>
       </c>
       <c r="J32" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>47</v>
+        <v>167</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>49</v>
+        <v>170</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>43</v>
@@ -3173,21 +3167,21 @@
         <v>23</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>76</v>
+        <v>162</v>
       </c>
       <c r="J33" s="3">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>164</v>
@@ -3196,58 +3190,58 @@
         <v>49</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>116</v>
+        <v>96</v>
       </c>
       <c r="J34" s="3">
-        <v>41</v>
+        <v>25</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>175</v>
+        <v>49</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F35" s="3"/>
       <c r="G35" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>162</v>
+        <v>122</v>
       </c>
       <c r="J35" s="3">
-        <v>31</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>164</v>
@@ -3263,116 +3257,116 @@
         <v>23</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>96</v>
+        <v>182</v>
       </c>
       <c r="J36" s="3">
-        <v>24</v>
+        <v>45</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="B37" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="B37" s="3" t="s">
-        <v>181</v>
-      </c>
       <c r="C37" s="3" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F37" s="3"/>
+        <v>43</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>184</v>
+      </c>
       <c r="G37" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>122</v>
+        <v>92</v>
       </c>
       <c r="J37" s="3">
-        <v>0</v>
+        <v>43</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>164</v>
+        <v>188</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>49</v>
+        <v>140</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="J38" s="3">
-        <v>44</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>164</v>
+        <v>193</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>189</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="F39" s="3"/>
       <c r="G39" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>92</v>
+        <v>195</v>
       </c>
       <c r="J39" s="3">
-        <v>42</v>
+        <v>87</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>169</v>
+        <v>191</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>192</v>
+        <v>164</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>49</v>
@@ -3385,54 +3379,54 @@
         <v>23</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="J40" s="3">
-        <v>86</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>197</v>
+        <v>177</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>198</v>
+        <v>49</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>59</v>
+        <v>122</v>
       </c>
       <c r="J41" s="3">
-        <v>43</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>169</v>
+        <v>191</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>49</v>
@@ -3445,24 +3439,24 @@
         <v>23</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>202</v>
+        <v>166</v>
       </c>
       <c r="J42" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>169</v>
+        <v>191</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>203</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>49</v>
@@ -3478,7 +3472,7 @@
         <v>204</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>122</v>
+        <v>190</v>
       </c>
       <c r="J43" s="3">
         <v>0</v>
@@ -3486,19 +3480,19 @@
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>169</v>
+        <v>47</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>205</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>164</v>
+        <v>193</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3" t="s">
@@ -3508,21 +3502,21 @@
         <v>206</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>96</v>
+        <v>182</v>
       </c>
       <c r="J44" s="3">
-        <v>24</v>
+        <v>45</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>169</v>
+        <v>191</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>207</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>182</v>
+        <v>56</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>49</v>
@@ -3541,18 +3535,18 @@
         <v>166</v>
       </c>
       <c r="J45" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>47</v>
+        <v>209</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>192</v>
+        <v>164</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>49</v>
@@ -3565,57 +3559,57 @@
         <v>23</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>187</v>
+        <v>76</v>
       </c>
       <c r="J46" s="3">
-        <v>44</v>
+        <v>29</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>169</v>
+        <v>47</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>56</v>
+        <v>164</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>166</v>
+        <v>122</v>
       </c>
       <c r="J47" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>195</v>
+        <v>47</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>49</v>
+        <v>170</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>43</v>
@@ -3625,13 +3619,13 @@
         <v>23</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>76</v>
+        <v>216</v>
       </c>
       <c r="J48" s="3">
-        <v>28</v>
+        <v>4</v>
       </c>
     </row>
     <row r="49">
@@ -3639,13 +3633,13 @@
         <v>47</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>164</v>
+        <v>218</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>49</v>
+        <v>219</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>43</v>
@@ -3655,13 +3649,13 @@
         <v>23</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>122</v>
+        <v>221</v>
       </c>
       <c r="J49" s="3">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="50">
@@ -3669,13 +3663,13 @@
         <v>47</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>175</v>
+        <v>49</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>43</v>
@@ -3685,54 +3679,54 @@
         <v>23</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>219</v>
+        <v>190</v>
       </c>
       <c r="J50" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>47</v>
+        <v>191</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>222</v>
+        <v>49</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F51" s="3"/>
       <c r="G51" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>224</v>
+        <v>96</v>
       </c>
       <c r="J51" s="3">
-        <v>16</v>
+        <v>25</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>169</v>
+        <v>191</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>226</v>
+        <v>164</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>49</v>
@@ -3745,27 +3739,27 @@
         <v>23</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>96</v>
+        <v>229</v>
       </c>
       <c r="J52" s="3">
-        <v>24</v>
+        <v>70</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>169</v>
+        <v>191</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>164</v>
+        <v>231</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>49</v>
+        <v>232</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>38</v>
@@ -3775,87 +3769,87 @@
         <v>23</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>230</v>
+        <v>166</v>
       </c>
       <c r="J53" s="3">
-        <v>69</v>
+        <v>5</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>169</v>
+        <v>47</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>197</v>
+        <v>164</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>198</v>
+        <v>49</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F54" s="3"/>
       <c r="G54" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>166</v>
+        <v>236</v>
       </c>
       <c r="J54" s="3">
-        <v>4</v>
+        <v>46</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>47</v>
+        <v>237</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>164</v>
+        <v>188</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>49</v>
+        <v>140</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>235</v>
+        <v>166</v>
       </c>
       <c r="J55" s="3">
-        <v>45</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>236</v>
+        <v>191</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>238</v>
+        <v>177</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>140</v>
+        <v>49</v>
       </c>
       <c r="E56" s="3" t="s">
         <v>38</v>
@@ -3865,27 +3859,27 @@
         <v>23</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>166</v>
+        <v>142</v>
       </c>
       <c r="J56" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>169</v>
+        <v>191</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>182</v>
+        <v>243</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>38</v>
@@ -3895,27 +3889,27 @@
         <v>23</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="I57" s="3" t="s">
         <v>142</v>
       </c>
       <c r="J57" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>169</v>
+        <v>191</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>243</v>
+        <v>177</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>38</v>
@@ -3925,24 +3919,24 @@
         <v>23</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="I58" s="3" t="s">
         <v>142</v>
       </c>
       <c r="J58" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>169</v>
+        <v>191</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>49</v>
@@ -3955,10 +3949,10 @@
         <v>23</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>142</v>
+        <v>122</v>
       </c>
       <c r="J59" s="3">
         <v>1</v>
@@ -3966,16 +3960,16 @@
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>169</v>
+        <v>191</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>182</v>
+        <v>218</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>49</v>
+        <v>219</v>
       </c>
       <c r="E60" s="3" t="s">
         <v>38</v>
@@ -3985,10 +3979,10 @@
         <v>23</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>122</v>
+        <v>190</v>
       </c>
       <c r="J60" s="3">
         <v>0</v>
@@ -3996,13 +3990,13 @@
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>49</v>
@@ -4015,24 +4009,24 @@
         <v>23</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="J61" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>238</v>
+        <v>188</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>140</v>
@@ -4045,27 +4039,27 @@
         <v>23</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="J62" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>47</v>
+        <v>258</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>257</v>
+        <v>164</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>140</v>
+        <v>49</v>
       </c>
       <c r="E63" s="3" t="s">
         <v>43</v>
@@ -4075,57 +4069,57 @@
         <v>23</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>259</v>
+        <v>65</v>
       </c>
       <c r="J63" s="3">
-        <v>6</v>
+        <v>24</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>260</v>
+        <v>191</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>261</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>164</v>
+        <v>262</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>49</v>
+        <v>232</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F64" s="3"/>
       <c r="G64" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>65</v>
+        <v>136</v>
       </c>
       <c r="J64" s="3">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>169</v>
+        <v>191</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>164</v>
+        <v>265</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>49</v>
+        <v>140</v>
       </c>
       <c r="E65" s="3" t="s">
         <v>38</v>
@@ -4135,10 +4129,10 @@
         <v>23</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>142</v>
+        <v>122</v>
       </c>
       <c r="J65" s="3">
         <v>1</v>
@@ -4146,16 +4140,16 @@
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>169</v>
+        <v>191</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>266</v>
+        <v>177</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>140</v>
+        <v>49</v>
       </c>
       <c r="E66" s="3" t="s">
         <v>38</v>
@@ -4165,30 +4159,30 @@
         <v>23</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I66" s="3" t="s">
         <v>122</v>
       </c>
       <c r="J66" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>270</v>
+        <v>164</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>140</v>
+        <v>49</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F67" s="3"/>
       <c r="G67" s="3" t="s">
@@ -4198,10 +4192,10 @@
         <v>271</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>166</v>
+        <v>65</v>
       </c>
       <c r="J67" s="3">
-        <v>4</v>
+        <v>24</v>
       </c>
     </row>
     <row r="68">
@@ -4231,7 +4225,7 @@
         <v>41</v>
       </c>
       <c r="J68" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="69">
@@ -4258,10 +4252,10 @@
         <v>277</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="J69" s="3">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="70">
@@ -4288,10 +4282,10 @@
         <v>279</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>187</v>
+        <v>92</v>
       </c>
       <c r="J70" s="3">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="71">
@@ -4302,7 +4296,7 @@
         <v>281</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="D71" s="3" t="s">
         <v>49</v>
@@ -4321,7 +4315,7 @@
         <v>122</v>
       </c>
       <c r="J71" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -4332,7 +4326,7 @@
         <v>284</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>49</v>
@@ -4351,7 +4345,7 @@
         <v>286</v>
       </c>
       <c r="J72" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="73">
@@ -4359,10 +4353,10 @@
         <v>287</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>238</v>
+        <v>188</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>140</v>
@@ -4381,7 +4375,7 @@
         <v>289</v>
       </c>
       <c r="J73" s="3">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="74">
@@ -4408,21 +4402,21 @@
         <v>291</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="J74" s="3">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>169</v>
+        <v>191</v>
       </c>
       <c r="B75" s="3" t="s">
         <v>292</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="D75" s="3" t="s">
         <v>49</v>
@@ -4438,10 +4432,10 @@
         <v>293</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="J75" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="76">
@@ -4452,7 +4446,7 @@
         <v>295</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>49</v>
@@ -4473,7 +4467,7 @@
         <v>81</v>
       </c>
       <c r="J76" s="3">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="77">
@@ -4481,67 +4475,67 @@
         <v>298</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>299</v>
+        <v>203</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="D77" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F77" s="3"/>
       <c r="G77" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>142</v>
+        <v>190</v>
       </c>
       <c r="J77" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="B78" s="3" t="s">
         <v>301</v>
       </c>
-      <c r="B78" s="3" t="s">
-        <v>302</v>
-      </c>
       <c r="C78" s="3" t="s">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="D78" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F78" s="3"/>
       <c r="G78" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>59</v>
+        <v>142</v>
       </c>
       <c r="J78" s="3">
-        <v>43</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>304</v>
+        <v>47</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C79" s="3" t="s">
         <v>164</v>
@@ -4550,31 +4544,31 @@
         <v>49</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F79" s="3"/>
       <c r="G79" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>142</v>
+        <v>92</v>
       </c>
       <c r="J79" s="3">
-        <v>1</v>
+        <v>43</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>192</v>
+        <v>164</v>
       </c>
       <c r="D80" s="3" t="s">
         <v>49</v>
@@ -4587,27 +4581,27 @@
         <v>23</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="J80" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="B81" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="C81" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="C81" s="3" t="s">
-        <v>182</v>
-      </c>
       <c r="D81" s="3" t="s">
-        <v>49</v>
+        <v>140</v>
       </c>
       <c r="E81" s="3" t="s">
         <v>38</v>
@@ -4620,7 +4614,7 @@
         <v>311</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>122</v>
+        <v>190</v>
       </c>
       <c r="J81" s="3">
         <v>0</v>
@@ -4631,10 +4625,10 @@
         <v>312</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="D82" s="3" t="s">
         <v>140</v>
@@ -4642,15 +4636,17 @@
       <c r="E82" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F82" s="3"/>
+      <c r="F82" s="3" t="s">
+        <v>313</v>
+      </c>
       <c r="G82" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>122</v>
+        <v>190</v>
       </c>
       <c r="J82" s="3">
         <v>0</v>
@@ -4658,10 +4654,10 @@
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="B83" s="3" t="s">
         <v>316</v>
-      </c>
-      <c r="B83" s="3" t="s">
-        <v>317</v>
       </c>
       <c r="C83" s="3" t="s">
         <v>164</v>
@@ -4670,37 +4666,37 @@
         <v>49</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F83" s="3"/>
       <c r="G83" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>122</v>
+        <v>59</v>
       </c>
       <c r="J83" s="3">
-        <v>0</v>
+        <v>44</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>53</v>
+        <v>318</v>
       </c>
       <c r="B84" s="3" t="s">
         <v>319</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>257</v>
+        <v>164</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>140</v>
+        <v>49</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F84" s="3"/>
       <c r="G84" s="3" t="s">
@@ -4710,27 +4706,27 @@
         <v>320</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>321</v>
+        <v>142</v>
       </c>
       <c r="J84" s="3">
-        <v>25</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>47</v>
+        <v>321</v>
       </c>
       <c r="B85" s="3" t="s">
         <v>322</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>221</v>
+        <v>193</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>222</v>
+        <v>49</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F85" s="3"/>
       <c r="G85" s="3" t="s">
@@ -4740,21 +4736,21 @@
         <v>323</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>128</v>
+        <v>198</v>
       </c>
       <c r="J85" s="3">
-        <v>52</v>
+        <v>3</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="B86" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="B86" s="3" t="s">
-        <v>228</v>
-      </c>
       <c r="C86" s="3" t="s">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="D86" s="3" t="s">
         <v>49</v>
@@ -4770,10 +4766,10 @@
         <v>325</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>230</v>
+        <v>122</v>
       </c>
       <c r="J86" s="3">
-        <v>69</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
@@ -4784,69 +4780,67 @@
         <v>327</v>
       </c>
       <c r="C87" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="D87" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E87" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F87" s="3"/>
+      <c r="G87" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H87" s="3" t="s">
         <v>328</v>
-      </c>
-      <c r="D87" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="E87" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F87" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="G87" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H87" s="3" t="s">
-        <v>330</v>
       </c>
       <c r="I87" s="3" t="s">
         <v>122</v>
       </c>
       <c r="J87" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>333</v>
+        <v>164</v>
       </c>
       <c r="D88" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F88" s="3"/>
       <c r="G88" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>219</v>
+        <v>122</v>
       </c>
       <c r="J88" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>335</v>
+        <v>53</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>337</v>
+        <v>310</v>
       </c>
       <c r="D89" s="3" t="s">
         <v>140</v>
@@ -4859,54 +4853,54 @@
         <v>23</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>142</v>
+        <v>334</v>
       </c>
       <c r="J89" s="3">
-        <v>1</v>
+        <v>26</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>339</v>
+        <v>47</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>243</v>
+        <v>218</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>37</v>
+        <v>219</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F90" s="3"/>
       <c r="G90" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="J90" s="3">
-        <v>0</v>
+        <v>53</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>343</v>
+        <v>227</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>49</v>
@@ -4914,61 +4908,61 @@
       <c r="E91" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F91" s="3" t="s">
-        <v>344</v>
-      </c>
+      <c r="F91" s="3"/>
       <c r="G91" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="J91" s="3">
-        <v>3</v>
+        <v>70</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>164</v>
+        <v>341</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>49</v>
+        <v>140</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F92" s="3"/>
+        <v>43</v>
+      </c>
+      <c r="F92" s="3" t="s">
+        <v>342</v>
+      </c>
       <c r="G92" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>65</v>
+        <v>122</v>
       </c>
       <c r="J92" s="3">
-        <v>23</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>182</v>
+        <v>346</v>
       </c>
       <c r="D93" s="3" t="s">
         <v>49</v>
@@ -4981,162 +4975,162 @@
         <v>23</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>76</v>
+        <v>216</v>
       </c>
       <c r="J93" s="3">
-        <v>28</v>
+        <v>4</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="s">
-        <v>169</v>
+        <v>348</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>182</v>
+        <v>350</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>49</v>
+        <v>140</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F94" s="3"/>
       <c r="G94" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>122</v>
+        <v>142</v>
       </c>
       <c r="J94" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>356</v>
+        <v>243</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>357</v>
+        <v>38</v>
       </c>
       <c r="F95" s="3"/>
       <c r="G95" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>219</v>
+        <v>122</v>
       </c>
       <c r="J95" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="D96" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F96" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>357</v>
+      </c>
       <c r="G96" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>142</v>
+        <v>216</v>
       </c>
       <c r="J96" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="D97" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E97" s="3" t="s">
         <v>362</v>
       </c>
-      <c r="B97" s="3" t="s">
+      <c r="F97" s="3"/>
+      <c r="G97" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H97" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="C97" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="D97" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="E97" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F97" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="G97" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H97" s="3" t="s">
-        <v>364</v>
-      </c>
       <c r="I97" s="3" t="s">
-        <v>122</v>
+        <v>216</v>
       </c>
       <c r="J97" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="B98" s="3" t="s">
         <v>365</v>
       </c>
-      <c r="B98" s="3" t="s">
-        <v>366</v>
-      </c>
       <c r="C98" s="3" t="s">
-        <v>333</v>
+        <v>164</v>
       </c>
       <c r="D98" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F98" s="3"/>
       <c r="G98" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I98" s="3" t="s">
-        <v>202</v>
+        <v>142</v>
       </c>
       <c r="J98" s="3">
         <v>2</v>
@@ -5144,46 +5138,48 @@
     </row>
     <row r="99">
       <c r="A99" s="3" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>369</v>
+        <v>187</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>49</v>
+        <v>140</v>
       </c>
       <c r="E99" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F99" s="3"/>
+      <c r="F99" s="3" t="s">
+        <v>342</v>
+      </c>
       <c r="G99" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H99" s="3" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="I99" s="3" t="s">
-        <v>219</v>
+        <v>122</v>
       </c>
       <c r="J99" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>363</v>
+        <v>261</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>238</v>
+        <v>346</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>140</v>
+        <v>49</v>
       </c>
       <c r="E100" s="3" t="s">
         <v>38</v>
@@ -5193,27 +5189,27 @@
         <v>23</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="I100" s="3" t="s">
-        <v>122</v>
+        <v>198</v>
       </c>
       <c r="J100" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>265</v>
+        <v>372</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>374</v>
+        <v>177</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>140</v>
+        <v>49</v>
       </c>
       <c r="E101" s="3" t="s">
         <v>38</v>
@@ -5223,27 +5219,27 @@
         <v>23</v>
       </c>
       <c r="H101" s="3" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="I101" s="3" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="J101" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>310</v>
+        <v>187</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>49</v>
+        <v>140</v>
       </c>
       <c r="E102" s="3" t="s">
         <v>38</v>
@@ -5253,24 +5249,24 @@
         <v>23</v>
       </c>
       <c r="H102" s="3" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="I102" s="3" t="s">
         <v>122</v>
       </c>
       <c r="J102" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>379</v>
+        <v>264</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>238</v>
+        <v>377</v>
       </c>
       <c r="D103" s="3" t="s">
         <v>140</v>
@@ -5283,24 +5279,24 @@
         <v>23</v>
       </c>
       <c r="H103" s="3" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="I103" s="3" t="s">
-        <v>122</v>
+        <v>216</v>
       </c>
       <c r="J103" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>382</v>
+        <v>324</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D104" s="3" t="s">
         <v>49</v>
@@ -5313,17 +5309,77 @@
         <v>23</v>
       </c>
       <c r="H104" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="I104" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="J104" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="B105" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="C105" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="D105" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="E105" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F105" s="3"/>
+      <c r="G105" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H105" s="3" t="s">
         <v>383</v>
       </c>
-      <c r="I104" s="3" t="s">
+      <c r="I105" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="J105" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="B106" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="C106" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="D106" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E106" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F106" s="3"/>
+      <c r="G106" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H106" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="I106" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="J104" s="3">
-        <v>21</v>
+      <c r="J106" s="3">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J104"/>
+  <autoFilter ref="A1:J106"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -5428,6 +5484,8 @@
     <hyperlink ref="H102" r:id="rId101"/>
     <hyperlink ref="H103" r:id="rId102"/>
     <hyperlink ref="H104" r:id="rId103"/>
+    <hyperlink ref="H105" r:id="rId104"/>
+    <hyperlink ref="H106" r:id="rId105"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5435,7 +5493,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="46" customWidth="1"/>
+    <col min="1" max="1" width="37" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
@@ -5469,32 +5527,32 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>117</v>
+        <v>186</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>118</v>
+        <v>187</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>119</v>
+        <v>188</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>121</v>
+        <v>189</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>180</v>
+        <v>191</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>181</v>
+        <v>203</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -5502,18 +5560,18 @@
         <v>23</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>183</v>
+        <v>204</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>169</v>
+        <v>47</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>203</v>
+        <v>222</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -5521,18 +5579,18 @@
         <v>23</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>204</v>
+        <v>223</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>47</v>
+        <v>191</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>215</v>
+        <v>249</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>164</v>
+        <v>218</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -5540,18 +5598,18 @@
         <v>23</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>216</v>
+        <v>250</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>169</v>
+        <v>298</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>247</v>
+        <v>203</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -5559,18 +5617,18 @@
         <v>23</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>248</v>
+        <v>299</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>169</v>
+        <v>308</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>265</v>
+        <v>309</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>266</v>
+        <v>310</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -5578,18 +5636,18 @@
         <v>23</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>267</v>
+        <v>311</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>280</v>
+        <v>312</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>281</v>
+        <v>309</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>182</v>
+        <v>310</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -5597,201 +5655,11 @@
         <v>23</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="C10" s="3" t="s">
         <v>314</v>
       </c>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>352</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="s">
-        <v>371</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="s">
-        <v>378</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>379</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>380</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G18"/>
+  <autoFilter ref="A1:G8"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -5800,16 +5668,6 @@
     <hyperlink ref="G6" r:id="rId5"/>
     <hyperlink ref="G7" r:id="rId6"/>
     <hyperlink ref="G8" r:id="rId7"/>
-    <hyperlink ref="G9" r:id="rId8"/>
-    <hyperlink ref="G10" r:id="rId9"/>
-    <hyperlink ref="G11" r:id="rId10"/>
-    <hyperlink ref="G12" r:id="rId11"/>
-    <hyperlink ref="G13" r:id="rId12"/>
-    <hyperlink ref="G14" r:id="rId13"/>
-    <hyperlink ref="G15" r:id="rId14"/>
-    <hyperlink ref="G16" r:id="rId15"/>
-    <hyperlink ref="G17" r:id="rId16"/>
-    <hyperlink ref="G18" r:id="rId17"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5823,10 +5681,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="2">
@@ -5839,7 +5697,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="B3" s="3">
         <v>20</v>
@@ -5847,7 +5705,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="B4" s="3">
         <v>20</v>
@@ -5855,7 +5713,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B5" s="3">
         <v>19</v>
@@ -5863,7 +5721,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>329</v>
+        <v>342</v>
       </c>
       <c r="B6" s="3">
         <v>15</v>
@@ -5879,7 +5737,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="B8" s="3">
         <v>12</v>
@@ -5887,7 +5745,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="B9" s="3">
         <v>11</v>
@@ -5895,7 +5753,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="B10" s="3">
         <v>11</v>
@@ -5903,7 +5761,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="B11" s="3">
         <v>10</v>
@@ -5911,7 +5769,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="B12" s="3">
         <v>10</v>
@@ -5919,7 +5777,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="B13" s="3">
         <v>9</v>
@@ -5927,7 +5785,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="B14" s="3">
         <v>8</v>
@@ -5935,7 +5793,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>344</v>
+        <v>357</v>
       </c>
       <c r="B15" s="3">
         <v>6</v>
@@ -5943,7 +5801,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="B16" s="3">
         <v>6</v>
@@ -5965,7 +5823,7 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="2">
@@ -6010,7 +5868,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>242</v>
+        <v>187</v>
       </c>
       <c r="B7" s="3">
         <v>3</v>
@@ -6018,15 +5876,15 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>48</v>
+        <v>242</v>
       </c>
       <c r="B8" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>130</v>
+        <v>48</v>
       </c>
       <c r="B9" s="3">
         <v>2</v>
@@ -6034,7 +5892,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>185</v>
+        <v>130</v>
       </c>
       <c r="B10" s="3">
         <v>2</v>
@@ -6042,7 +5900,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>228</v>
+        <v>180</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -6050,7 +5908,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>237</v>
+        <v>203</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -6058,7 +5916,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>265</v>
+        <v>227</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -6066,7 +5924,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>310</v>
+        <v>238</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -6074,7 +5932,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>363</v>
+        <v>261</v>
       </c>
       <c r="B15" s="3">
         <v>2</v>
@@ -6082,10 +5940,10 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>55</v>
+        <v>264</v>
       </c>
       <c r="B16" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -6103,16 +5961,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="2">
@@ -6218,13 +6076,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>130</v>
+        <v>187</v>
       </c>
       <c r="C9" s="3">
-        <v>3.6</v>
+        <v>4.0</v>
       </c>
       <c r="D9" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -6232,13 +6090,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>55</v>
+        <v>130</v>
       </c>
       <c r="C10" s="3">
-        <v>3.0</v>
+        <v>3.6</v>
       </c>
       <c r="D10" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -6246,10 +6104,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>144</v>
+        <v>55</v>
       </c>
       <c r="C11" s="3">
-        <v>2.6</v>
+        <v>3.0</v>
       </c>
       <c r="D11" s="3">
         <v>1</v>
@@ -6260,13 +6118,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>185</v>
+        <v>144</v>
       </c>
       <c r="C12" s="3">
         <v>2.6</v>
       </c>
       <c r="D12" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -6274,7 +6132,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>363</v>
+        <v>180</v>
       </c>
       <c r="C13" s="3">
         <v>2.6</v>
@@ -6288,13 +6146,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>149</v>
+        <v>309</v>
       </c>
       <c r="C14" s="3">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="D14" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -6302,13 +6160,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>228</v>
+        <v>149</v>
       </c>
       <c r="C15" s="3">
         <v>2.4</v>
       </c>
       <c r="D15" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -6316,7 +6174,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>237</v>
+        <v>203</v>
       </c>
       <c r="C16" s="3">
         <v>2.4</v>
@@ -6342,15 +6200,15 @@
         <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="B2" s="3">
         <v>1</v>
@@ -6364,10 +6222,10 @@
         <v>38</v>
       </c>
       <c r="B3" s="3">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="4">
@@ -6375,10 +6233,10 @@
         <v>43</v>
       </c>
       <c r="B4" s="3">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
   </sheetData>
@@ -6397,7 +6255,7 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="2">
@@ -6405,7 +6263,7 @@
         <v>49</v>
       </c>
       <c r="B2" s="3">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3">
@@ -6426,15 +6284,15 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>175</v>
+        <v>219</v>
       </c>
       <c r="B5" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>198</v>
+        <v>170</v>
       </c>
       <c r="B6" s="3">
         <v>2</v>
@@ -6442,7 +6300,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="B7" s="3">
         <v>2</v>
@@ -6469,10 +6327,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>26</v>
@@ -6484,10 +6342,10 @@
         <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>21</v>
@@ -6504,28 +6362,28 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>286</v>
@@ -6536,31 +6394,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>164</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
     </row>
     <row r="4">
@@ -6568,28 +6426,28 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>243</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>88</v>
@@ -6600,28 +6458,28 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>317</v>
+        <v>330</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>164</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="F5" s="3">
         <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>88</v>
@@ -6632,31 +6490,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="F6" s="3">
         <v>88</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
     </row>
     <row r="7">
@@ -6664,7 +6522,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>242</v>
@@ -6673,22 +6531,22 @@
         <v>276</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="F7" s="3">
         <v>84</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="8">
@@ -6696,31 +6554,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>164</v>
+        <v>193</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>409</v>
+        <v>423</v>
       </c>
       <c r="F8" s="3">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>436</v>
+        <v>122</v>
       </c>
     </row>
     <row r="9">
@@ -6728,31 +6586,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>192</v>
+        <v>164</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>420</v>
+        <v>412</v>
       </c>
       <c r="F9" s="3">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>431</v>
+        <v>443</v>
       </c>
     </row>
     <row r="10">
@@ -6760,31 +6618,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>443</v>
+        <v>193</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="F10" s="3">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>88</v>
+        <v>434</v>
       </c>
     </row>
     <row r="11">
@@ -6792,31 +6650,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>419</v>
+        <v>448</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>243</v>
+        <v>449</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="F11" s="3">
         <v>70</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>142</v>
+        <v>88</v>
       </c>
     </row>
     <row r="12">
@@ -6824,31 +6682,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>450</v>
+        <v>422</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>451</v>
+        <v>243</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>409</v>
+        <v>423</v>
       </c>
       <c r="F12" s="3">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>454</v>
+        <v>142</v>
       </c>
     </row>
     <row r="13">
@@ -6862,25 +6720,25 @@
         <v>456</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>164</v>
+        <v>457</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>457</v>
+        <v>412</v>
       </c>
       <c r="F13" s="3">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>458</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I13" s="3" t="s">
         <v>459</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>81</v>
+        <v>460</v>
       </c>
     </row>
     <row r="14">
@@ -6888,31 +6746,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>331</v>
+        <v>461</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>332</v>
+        <v>462</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>333</v>
+        <v>164</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>409</v>
+        <v>463</v>
       </c>
       <c r="F14" s="3">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>334</v>
+        <v>465</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>219</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15">
@@ -6920,31 +6778,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>461</v>
+        <v>344</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>281</v>
+        <v>345</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>182</v>
+        <v>346</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="F15" s="3">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>463</v>
+        <v>347</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>142</v>
+        <v>216</v>
       </c>
     </row>
     <row r="16">
@@ -6952,31 +6810,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>438</v>
+        <v>284</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>192</v>
+        <v>262</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>457</v>
+        <v>429</v>
       </c>
       <c r="F16" s="3">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>467</v>
+        <v>122</v>
       </c>
     </row>
     <row r="17">
@@ -6984,31 +6842,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>469</v>
+        <v>281</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>238</v>
+        <v>177</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>426</v>
+        <v>412</v>
       </c>
       <c r="F17" s="3">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>59</v>
+        <v>142</v>
       </c>
     </row>
     <row r="18">
@@ -7016,31 +6874,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>164</v>
+        <v>188</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>420</v>
+        <v>429</v>
       </c>
       <c r="F18" s="3">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>219</v>
+        <v>59</v>
       </c>
     </row>
     <row r="19">
@@ -7048,31 +6906,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>477</v>
+        <v>98</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>257</v>
+        <v>99</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="F19" s="3">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>478</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I19" s="3" t="s">
         <v>479</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>88</v>
+        <v>122</v>
       </c>
     </row>
     <row r="20">
@@ -7089,10 +6947,10 @@
         <v>164</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>409</v>
+        <v>423</v>
       </c>
       <c r="F20" s="3">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>482</v>
@@ -7104,7 +6962,7 @@
         <v>483</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>484</v>
+        <v>216</v>
       </c>
     </row>
     <row r="21">
@@ -7112,31 +6970,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="D21" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="F21" s="3">
+        <v>39</v>
+      </c>
+      <c r="G21" s="3" t="s">
         <v>486</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="H21" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I21" s="3" t="s">
         <v>487</v>
       </c>
-      <c r="E21" s="3" t="s">
-        <v>457</v>
-      </c>
-      <c r="F21" s="3">
-        <v>34</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>488</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>489</v>
-      </c>
       <c r="J21" s="3" t="s">
-        <v>142</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>

--- a/reports/devops-jobs-israel-2026-W41.xlsx
+++ b/reports/devops-jobs-israel-2026-W41.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="505">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="507">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-09T13:05:08</t>
+    <t xml:space="preserve">2026-10-11T12:37:32</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -228,18 +228,6 @@
     <t xml:space="preserve">https://join.jfrog.com/job/?job=7434101&amp;gh_jid=7434101</t>
   </si>
   <si>
-    <t xml:space="preserve">R&amp;D Director</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=8235896&amp;gh_jid=8235896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-28</t>
-  </si>
-  <si>
     <t xml:space="preserve">Senior Software Engineer</t>
   </si>
   <si>
@@ -510,22 +498,169 @@
     <t xml:space="preserve">2026-09-07</t>
   </si>
   <si>
-    <t xml:space="preserve">Nym</t>
+    <t xml:space="preserve">DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vectorious Medical Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-vectorious-medical-technologies-4478097565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Platform Engineer- CTI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dream</t>
   </si>
   <si>
     <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nym-4473896883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eitan Medical</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-platform-engineer-cti-at-dream-4465727084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer (25769)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yael Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-25769-at-yael-group-4474444402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer - Data Platform (Cortex)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palo Alto Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-data-platform-cortex-at-palo-alto-networks-4455871961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Principal DevOps Engineer (Cortex Agentix Endpoint Security)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-devops-engineer-cortex-agentix-endpoint-security-at-palo-alto-networks-4418753719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer (37047)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-37047-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4477184463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Checkmarx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-checkmarx-4439196775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gini-Apps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gini-apps-4476189127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stealth Startup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-stealth-startup-4475656469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connecteam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4290904319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARAN Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-aran-software-4478307184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comblack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-comblack-4477185811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MalamTeam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-malamteam-4478301843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akeyless Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-akeyless-security-4457183616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer - Cloud Infra Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-cloud-infra-team-at-wix-4478094744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bitsight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-bitsight-4476962715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr. DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zscaler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-devops-engineer-at-zscaler-4465317702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fetcherr</t>
   </si>
   <si>
     <t xml:space="preserve">Netanya, Center District, Israel</t>
@@ -534,238 +669,82 @@
     <t xml:space="preserve">Netanya</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-eitan-medical-4461889332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Platform Engineer- CTI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dream</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-platform-engineer-cti-at-dream-4465727084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (25769)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yael Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-25769-at-yael-group-4474444402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer - Data Platform (Cortex)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palo Alto Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-data-platform-cortex-at-palo-alto-networks-4455871961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Principal DevOps Engineer (Cortex Agentix Endpoint Security)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-devops-engineer-cortex-agentix-endpoint-security-at-palo-alto-networks-4418753719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (37047)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-37047-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4477184463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Checkmarx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-checkmarx-4439196775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gini-Apps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gini-apps-4476189127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stealth Startup</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-stealth-startup-4475760813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Buildots</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-buildots-4473477683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comblack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-comblack-4477185811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Akeyless Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-akeyless-security-4457183616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blink</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-blink-4473214725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sr. DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zscaler</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-devops-engineer-at-zscaler-4465317702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bitsight</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-bitsight-4476962715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fetcherr</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fetcherr-4429844723</t>
   </si>
   <si>
     <t xml:space="preserve">2026-10-05</t>
   </si>
   <si>
-    <t xml:space="preserve">Cellebrite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-cellebrite-4469980397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-22</t>
-  </si>
-  <si>
     <t xml:space="preserve">Fig Security</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fig-security-4475988067</t>
   </si>
   <si>
-    <t xml:space="preserve">Personetics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-personetics-4428829912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moon Active</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-moon-active-4447023421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Polytex Technologies</t>
+    <t xml:space="preserve">Gong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-gong-4457888927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GenAI Group DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/genai-group-devops-engineer-at-elbit-systems-israel-4395652910</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4475164979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-4474645372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gloat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gloat-4474071911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cybersixgill, a Bitsight Company</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cybersixgill-a-bitsight-company-4476927366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cisco</t>
   </si>
   <si>
     <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-polytex-technologies-4473474269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-gong-4457888927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extreme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-devops-engineer-at-extreme-4475385097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4475164979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-4474645372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gloat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gloat-4474071911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cybersixgill, a Bitsight Company</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cybersixgill-a-bitsight-company-4476927366</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-cisco-4478317023</t>
   </si>
   <si>
     <t xml:space="preserve">Commit</t>
@@ -804,10 +783,25 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-devops-lead-at-april-4416179005</t>
   </si>
   <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
+    <t xml:space="preserve">AITAN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-aitan-4478069626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps &amp; Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Varonis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-varonis-4478303514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medulla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-medulla-4478313160</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-elbit-systems-israel-4394529806</t>
@@ -822,28 +816,22 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sqlink-group-4476701773</t>
   </si>
   <si>
+    <t xml:space="preserve">DevOps Engineer #8106</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tesnet Group Ltd</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-tesnet-group-ltd-4477160595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DriveNets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-devops-engineer-at-drivenets-4465793281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Staff Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grubhub</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/staff-site-reliability-engineer-at-grubhub-4473025762</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-%238106-at-tesnet-group-ltd-4477160595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps &amp; Infrastructure Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yanolja Go Global</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-team-lead-at-yanolja-go-global-4475903431</t>
   </si>
   <si>
     <t xml:space="preserve">Senior Site Reliability Engineering - Storage</t>
@@ -870,6 +858,15 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-integrator-sre-at-compie-technologies-4477142119</t>
   </si>
   <si>
+    <t xml:space="preserve">Site Reliability Engineer (SRE) On-Prem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-on-prem-at-dream-4463814798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-09</t>
+  </si>
+  <si>
     <t xml:space="preserve">Software Engineer III, Platform Engineering and Infrastructure</t>
   </si>
   <si>
@@ -882,27 +879,12 @@
     <t xml:space="preserve">2026-09-16</t>
   </si>
   <si>
-    <t xml:space="preserve">Cloud Platform &amp; SRE Group Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-sre-group-leader-at-extreme-4450267100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-07</t>
-  </si>
-  <si>
     <t xml:space="preserve">SciPlay</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-sciplay-4391151881</t>
   </si>
   <si>
-    <t xml:space="preserve">Medulla</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-medulla-4475546635</t>
-  </si>
-  <si>
     <t xml:space="preserve">Infrastructure Engineer (Kubernetes &amp; Node.js)</t>
   </si>
   <si>
@@ -936,13 +918,10 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fiverr-4458388230</t>
   </si>
   <si>
-    <t xml:space="preserve">Cloud DevOps Technical Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OnTarget Communications</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-devops-technical-manager-at-ontarget-communications-4475801640</t>
+    <t xml:space="preserve">MIND</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-mind-4477244856</t>
   </si>
   <si>
     <t xml:space="preserve">Software Infrastructure Engineer</t>
@@ -957,6 +936,15 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-infrastructure-engineer-at-teracyte-analytics-4475993753</t>
   </si>
   <si>
+    <t xml:space="preserve">Research Infra Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/research-infra-engineer-at-dream-4370342612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-20</t>
+  </si>
+  <si>
     <t xml:space="preserve">MLOps &amp; Cloud Engineer</t>
   </si>
   <si>
@@ -984,6 +972,15 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-software-infra-engineer-at-biocatch-4447894244</t>
   </si>
   <si>
+    <t xml:space="preserve">Sr Staff DevOps Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-staff-devops-platform-engineer-at-palo-alto-networks-4419603015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-10</t>
+  </si>
+  <si>
     <t xml:space="preserve">AI Platform Engineer</t>
   </si>
   <si>
@@ -1017,13 +1014,13 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-developer-devops-and-infrastructure-at-rapyd-4475489875</t>
   </si>
   <si>
-    <t xml:space="preserve">DoiT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-doit-4463987032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-13</t>
+    <t xml:space="preserve">TAIRC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Akiva, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-tairc-4475262509</t>
   </si>
   <si>
     <t xml:space="preserve">TeraSky</t>
@@ -1032,12 +1029,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-terasky-4455198528</t>
   </si>
   <si>
-    <t xml:space="preserve">IT Infrastructure &amp; Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-cloud-engineer-at-moon-active-4447031167</t>
-  </si>
-  <si>
     <t xml:space="preserve">Senior Cloud Engineer (GCP Focus)</t>
   </si>
   <si>
@@ -1053,375 +1044,399 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloud-engineer-gcp-focus-at-myops-by-yael-group-4477131302</t>
   </si>
   <si>
+    <t xml:space="preserve">Senior Cloud Network &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Applied Materials - Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloud-network-devops-engineer-at-applied-materials-israel-4474407748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT DevOps Engineer - 244284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-devops-engineer-244284-at-experis-israel-4475777772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer (FinOps oriented)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CloudTeam.ai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FinOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-finops-oriented-at-cloudteam-ai-4473603103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior System &amp; Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Final</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat HaSharon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-infrastructure-engineer-at-final-4475581791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Infrastructure Engineer - Proxy Network</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nimble</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-proxy-network-at-nimble-4475424343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP &amp; System Administrator (36759)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/gcp-system-administrator-36759-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4477174630</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-elbit-systems-israel-4474036853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-system-engineer-at-comda-4473615194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calanit by one</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-calanit-by-one-4478305717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft System Engineer (37652)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-system-engineer-37652-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4477168624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashdod, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-sqlink-group-4473649114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-system-administrator-at-shavit-software-4476766481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft System Administrator (5515)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INGIMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-system-administrator-5515-at-ingima-4476707352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Infrastructure &amp; Automation Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aman Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-automation-engineer-at-aman-group-4477162203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Development Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clarivate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/development-operations-engineer-at-clarivate-4467992253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps &amp; Cloud Infrastructure Intern</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-infrastructure-intern-at-f5-4464650168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Student DevOps Engineer- CxP Commercial Foundation Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Terraform/IaC, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-devops-engineer-cxp-commercial-foundation-services-at-sap-4436819328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Terraform/IaC, Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HPC Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Terraform/IaC, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/hpc-operations-engineer-at-nvidia-4471977303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Monitoring Engineer (Student Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upwind Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-monitoring-engineer-student-position-at-upwind-security-4476759903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Technical Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4452212223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security Analyst (Student Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/security-analyst-student-position-at-upwind-security-4473525994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineer Student, SPIV team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amazon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, CI/CD, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-student-spiv-team-at-amazon-4456348779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Student Software Engineer – Cloud, Big Data, Billing &amp; AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Cloud (any), Docker, Kubernetes, CI/CD, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-software-engineer-%E2%80%93-cloud-big-data-billing-ai-at-sap-4476596020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Production Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Torq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6179167004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kela Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk / IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4461059776</t>
+  </si>
+  <si>
     <t xml:space="preserve">Infrastructure System Engineer</t>
   </si>
   <si>
     <t xml:space="preserve">Logica-IT</t>
   </si>
   <si>
-    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Terraform/IaC, Networking, Automation</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-system-engineer-at-logica-it-4473666027</t>
   </si>
   <si>
-    <t xml:space="preserve">Senior Cloud Network &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Applied Materials - Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloud-network-devops-engineer-at-applied-materials-israel-4474407748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT DevOps Engineer - 244284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-devops-engineer-244284-at-experis-israel-4475777772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (FinOps oriented)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CloudTeam.ai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FinOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-finops-oriented-at-cloudteam-ai-4473603103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior System &amp; Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Final</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat HaSharon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-infrastructure-engineer-at-final-4475581791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Infrastructure Engineer - Proxy Network</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nimble</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-proxy-network-at-nimble-4475424343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP &amp; System Administrator (36759)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/gcp-system-administrator-36759-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4477174630</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-elbit-systems-israel-4474036853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-system-engineer-at-comda-4473615194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft System Engineer (37652)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-system-engineer-37652-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4477168624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ashdod, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-sqlink-group-4473649114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-system-administrator-at-shavit-software-4476766481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft System Administrator (5515)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INGIMA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-system-administrator-5515-at-ingima-4476707352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Talent Integration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-talent-integration-4466204750</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strength Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.2%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.8%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Development Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clarivate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/development-operations-engineer-at-clarivate-4467992253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps &amp; Cloud Infrastructure Intern</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-infrastructure-intern-at-f5-4464650168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Student DevOps Engineer- CxP Commercial Foundation Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Terraform/IaC, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-devops-engineer-cxp-commercial-foundation-services-at-sap-4436819328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Terraform/IaC, Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HPC Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Terraform/IaC, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/hpc-operations-engineer-at-nvidia-4471977303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Monitoring Engineer (Student Position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upwind Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-monitoring-engineer-student-position-at-upwind-security-4476759903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Technical Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4452212223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security Analyst (Student Position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/security-analyst-student-position-at-upwind-security-4473525994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineer Student, SPIV team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amazon Web Services (AWS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, CI/CD, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-student-spiv-team-at-amazon-web-services-aws-4456348779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Student Software Engineer – Cloud, Big Data, Billing &amp; AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Cloud (any), Docker, Kubernetes, CI/CD, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-software-engineer-%E2%80%93-cloud-big-data-billing-ai-at-sap-4476596020</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Production Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Torq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6179167004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kela Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk / IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4461059776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Terraform/IaC, Networking, Automation</t>
-  </si>
-  <si>
     <t xml:space="preserve">Junior CAD Engineer, University Graduate, Google Cloud</t>
   </si>
   <si>
@@ -1431,6 +1446,18 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cad-engineer-university-graduate-google-cloud-at-google-4475452638</t>
   </si>
   <si>
+    <t xml:space="preserve">Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-cye-4477476916</t>
+  </si>
+  <si>
     <t xml:space="preserve">Network Operations Center</t>
   </si>
   <si>
@@ -1452,15 +1479,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
   </si>
   <si>
-    <t xml:space="preserve">Software Engineer Intern</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Docker, Kubernetes, CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/8229871?gh_jid=8229871</t>
-  </si>
-  <si>
     <t xml:space="preserve">Data Operations Student - Nights &amp; Weekend shifts</t>
   </si>
   <si>
@@ -1473,18 +1491,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-operations-student-nights-weekend-shifts-at-voyantis-4473649691</t>
   </si>
   <si>
-    <t xml:space="preserve">Software Engineering INTERN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Cloud (any), CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-intern-at-microsoft-4451071541</t>
-  </si>
-  <si>
     <t xml:space="preserve">Junior SysAdmin / Linux</t>
   </si>
   <si>
@@ -1494,10 +1500,10 @@
     <t xml:space="preserve">Monitoring</t>
   </si>
   <si>
+    <t xml:space="preserve">Troubleshooting</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cloud (any)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Troubleshooting</t>
   </si>
   <si>
     <t xml:space="preserve">Automation</t>
@@ -1658,7 +1664,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="7">
@@ -1666,7 +1672,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8">
@@ -1674,7 +1680,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9">
@@ -1682,7 +1688,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>884</v>
+        <v>868</v>
       </c>
     </row>
     <row r="10">
@@ -1762,7 +1768,7 @@
         <v>24</v>
       </c>
       <c r="B20" s="3">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -1789,28 +1795,28 @@
         <v>412</v>
       </c>
       <c r="B2" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B3" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B4" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="B5" s="3">
         <v>3</v>
@@ -1826,7 +1832,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="B7" s="3">
         <v>1</v>
@@ -1845,42 +1851,42 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="B2" s="3">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="B3" s="3">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="B4" s="3">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="B5" s="3">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
@@ -1888,15 +1894,15 @@
         <v>395</v>
       </c>
       <c r="B6" s="3">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>394</v>
+        <v>371</v>
       </c>
       <c r="B7" s="3">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8">
@@ -1904,20 +1910,20 @@
         <v>398</v>
       </c>
       <c r="B8" s="3">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="B9" s="3">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B10" s="3">
         <v>11</v>
@@ -1925,7 +1931,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="B11" s="3">
         <v>11</v>
@@ -1933,7 +1939,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B12" s="3">
         <v>10</v>
@@ -1941,34 +1947,34 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="B13" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="B14" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="B15" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="B16" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -1993,13 +1999,13 @@
         <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="2">
@@ -2007,13 +2013,13 @@
         <v>24</v>
       </c>
       <c r="B2" s="3">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C2" s="3">
-        <v>12.5</v>
+        <v>11.9</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -2022,88 +2028,88 @@
         <v>23</v>
       </c>
       <c r="B3" s="3">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C3" s="3">
-        <v>35.8</v>
+        <v>54.3</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>9.2</v>
+        <v>8.4</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>3.7</v>
+        <v>1.7</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>33.5</v>
+        <v>34.6</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>16.3</v>
+        <v>15.6</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>23.1</v>
+        <v>20.8</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -2116,7 +2122,7 @@
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="43" customWidth="1"/>
+    <col min="3" max="3" width="44" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -2187,7 +2193,7 @@
         <v>41</v>
       </c>
       <c r="J2" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
@@ -2219,7 +2225,7 @@
         <v>41</v>
       </c>
       <c r="J3" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4">
@@ -2251,7 +2257,7 @@
         <v>41</v>
       </c>
       <c r="J4" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5">
@@ -2283,7 +2289,7 @@
         <v>52</v>
       </c>
       <c r="J5" s="3">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6">
@@ -2315,7 +2321,7 @@
         <v>52</v>
       </c>
       <c r="J6" s="3">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7">
@@ -2347,7 +2353,7 @@
         <v>59</v>
       </c>
       <c r="J7" s="3">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8">
@@ -2379,7 +2385,7 @@
         <v>65</v>
       </c>
       <c r="J8" s="3">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9">
@@ -2411,7 +2417,7 @@
         <v>52</v>
       </c>
       <c r="J9" s="3">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10">
@@ -2428,7 +2434,7 @@
         <v>49</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>70</v>
@@ -2443,7 +2449,7 @@
         <v>72</v>
       </c>
       <c r="J10" s="3">
-        <v>11</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11">
@@ -2451,10 +2457,10 @@
         <v>73</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>49</v>
@@ -2463,27 +2469,27 @@
         <v>43</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J11" s="3">
-        <v>29</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>77</v>
+        <v>47</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>49</v>
@@ -2495,27 +2501,27 @@
         <v>43</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H12" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="I12" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="I12" s="3" t="s">
-        <v>81</v>
-      </c>
       <c r="J12" s="3">
-        <v>39</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>47</v>
+        <v>81</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>49</v>
@@ -2539,7 +2545,7 @@
         <v>84</v>
       </c>
       <c r="J13" s="3">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="14">
@@ -2547,7 +2553,7 @@
         <v>85</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>49</v>
@@ -2571,7 +2577,7 @@
         <v>88</v>
       </c>
       <c r="J14" s="3">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15">
@@ -2579,7 +2585,7 @@
         <v>89</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>49</v>
@@ -2603,7 +2609,7 @@
         <v>92</v>
       </c>
       <c r="J15" s="3">
-        <v>43</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16">
@@ -2611,10 +2617,10 @@
         <v>93</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>49</v>
+        <v>95</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>49</v>
@@ -2623,30 +2629,30 @@
         <v>43</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="J16" s="3">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>49</v>
@@ -2667,7 +2673,7 @@
         <v>102</v>
       </c>
       <c r="J17" s="3">
-        <v>22</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -2675,16 +2681,16 @@
         <v>103</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>104</v>
@@ -2696,21 +2702,21 @@
         <v>105</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="J18" s="3">
-        <v>74</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>49</v>
@@ -2719,51 +2725,51 @@
         <v>38</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>96</v>
+        <v>65</v>
       </c>
       <c r="J19" s="3">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F20" s="3" t="s">
         <v>110</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>111</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H20" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="I20" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="I20" s="3" t="s">
-        <v>65</v>
-      </c>
       <c r="J20" s="3">
-        <v>24</v>
+        <v>44</v>
       </c>
     </row>
     <row r="21">
@@ -2771,48 +2777,48 @@
         <v>113</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="J21" s="3">
-        <v>42</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>120</v>
@@ -2824,21 +2830,21 @@
         <v>121</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>122</v>
+        <v>88</v>
       </c>
       <c r="J22" s="3">
-        <v>1</v>
+        <v>45</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>123</v>
+        <v>47</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>99</v>
+        <v>49</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>49</v>
@@ -2847,27 +2853,27 @@
         <v>43</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>92</v>
+        <v>124</v>
       </c>
       <c r="J23" s="3">
-        <v>43</v>
+        <v>55</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>47</v>
+        <v>125</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>49</v>
@@ -2876,30 +2882,30 @@
         <v>49</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="J24" s="3">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>49</v>
@@ -2908,95 +2914,95 @@
         <v>49</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>131</v>
+        <v>67</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H25" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="I25" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="I25" s="3" t="s">
-        <v>133</v>
-      </c>
       <c r="J25" s="3">
-        <v>49</v>
+        <v>23</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B26" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>130</v>
-      </c>
       <c r="C26" s="3" t="s">
-        <v>49</v>
+        <v>135</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>49</v>
+        <v>136</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F26" s="3" t="s">
-        <v>67</v>
-      </c>
+      <c r="F26" s="3"/>
       <c r="G26" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="J26" s="3">
-        <v>21</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>139</v>
+        <v>95</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>140</v>
+        <v>49</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F27" s="3"/>
+      <c r="F27" s="3" t="s">
+        <v>141</v>
+      </c>
       <c r="G27" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="J27" s="3">
-        <v>2</v>
+        <v>68</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>99</v>
+        <v>146</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>49</v>
@@ -3005,68 +3011,68 @@
         <v>43</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>147</v>
+        <v>52</v>
       </c>
       <c r="J28" s="3">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>49</v>
+        <v>136</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>43</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="J29" s="3">
-        <v>59</v>
+        <v>41</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>155</v>
+        <v>49</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>140</v>
+        <v>49</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>156</v>
@@ -3078,21 +3084,21 @@
         <v>157</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>81</v>
+        <v>158</v>
       </c>
       <c r="J30" s="3">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>49</v>
+        <v>161</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>49</v>
@@ -3100,31 +3106,29 @@
       <c r="E31" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F31" s="3" t="s">
-        <v>160</v>
-      </c>
+      <c r="F31" s="3"/>
       <c r="G31" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J31" s="3">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>47</v>
+        <v>164</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>49</v>
@@ -3137,54 +3141,54 @@
         <v>23</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>166</v>
+        <v>92</v>
       </c>
       <c r="J32" s="3">
-        <v>5</v>
+        <v>27</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>170</v>
+        <v>49</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F33" s="3"/>
       <c r="G33" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>162</v>
+        <v>118</v>
       </c>
       <c r="J33" s="3">
-        <v>32</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="B34" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>173</v>
-      </c>
       <c r="C34" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>49</v>
@@ -3197,13 +3201,13 @@
         <v>23</v>
       </c>
       <c r="H34" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="I34" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="I34" s="3" t="s">
-        <v>96</v>
-      </c>
       <c r="J34" s="3">
-        <v>25</v>
+        <v>47</v>
       </c>
     </row>
     <row r="35">
@@ -3211,46 +3215,48 @@
         <v>175</v>
       </c>
       <c r="B35" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F35" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="G35" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H35" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F35" s="3"/>
-      <c r="G35" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>178</v>
-      </c>
       <c r="I35" s="3" t="s">
-        <v>122</v>
+        <v>88</v>
       </c>
       <c r="J35" s="3">
-        <v>1</v>
+        <v>45</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="B36" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="C36" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="C36" s="3" t="s">
-        <v>164</v>
-      </c>
       <c r="D36" s="3" t="s">
-        <v>49</v>
+        <v>136</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
@@ -3263,28 +3269,26 @@
         <v>182</v>
       </c>
       <c r="J36" s="3">
-        <v>45</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="B37" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="B37" s="3" t="s">
-        <v>180</v>
-      </c>
       <c r="C37" s="3" t="s">
-        <v>164</v>
+        <v>184</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>184</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="F37" s="3"/>
       <c r="G37" s="3" t="s">
         <v>23</v>
       </c>
@@ -3292,24 +3296,24 @@
         <v>185</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>92</v>
+        <v>186</v>
       </c>
       <c r="J37" s="3">
-        <v>43</v>
+        <v>89</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>186</v>
+        <v>159</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>187</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>188</v>
+        <v>166</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>140</v>
+        <v>49</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>38</v>
@@ -3319,24 +3323,24 @@
         <v>23</v>
       </c>
       <c r="H38" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="I38" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="I38" s="3" t="s">
-        <v>190</v>
-      </c>
       <c r="J38" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>191</v>
+        <v>159</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>193</v>
+        <v>161</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>49</v>
@@ -3349,24 +3353,24 @@
         <v>23</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>195</v>
+        <v>163</v>
       </c>
       <c r="J39" s="3">
-        <v>87</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>191</v>
+        <v>159</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>49</v>
@@ -3379,27 +3383,27 @@
         <v>23</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>198</v>
+        <v>112</v>
       </c>
       <c r="J40" s="3">
-        <v>3</v>
+        <v>44</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>191</v>
+        <v>159</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>49</v>
+        <v>136</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>38</v>
@@ -3409,24 +3413,24 @@
         <v>23</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>122</v>
+        <v>163</v>
       </c>
       <c r="J41" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>191</v>
+        <v>159</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>49</v>
@@ -3439,27 +3443,27 @@
         <v>23</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>166</v>
+        <v>182</v>
       </c>
       <c r="J42" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>164</v>
+        <v>200</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>49</v>
+        <v>201</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>38</v>
@@ -3469,10 +3473,10 @@
         <v>23</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>190</v>
+        <v>163</v>
       </c>
       <c r="J43" s="3">
         <v>0</v>
@@ -3483,10 +3487,10 @@
         <v>47</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>49</v>
@@ -3499,24 +3503,24 @@
         <v>23</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="J44" s="3">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>191</v>
+        <v>205</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>56</v>
+        <v>166</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>49</v>
@@ -3529,24 +3533,24 @@
         <v>23</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="J45" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>209</v>
+        <v>47</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>49</v>
@@ -3559,24 +3563,24 @@
         <v>23</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>76</v>
+        <v>118</v>
       </c>
       <c r="J46" s="3">
-        <v>29</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>47</v>
+        <v>210</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>49</v>
@@ -3589,13 +3593,13 @@
         <v>23</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>122</v>
+        <v>72</v>
       </c>
       <c r="J47" s="3">
-        <v>1</v>
+        <v>31</v>
       </c>
     </row>
     <row r="48">
@@ -3603,13 +3607,13 @@
         <v>47</v>
       </c>
       <c r="B48" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C48" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="C48" s="3" t="s">
-        <v>169</v>
-      </c>
       <c r="D48" s="3" t="s">
-        <v>170</v>
+        <v>215</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>43</v>
@@ -3619,13 +3623,13 @@
         <v>23</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J48" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="49">
@@ -3633,13 +3637,13 @@
         <v>47</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>218</v>
+        <v>166</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>219</v>
+        <v>49</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>43</v>
@@ -3649,13 +3653,13 @@
         <v>23</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>221</v>
+        <v>182</v>
       </c>
       <c r="J49" s="3">
-        <v>17</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -3663,10 +3667,10 @@
         <v>47</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>49</v>
@@ -3679,18 +3683,18 @@
         <v>23</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>190</v>
+        <v>222</v>
       </c>
       <c r="J50" s="3">
-        <v>0</v>
+        <v>48</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>191</v>
+        <v>223</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>224</v>
@@ -3699,7 +3703,7 @@
         <v>225</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>49</v>
+        <v>226</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>38</v>
@@ -3709,24 +3713,24 @@
         <v>23</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>96</v>
+        <v>228</v>
       </c>
       <c r="J51" s="3">
-        <v>25</v>
+        <v>38</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>191</v>
+        <v>159</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>49</v>
@@ -3739,27 +3743,27 @@
         <v>23</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>229</v>
+        <v>138</v>
       </c>
       <c r="J52" s="3">
-        <v>70</v>
+        <v>4</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>191</v>
+        <v>159</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>232</v>
+        <v>37</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>38</v>
@@ -3772,27 +3776,27 @@
         <v>233</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>166</v>
+        <v>138</v>
       </c>
       <c r="J53" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>47</v>
+        <v>159</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>234</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F54" s="3"/>
       <c r="G54" s="3" t="s">
@@ -3802,24 +3806,24 @@
         <v>235</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>236</v>
+        <v>138</v>
       </c>
       <c r="J54" s="3">
-        <v>46</v>
+        <v>4</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>237</v>
+        <v>159</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>188</v>
+        <v>161</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>140</v>
+        <v>49</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>38</v>
@@ -3829,27 +3833,27 @@
         <v>23</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>166</v>
+        <v>118</v>
       </c>
       <c r="J55" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>191</v>
+        <v>238</v>
       </c>
       <c r="B56" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="C56" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="C56" s="3" t="s">
-        <v>177</v>
-      </c>
       <c r="D56" s="3" t="s">
-        <v>49</v>
+        <v>226</v>
       </c>
       <c r="E56" s="3" t="s">
         <v>38</v>
@@ -3862,24 +3866,24 @@
         <v>241</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>142</v>
+        <v>163</v>
       </c>
       <c r="J56" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>191</v>
+        <v>159</v>
       </c>
       <c r="B57" s="3" t="s">
         <v>242</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>243</v>
+        <v>200</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>37</v>
+        <v>201</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>38</v>
@@ -3889,10 +3893,10 @@
         <v>23</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>142</v>
+        <v>182</v>
       </c>
       <c r="J57" s="3">
         <v>2</v>
@@ -3900,13 +3904,13 @@
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>191</v>
+        <v>244</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>245</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>177</v>
+        <v>246</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>49</v>
@@ -3919,27 +3923,27 @@
         <v>23</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>142</v>
+        <v>217</v>
       </c>
       <c r="J58" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>191</v>
+        <v>248</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>49</v>
+        <v>136</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>38</v>
@@ -3949,87 +3953,87 @@
         <v>23</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>122</v>
+        <v>217</v>
       </c>
       <c r="J59" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>191</v>
+        <v>251</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>218</v>
+        <v>166</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>219</v>
+        <v>49</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F60" s="3"/>
       <c r="G60" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>190</v>
+        <v>65</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>26</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>251</v>
+        <v>42</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>253</v>
+        <v>184</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F61" s="3"/>
       <c r="G61" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>216</v>
+        <v>163</v>
       </c>
       <c r="J61" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>188</v>
+        <v>56</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>140</v>
+        <v>49</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>38</v>
@@ -4039,30 +4043,30 @@
         <v>23</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>216</v>
+        <v>163</v>
       </c>
       <c r="J62" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>258</v>
+        <v>159</v>
       </c>
       <c r="B63" s="3" t="s">
         <v>259</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F63" s="3"/>
       <c r="G63" s="3" t="s">
@@ -4072,24 +4076,24 @@
         <v>260</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>65</v>
+        <v>163</v>
       </c>
       <c r="J63" s="3">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>191</v>
+        <v>159</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>261</v>
+        <v>224</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>262</v>
+        <v>225</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="E64" s="3" t="s">
         <v>38</v>
@@ -4099,27 +4103,27 @@
         <v>23</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="J64" s="3">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>191</v>
+        <v>159</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="E65" s="3" t="s">
         <v>38</v>
@@ -4129,24 +4133,24 @@
         <v>23</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="J65" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>191</v>
+        <v>265</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>177</v>
+        <v>161</v>
       </c>
       <c r="D66" s="3" t="s">
         <v>49</v>
@@ -4159,57 +4163,57 @@
         <v>23</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="J66" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="B67" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="B67" s="3" t="s">
-        <v>270</v>
-      </c>
       <c r="C67" s="3" t="s">
-        <v>164</v>
+        <v>246</v>
       </c>
       <c r="D67" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F67" s="3"/>
       <c r="G67" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>65</v>
+        <v>163</v>
       </c>
       <c r="J67" s="3">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="C68" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="B68" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="C68" s="3" t="s">
-        <v>164</v>
-      </c>
       <c r="D68" s="3" t="s">
-        <v>49</v>
+        <v>136</v>
       </c>
       <c r="E68" s="3" t="s">
         <v>43</v>
@@ -4219,27 +4223,27 @@
         <v>23</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>41</v>
+        <v>174</v>
       </c>
       <c r="J68" s="3">
-        <v>10</v>
+        <v>47</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>242</v>
+        <v>231</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="E69" s="3" t="s">
         <v>43</v>
@@ -4249,10 +4253,10 @@
         <v>23</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>182</v>
+        <v>88</v>
       </c>
       <c r="J69" s="3">
         <v>45</v>
@@ -4260,43 +4264,43 @@
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>242</v>
+        <v>277</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>276</v>
+        <v>161</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>140</v>
+        <v>49</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F70" s="3"/>
       <c r="G70" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>92</v>
+        <v>118</v>
       </c>
       <c r="J70" s="3">
-        <v>43</v>
+        <v>3</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>281</v>
+        <v>165</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="D71" s="3" t="s">
         <v>49</v>
@@ -4309,24 +4313,24 @@
         <v>23</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>122</v>
+        <v>281</v>
       </c>
       <c r="J71" s="3">
-        <v>1</v>
+        <v>32</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="B72" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="B72" s="3" t="s">
-        <v>284</v>
-      </c>
       <c r="C72" s="3" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>49</v>
@@ -4339,62 +4343,64 @@
         <v>23</v>
       </c>
       <c r="H72" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="I72" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="I72" s="3" t="s">
-        <v>286</v>
-      </c>
       <c r="J72" s="3">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>287</v>
+        <v>53</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>238</v>
+        <v>286</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>188</v>
+        <v>166</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>140</v>
+        <v>49</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F73" s="3"/>
       <c r="G73" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>289</v>
+        <v>222</v>
       </c>
       <c r="J73" s="3">
-        <v>63</v>
+        <v>48</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>53</v>
+        <v>288</v>
       </c>
       <c r="B74" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F74" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="C74" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="D74" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E74" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F74" s="3"/>
       <c r="G74" s="3" t="s">
         <v>23</v>
       </c>
@@ -4402,21 +4408,21 @@
         <v>291</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>236</v>
+        <v>77</v>
       </c>
       <c r="J74" s="3">
-        <v>46</v>
+        <v>41</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>191</v>
+        <v>292</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>292</v>
+        <v>196</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="D75" s="3" t="s">
         <v>49</v>
@@ -4432,10 +4438,10 @@
         <v>293</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>216</v>
+        <v>182</v>
       </c>
       <c r="J75" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76">
@@ -4446,69 +4452,67 @@
         <v>295</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>177</v>
+        <v>161</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F76" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F76" s="3"/>
+      <c r="G76" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H76" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="G76" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H76" s="3" t="s">
-        <v>297</v>
-      </c>
       <c r="I76" s="3" t="s">
-        <v>81</v>
+        <v>138</v>
       </c>
       <c r="J76" s="3">
-        <v>39</v>
+        <v>4</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>298</v>
+        <v>47</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>203</v>
+        <v>297</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>193</v>
+        <v>166</v>
       </c>
       <c r="D77" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F77" s="3"/>
       <c r="G77" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>190</v>
+        <v>88</v>
       </c>
       <c r="J77" s="3">
-        <v>0</v>
+        <v>45</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>300</v>
+        <v>53</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="D78" s="3" t="s">
         <v>49</v>
@@ -4521,30 +4525,30 @@
         <v>23</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>142</v>
+        <v>163</v>
       </c>
       <c r="J78" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>47</v>
+        <v>301</v>
       </c>
       <c r="B79" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="C79" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="C79" s="3" t="s">
-        <v>164</v>
-      </c>
       <c r="D79" s="3" t="s">
-        <v>49</v>
+        <v>136</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F79" s="3"/>
       <c r="G79" s="3" t="s">
@@ -4554,10 +4558,10 @@
         <v>304</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>92</v>
+        <v>182</v>
       </c>
       <c r="J79" s="3">
-        <v>43</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80">
@@ -4565,10 +4569,10 @@
         <v>305</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>306</v>
+        <v>165</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D80" s="3" t="s">
         <v>49</v>
@@ -4581,13 +4585,13 @@
         <v>23</v>
       </c>
       <c r="H80" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="I80" s="3" t="s">
         <v>307</v>
       </c>
-      <c r="I80" s="3" t="s">
-        <v>198</v>
-      </c>
       <c r="J80" s="3">
-        <v>3</v>
+        <v>21</v>
       </c>
     </row>
     <row r="81">
@@ -4595,72 +4599,72 @@
         <v>308</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="E81" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F81" s="3"/>
+      <c r="F81" s="3" t="s">
+        <v>309</v>
+      </c>
       <c r="G81" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="J81" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="B82" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="B82" s="3" t="s">
-        <v>309</v>
-      </c>
       <c r="C82" s="3" t="s">
-        <v>310</v>
+        <v>166</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>140</v>
+        <v>49</v>
       </c>
       <c r="E82" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F82" s="3" t="s">
+      <c r="F82" s="3"/>
+      <c r="G82" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H82" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="G82" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H82" s="3" t="s">
-        <v>314</v>
-      </c>
       <c r="I82" s="3" t="s">
-        <v>190</v>
+        <v>59</v>
       </c>
       <c r="J82" s="3">
-        <v>0</v>
+        <v>46</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="B83" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="B83" s="3" t="s">
-        <v>316</v>
-      </c>
       <c r="C83" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D83" s="3" t="s">
         <v>49</v>
@@ -4673,54 +4677,54 @@
         <v>23</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>59</v>
+        <v>138</v>
       </c>
       <c r="J83" s="3">
-        <v>44</v>
+        <v>4</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>319</v>
+        <v>172</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>164</v>
+        <v>200</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>49</v>
+        <v>201</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F84" s="3"/>
       <c r="G84" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>142</v>
+        <v>319</v>
       </c>
       <c r="J84" s="3">
-        <v>2</v>
+        <v>62</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="B85" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="B85" s="3" t="s">
-        <v>322</v>
-      </c>
       <c r="C85" s="3" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="D85" s="3" t="s">
         <v>49</v>
@@ -4733,24 +4737,24 @@
         <v>23</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="J85" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>177</v>
+        <v>161</v>
       </c>
       <c r="D86" s="3" t="s">
         <v>49</v>
@@ -4763,24 +4767,24 @@
         <v>23</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="J86" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="B87" s="3" t="s">
         <v>326</v>
       </c>
-      <c r="B87" s="3" t="s">
-        <v>327</v>
-      </c>
       <c r="C87" s="3" t="s">
-        <v>177</v>
+        <v>161</v>
       </c>
       <c r="D87" s="3" t="s">
         <v>49</v>
@@ -4793,24 +4797,24 @@
         <v>23</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="J87" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="B88" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="B88" s="3" t="s">
-        <v>330</v>
-      </c>
       <c r="C88" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D88" s="3" t="s">
         <v>49</v>
@@ -4823,30 +4827,30 @@
         <v>23</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="J88" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>53</v>
+        <v>320</v>
       </c>
       <c r="B89" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="C89" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="C89" s="3" t="s">
-        <v>310</v>
-      </c>
       <c r="D89" s="3" t="s">
-        <v>140</v>
+        <v>226</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F89" s="3"/>
       <c r="G89" s="3" t="s">
@@ -4856,10 +4860,10 @@
         <v>333</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>334</v>
+        <v>163</v>
       </c>
       <c r="J89" s="3">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -4867,13 +4871,13 @@
         <v>47</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>218</v>
+        <v>200</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>219</v>
+        <v>201</v>
       </c>
       <c r="E90" s="3" t="s">
         <v>43</v>
@@ -4883,89 +4887,89 @@
         <v>23</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="J90" s="3">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="B91" s="3" t="s">
         <v>337</v>
       </c>
-      <c r="B91" s="3" t="s">
-        <v>227</v>
-      </c>
       <c r="C91" s="3" t="s">
-        <v>164</v>
+        <v>338</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>49</v>
+        <v>136</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F91" s="3"/>
+        <v>43</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>339</v>
+      </c>
       <c r="G91" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>229</v>
+        <v>118</v>
       </c>
       <c r="J91" s="3">
-        <v>70</v>
+        <v>3</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="E92" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F92" s="3" t="s">
-        <v>342</v>
-      </c>
+      <c r="F92" s="3"/>
       <c r="G92" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="J92" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>346</v>
+        <v>232</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="E93" s="3" t="s">
         <v>38</v>
@@ -4978,10 +4982,10 @@
         <v>347</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>216</v>
+        <v>118</v>
       </c>
       <c r="J93" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="94">
@@ -4992,15 +4996,17 @@
         <v>349</v>
       </c>
       <c r="C94" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="D94" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F94" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="E94" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F94" s="3"/>
       <c r="G94" s="3" t="s">
         <v>23</v>
       </c>
@@ -5008,10 +5014,10 @@
         <v>351</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>142</v>
+        <v>217</v>
       </c>
       <c r="J94" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="95">
@@ -5022,55 +5028,53 @@
         <v>353</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>243</v>
+        <v>354</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>38</v>
+        <v>355</v>
       </c>
       <c r="F95" s="3"/>
       <c r="G95" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>122</v>
+        <v>217</v>
       </c>
       <c r="J95" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="D96" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F96" s="3" t="s">
-        <v>357</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="F96" s="3"/>
       <c r="G96" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>216</v>
+        <v>138</v>
       </c>
       <c r="J96" s="3">
         <v>4</v>
@@ -5078,138 +5082,140 @@
     </row>
     <row r="97">
       <c r="A97" s="3" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>360</v>
+        <v>179</v>
       </c>
       <c r="C97" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D97" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E97" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F97" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="G97" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H97" s="3" t="s">
         <v>361</v>
       </c>
-      <c r="D97" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E97" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="F97" s="3"/>
-      <c r="G97" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H97" s="3" t="s">
-        <v>363</v>
-      </c>
       <c r="I97" s="3" t="s">
-        <v>216</v>
+        <v>118</v>
       </c>
       <c r="J97" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>365</v>
+        <v>224</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>164</v>
+        <v>363</v>
       </c>
       <c r="D98" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F98" s="3"/>
       <c r="G98" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="I98" s="3" t="s">
-        <v>142</v>
+        <v>189</v>
       </c>
       <c r="J98" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>187</v>
+        <v>366</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>188</v>
+        <v>161</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>140</v>
+        <v>49</v>
       </c>
       <c r="E99" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F99" s="3" t="s">
-        <v>342</v>
-      </c>
+      <c r="F99" s="3"/>
       <c r="G99" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H99" s="3" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I99" s="3" t="s">
-        <v>122</v>
+        <v>217</v>
       </c>
       <c r="J99" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="B100" s="3" t="s">
         <v>369</v>
       </c>
-      <c r="B100" s="3" t="s">
-        <v>261</v>
-      </c>
       <c r="C100" s="3" t="s">
-        <v>346</v>
+        <v>370</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>49</v>
+        <v>136</v>
       </c>
       <c r="E100" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F100" s="3"/>
+      <c r="F100" s="3" t="s">
+        <v>371</v>
+      </c>
       <c r="G100" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="I100" s="3" t="s">
-        <v>198</v>
+        <v>163</v>
       </c>
       <c r="J100" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>372</v>
+        <v>179</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>49</v>
+        <v>136</v>
       </c>
       <c r="E101" s="3" t="s">
         <v>38</v>
@@ -5219,27 +5225,27 @@
         <v>23</v>
       </c>
       <c r="H101" s="3" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="I101" s="3" t="s">
-        <v>216</v>
+        <v>118</v>
       </c>
       <c r="J101" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>187</v>
+        <v>262</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>188</v>
+        <v>376</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="E102" s="3" t="s">
         <v>38</v>
@@ -5249,27 +5255,27 @@
         <v>23</v>
       </c>
       <c r="H102" s="3" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="I102" s="3" t="s">
-        <v>122</v>
+        <v>217</v>
       </c>
       <c r="J102" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>264</v>
+        <v>323</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>377</v>
+        <v>184</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>140</v>
+        <v>49</v>
       </c>
       <c r="E103" s="3" t="s">
         <v>38</v>
@@ -5279,27 +5285,27 @@
         <v>23</v>
       </c>
       <c r="H103" s="3" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="I103" s="3" t="s">
-        <v>216</v>
+        <v>118</v>
       </c>
       <c r="J103" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>324</v>
+        <v>381</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>49</v>
+        <v>136</v>
       </c>
       <c r="E104" s="3" t="s">
         <v>38</v>
@@ -5309,27 +5315,27 @@
         <v>23</v>
       </c>
       <c r="H104" s="3" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="I104" s="3" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="J104" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>188</v>
+        <v>385</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>140</v>
+        <v>386</v>
       </c>
       <c r="E105" s="3" t="s">
         <v>38</v>
@@ -5339,47 +5345,17 @@
         <v>23</v>
       </c>
       <c r="H105" s="3" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="I105" s="3" t="s">
-        <v>122</v>
+        <v>163</v>
       </c>
       <c r="J105" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="3" t="s">
-        <v>384</v>
-      </c>
-      <c r="B106" s="3" t="s">
-        <v>385</v>
-      </c>
-      <c r="C106" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="D106" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E106" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F106" s="3"/>
-      <c r="G106" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H106" s="3" t="s">
-        <v>386</v>
-      </c>
-      <c r="I106" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="J106" s="3">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J106"/>
+  <autoFilter ref="A1:J105"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -5485,7 +5461,6 @@
     <hyperlink ref="H103" r:id="rId102"/>
     <hyperlink ref="H104" r:id="rId103"/>
     <hyperlink ref="H105" r:id="rId104"/>
-    <hyperlink ref="H106" r:id="rId105"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5493,9 +5468,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="37" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="42" customWidth="1"/>
+    <col min="1" max="1" width="41" customWidth="1"/>
+    <col min="2" max="2" width="33" customWidth="1"/>
+    <col min="3" max="3" width="44" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
@@ -5527,13 +5502,13 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>186</v>
+        <v>159</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>187</v>
+        <v>160</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>188</v>
+        <v>161</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
@@ -5541,18 +5516,18 @@
         <v>23</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>189</v>
+        <v>162</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>191</v>
+        <v>159</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>203</v>
+        <v>190</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -5560,18 +5535,18 @@
         <v>23</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>204</v>
+        <v>191</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>47</v>
+        <v>159</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>222</v>
+        <v>194</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>164</v>
+        <v>180</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -5579,18 +5554,18 @@
         <v>23</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>223</v>
+        <v>195</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>249</v>
+        <v>199</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>218</v>
+        <v>200</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -5598,18 +5573,18 @@
         <v>23</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>250</v>
+        <v>202</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>298</v>
+        <v>205</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>193</v>
+        <v>166</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -5617,18 +5592,18 @@
         <v>23</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>299</v>
+        <v>207</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>308</v>
+        <v>238</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>309</v>
+        <v>239</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>310</v>
+        <v>240</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -5636,18 +5611,18 @@
         <v>23</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>311</v>
+        <v>241</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>312</v>
+        <v>42</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>309</v>
+        <v>254</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>310</v>
+        <v>184</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -5655,11 +5630,144 @@
         <v>23</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>314</v>
+        <v>255</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>387</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G8"/>
+  <autoFilter ref="A1:G15"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -5668,6 +5776,13 @@
     <hyperlink ref="G6" r:id="rId5"/>
     <hyperlink ref="G7" r:id="rId6"/>
     <hyperlink ref="G8" r:id="rId7"/>
+    <hyperlink ref="G9" r:id="rId8"/>
+    <hyperlink ref="G10" r:id="rId9"/>
+    <hyperlink ref="G11" r:id="rId10"/>
+    <hyperlink ref="G12" r:id="rId11"/>
+    <hyperlink ref="G13" r:id="rId12"/>
+    <hyperlink ref="G14" r:id="rId13"/>
+    <hyperlink ref="G15" r:id="rId14"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5681,15 +5796,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="B2" s="3">
         <v>22</v>
@@ -5697,7 +5812,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B3" s="3">
         <v>20</v>
@@ -5705,31 +5820,31 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="B4" s="3">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B5" s="3">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="B6" s="3">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="B7" s="3">
         <v>13</v>
@@ -5737,7 +5852,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B8" s="3">
         <v>12</v>
@@ -5745,7 +5860,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B9" s="3">
         <v>11</v>
@@ -5753,7 +5868,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>393</v>
+        <v>371</v>
       </c>
       <c r="B10" s="3">
         <v>11</v>
@@ -5793,7 +5908,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="B15" s="3">
         <v>6</v>
@@ -5828,7 +5943,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B2" s="3">
         <v>5</v>
@@ -5836,7 +5951,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B3" s="3">
         <v>5</v>
@@ -5844,15 +5959,15 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="B4" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="B5" s="3">
         <v>3</v>
@@ -5860,7 +5975,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="B6" s="3">
         <v>3</v>
@@ -5868,7 +5983,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>187</v>
+        <v>165</v>
       </c>
       <c r="B7" s="3">
         <v>3</v>
@@ -5876,7 +5991,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>242</v>
+        <v>172</v>
       </c>
       <c r="B8" s="3">
         <v>3</v>
@@ -5884,31 +5999,31 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>48</v>
+        <v>179</v>
       </c>
       <c r="B9" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>130</v>
+        <v>224</v>
       </c>
       <c r="B10" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>180</v>
+        <v>231</v>
       </c>
       <c r="B11" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>203</v>
+        <v>48</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -5916,7 +6031,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>227</v>
+        <v>126</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -5924,7 +6039,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>238</v>
+        <v>196</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -5932,7 +6047,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B15" s="3">
         <v>2</v>
@@ -5940,7 +6055,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>264</v>
+        <v>302</v>
       </c>
       <c r="B16" s="3">
         <v>2</v>
@@ -5978,7 +6093,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C2" s="3">
         <v>23.8</v>
@@ -5992,7 +6107,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C3" s="3">
         <v>18.6</v>
@@ -6009,10 +6124,10 @@
         <v>61</v>
       </c>
       <c r="C4" s="3">
-        <v>13.4</v>
+        <v>10.1</v>
       </c>
       <c r="D4" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -6020,7 +6135,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C5" s="3">
         <v>9.2</v>
@@ -6062,7 +6177,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>242</v>
+        <v>165</v>
       </c>
       <c r="C8" s="3">
         <v>4.2</v>
@@ -6076,10 +6191,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>187</v>
+        <v>231</v>
       </c>
       <c r="C9" s="3">
-        <v>4.0</v>
+        <v>4.2</v>
       </c>
       <c r="D9" s="3">
         <v>3</v>
@@ -6090,13 +6205,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>130</v>
+        <v>172</v>
       </c>
       <c r="C10" s="3">
-        <v>3.6</v>
+        <v>4.0</v>
       </c>
       <c r="D10" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -6104,13 +6219,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>55</v>
+        <v>179</v>
       </c>
       <c r="C11" s="3">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="D11" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -6118,13 +6233,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="C12" s="3">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="D12" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -6132,13 +6247,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>180</v>
+        <v>224</v>
       </c>
       <c r="C13" s="3">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="D13" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -6146,13 +6261,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>309</v>
+        <v>55</v>
       </c>
       <c r="C14" s="3">
-        <v>2.6</v>
+        <v>3.0</v>
       </c>
       <c r="D14" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -6160,10 +6275,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="C15" s="3">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="D15" s="3">
         <v>1</v>
@@ -6174,10 +6289,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>203</v>
+        <v>302</v>
       </c>
       <c r="C16" s="3">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="D16" s="3">
         <v>2</v>
@@ -6208,7 +6323,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="B2" s="3">
         <v>1</v>
@@ -6233,7 +6348,7 @@
         <v>43</v>
       </c>
       <c r="B4" s="3">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>405</v>
@@ -6263,15 +6378,15 @@
         <v>49</v>
       </c>
       <c r="B2" s="3">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B3" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4">
@@ -6284,26 +6399,34 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>219</v>
+        <v>201</v>
       </c>
       <c r="B5" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>170</v>
+        <v>226</v>
       </c>
       <c r="B6" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>232</v>
+        <v>215</v>
       </c>
       <c r="B7" s="3">
-        <v>2</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="B8" s="3">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -6386,7 +6509,7 @@
         <v>414</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="3">
@@ -6400,7 +6523,7 @@
         <v>416</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>417</v>
@@ -6418,7 +6541,7 @@
         <v>419</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>420</v>
+        <v>281</v>
       </c>
     </row>
     <row r="4">
@@ -6426,31 +6549,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>421</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>422</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>423</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I4" s="3" t="s">
         <v>424</v>
       </c>
-      <c r="H4" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>425</v>
-      </c>
       <c r="J4" s="3" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="5">
@@ -6458,13 +6581,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>412</v>
@@ -6473,16 +6596,16 @@
         <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>427</v>
       </c>
-      <c r="H5" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>428</v>
-      </c>
       <c r="J5" s="3" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6">
@@ -6490,31 +6613,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>359</v>
+        <v>375</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>360</v>
+        <v>428</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>361</v>
+        <v>166</v>
       </c>
       <c r="E6" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="F6" s="3">
+        <v>100</v>
+      </c>
+      <c r="G6" s="3" t="s">
         <v>429</v>
       </c>
-      <c r="F6" s="3">
-        <v>88</v>
-      </c>
-      <c r="G6" s="3" t="s">
+      <c r="H6" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I6" s="3" t="s">
         <v>430</v>
       </c>
-      <c r="H6" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>363</v>
-      </c>
       <c r="J6" s="3" t="s">
-        <v>216</v>
+        <v>431</v>
       </c>
     </row>
     <row r="7">
@@ -6522,31 +6645,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>431</v>
+        <v>352</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>242</v>
+        <v>353</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>276</v>
+        <v>354</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>412</v>
+        <v>432</v>
       </c>
       <c r="F7" s="3">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>433</v>
+        <v>356</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>434</v>
+        <v>217</v>
       </c>
     </row>
     <row r="8">
@@ -6554,31 +6677,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="F8" s="3">
+        <v>84</v>
+      </c>
+      <c r="G8" s="3" t="s">
         <v>435</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="H8" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>436</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>423</v>
-      </c>
-      <c r="F8" s="3">
-        <v>83</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>437</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>438</v>
-      </c>
       <c r="J8" s="3" t="s">
-        <v>122</v>
+        <v>431</v>
       </c>
     </row>
     <row r="9">
@@ -6586,31 +6709,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="F9" s="3">
+        <v>83</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>439</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="H9" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I9" s="3" t="s">
         <v>440</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>412</v>
-      </c>
-      <c r="F9" s="3">
-        <v>80</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>441</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>442</v>
-      </c>
       <c r="J9" s="3" t="s">
-        <v>443</v>
+        <v>118</v>
       </c>
     </row>
     <row r="10">
@@ -6618,31 +6741,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="F10" s="3">
+        <v>80</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>444</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>436</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>423</v>
-      </c>
-      <c r="F10" s="3">
-        <v>74</v>
-      </c>
-      <c r="G10" s="3" t="s">
+      <c r="J10" s="3" t="s">
         <v>445</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>446</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>434</v>
       </c>
     </row>
     <row r="11">
@@ -6650,31 +6773,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="F11" s="3">
+        <v>74</v>
+      </c>
+      <c r="G11" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="H11" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I11" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>449</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>423</v>
-      </c>
-      <c r="F11" s="3">
-        <v>70</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>450</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>451</v>
-      </c>
       <c r="J11" s="3" t="s">
-        <v>88</v>
+        <v>431</v>
       </c>
     </row>
     <row r="12">
@@ -6682,31 +6805,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="C12" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="E12" s="3" t="s">
         <v>422</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>423</v>
       </c>
       <c r="F12" s="3">
         <v>70</v>
       </c>
       <c r="G12" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I12" s="3" t="s">
         <v>453</v>
       </c>
-      <c r="H12" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>454</v>
-      </c>
       <c r="J12" s="3" t="s">
-        <v>142</v>
+        <v>84</v>
       </c>
     </row>
     <row r="13">
@@ -6714,31 +6837,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="F13" s="3">
+        <v>70</v>
+      </c>
+      <c r="G13" s="3" t="s">
         <v>455</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="H13" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I13" s="3" t="s">
         <v>456</v>
       </c>
-      <c r="D13" s="3" t="s">
-        <v>457</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>412</v>
-      </c>
-      <c r="F13" s="3">
-        <v>68</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>458</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>459</v>
-      </c>
       <c r="J13" s="3" t="s">
-        <v>460</v>
+        <v>138</v>
       </c>
     </row>
     <row r="14">
@@ -6746,31 +6869,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="F14" s="3">
+        <v>68</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I14" s="3" t="s">
         <v>461</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="J14" s="3" t="s">
         <v>462</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>463</v>
-      </c>
-      <c r="F14" s="3">
-        <v>61</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>464</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>465</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="15">
@@ -6778,19 +6901,19 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>344</v>
+        <v>463</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>345</v>
+        <v>464</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>346</v>
+        <v>166</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>412</v>
+        <v>465</v>
       </c>
       <c r="F15" s="3">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>466</v>
@@ -6799,10 +6922,10 @@
         <v>23</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>347</v>
+        <v>467</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>216</v>
+        <v>77</v>
       </c>
     </row>
     <row r="16">
@@ -6810,31 +6933,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>284</v>
+        <v>469</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>262</v>
+        <v>363</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>429</v>
+        <v>412</v>
       </c>
       <c r="F16" s="3">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>122</v>
+        <v>217</v>
       </c>
     </row>
     <row r="17">
@@ -6842,31 +6965,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>177</v>
+        <v>225</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>412</v>
+        <v>432</v>
       </c>
       <c r="F17" s="3">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>142</v>
+        <v>118</v>
       </c>
     </row>
     <row r="18">
@@ -6874,31 +6997,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>188</v>
+        <v>56</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>429</v>
+        <v>465</v>
       </c>
       <c r="F18" s="3">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>59</v>
+        <v>182</v>
       </c>
     </row>
     <row r="19">
@@ -6906,31 +7029,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>98</v>
+        <v>277</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>99</v>
+        <v>161</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>423</v>
+        <v>412</v>
       </c>
       <c r="F19" s="3">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
     </row>
     <row r="20">
@@ -6938,31 +7061,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>164</v>
+        <v>180</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>423</v>
+        <v>432</v>
       </c>
       <c r="F20" s="3">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>216</v>
+        <v>59</v>
       </c>
     </row>
     <row r="21">
@@ -6970,31 +7093,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>310</v>
+        <v>166</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="F21" s="3">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>88</v>
+        <v>217</v>
       </c>
     </row>
   </sheetData>
